--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE72"/>
+  <dimension ref="A1:AE73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 8475-2025</t>
+          <t>A 37056-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45709</v>
+        <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         <v>15</v>
       </c>
       <c r="U3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
@@ -793,46 +793,46 @@
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 8475-2025 artfynd.xlsx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 37056-2026 artfynd.xlsx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 8475-2025 karta.png", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 37056-2026 karta.png", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 8475-2025 georefererad karta.tif", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 37056-2026 georefererad karta.tif", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="Z3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 8475-2025 karta knärot.png", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 37056-2026 karta knärot.png", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 8475-2025 FSC-klagomål.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 37056-2026 FSC-klagomål.docx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 8475-2025 FSC-klagomål mail.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 37056-2026 FSC-klagomål mail.docx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 8475-2025 tillsynsbegäran.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 37056-2026 tillsynsbegäran.docx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 8475-2025 tillsynsbegäran mail.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 37056-2026 tillsynsbegäran mail.docx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/fåglar/A 8475-2025 prioriterade fågelarter.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/fåglar/A 37056-2026 prioriterade fågelarter.docx", "A 37056-2026")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 37056-2026</t>
+          <t>A 8475-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46273</v>
+        <v>45709</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>15</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
@@ -913,39 +913,39 @@
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 37056-2026 artfynd.xlsx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 8475-2025 artfynd.xlsx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 37056-2026 karta.png", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 8475-2025 karta.png", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 37056-2026 georefererad karta.tif", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 8475-2025 georefererad karta.tif", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="Z4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 37056-2026 karta knärot.png", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 8475-2025 karta knärot.png", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 37056-2026 FSC-klagomål.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 8475-2025 FSC-klagomål.docx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 37056-2026 FSC-klagomål mail.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 8475-2025 FSC-klagomål mail.docx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 37056-2026 tillsynsbegäran.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 8475-2025 tillsynsbegäran.docx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 37056-2026 tillsynsbegäran mail.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 8475-2025 tillsynsbegäran mail.docx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/fåglar/A 37056-2026 prioriterade fågelarter.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/fåglar/A 8475-2025 prioriterade fågelarter.docx", "A 8475-2025")</f>
         <v/>
       </c>
     </row>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25961-2026</t>
+          <t>A 53870-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46181</v>
+        <v>44880</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1430,8 +1430,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>7.3</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1443,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1455,10 +1460,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1467,50 +1472,46 @@
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
-        <v/>
-      </c>
-      <c r="Z9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 53870-2022</t>
+          <t>A 25961-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1524,10 +1525,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44880</v>
+        <v>46181</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1539,13 +1540,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>2.3</v>
+        <v>7.3</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1557,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1569,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1581,39 +1577,43 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
+        <v/>
+      </c>
+      <c r="Z10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44470</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44545</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44600</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>44620</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 19082-2023</t>
+          <t>A 41446-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2150,10 +2150,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45048</v>
+        <v>45175</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>6.5</v>
+        <v>8.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2214,7 +2214,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 40815-2022</t>
+          <t>A 30621-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44824</v>
+        <v>45112</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>15.9</v>
+        <v>3.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2287,7 +2287,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 55072-2021</t>
+          <t>A 30623-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2301,10 +2301,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44474</v>
+        <v>45112</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2360,7 +2360,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 52795-2023</t>
+          <t>A 51096-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45226</v>
+        <v>45603</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2433,7 +2433,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 52802-2022</t>
+          <t>A 40607-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44875</v>
+        <v>45556</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2462,13 +2462,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>5.8</v>
+        <v>3.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2511,7 +2506,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 6734-2022</t>
+          <t>A 19420-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2525,10 +2520,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44602</v>
+        <v>45429</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2541,7 +2536,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>32.3</v>
+        <v>3.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2584,7 +2579,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 30621-2023</t>
+          <t>A 60754-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2598,10 +2593,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45112</v>
+        <v>45644</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2614,7 +2609,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2657,7 +2652,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 30623-2023</t>
+          <t>A 24023-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2671,10 +2666,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45112</v>
+        <v>45796</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2687,7 +2682,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2730,7 +2725,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 59853-2022</t>
+          <t>A 11771-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2744,10 +2739,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44908</v>
+        <v>45727</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2760,7 +2755,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2803,7 +2798,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 1040-2025</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2817,10 +2812,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45666</v>
+        <v>44491</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2833,7 +2828,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>6.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2876,7 +2871,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 3683-2023</t>
+          <t>A 1040-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2890,10 +2885,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44950</v>
+        <v>45666</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2905,13 +2900,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>6.3</v>
+        <v>1.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2954,7 +2944,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 23574-2023</t>
+          <t>A 59805-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2968,10 +2958,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45077</v>
+        <v>45639</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2984,7 +2974,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3027,7 +3017,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 41446-2023</t>
+          <t>A 10298-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3041,10 +3031,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45175</v>
+        <v>46076</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3056,13 +3046,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>8.4</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3105,7 +3090,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 39717-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3119,10 +3104,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44491</v>
+        <v>45167</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3135,7 +3120,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>6.8</v>
+        <v>2.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3178,7 +3163,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 30634-2023</t>
+          <t>A 38308-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3192,10 +3177,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45112</v>
+        <v>45161</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3208,7 +3193,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>6.2</v>
+        <v>2.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3251,7 +3236,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 26382-2023</t>
+          <t>A 55003-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3265,10 +3250,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45092</v>
+        <v>44886</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3280,13 +3265,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>20.3</v>
+        <v>6.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3329,7 +3309,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 10298-2026</t>
+          <t>A 47123-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3343,10 +3323,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46076</v>
+        <v>45586</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3359,7 +3339,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3402,7 +3382,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 40815-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3416,10 +3396,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44491</v>
+        <v>44824</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3432,7 +3412,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>6.8</v>
+        <v>15.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3475,7 +3455,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 11771-2025</t>
+          <t>A 33022-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3489,10 +3469,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45727</v>
+        <v>45840</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3505,7 +3485,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3565,7 +3545,7 @@
         <v>46000</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3621,7 +3601,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 52809-2022</t>
+          <t>A 55072-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3635,10 +3615,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44875</v>
+        <v>44474</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3650,13 +3630,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3699,7 +3674,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 16735-2023</t>
+          <t>A 10516-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3713,10 +3688,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45030</v>
+        <v>44623</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3729,7 +3704,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>8.699999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3772,7 +3747,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 33022-2025</t>
+          <t>A 10517-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3786,10 +3761,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45840</v>
+        <v>44623</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3802,7 +3777,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3845,7 +3820,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 1906-2022</t>
+          <t>A 50058-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3859,10 +3834,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44575</v>
+        <v>44456</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3874,8 +3849,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3918,7 +3898,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 39269-2023</t>
+          <t>A 26274-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3932,10 +3912,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45166</v>
+        <v>46182</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3948,7 +3928,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3991,7 +3971,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 59612-2021</t>
+          <t>A 26257-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4005,10 +3985,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44491</v>
+        <v>46182</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4021,7 +4001,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4064,7 +4044,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 19266-2024</t>
+          <t>A 27399-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4074,14 +4054,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45428</v>
+        <v>46189</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4094,7 +4074,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4137,7 +4117,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 10516-2022</t>
+          <t>A 27400-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4147,14 +4127,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44623</v>
+        <v>46189</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4167,7 +4147,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4210,7 +4190,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 10517-2022</t>
+          <t>A 6734-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4224,10 +4204,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44623</v>
+        <v>44602</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4240,7 +4220,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.2</v>
+        <v>32.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4283,7 +4263,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 39717-2023</t>
+          <t>A 30634-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4297,10 +4277,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45167</v>
+        <v>45112</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4313,7 +4293,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.3</v>
+        <v>6.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4356,7 +4336,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 26274-2026</t>
+          <t>A 35521-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4370,10 +4350,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46182</v>
+        <v>46262</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4385,8 +4365,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>6.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4429,7 +4414,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 26257-2026</t>
+          <t>A 35459-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4443,10 +4428,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46182</v>
+        <v>46262</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4459,7 +4444,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4502,7 +4487,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 55003-2022</t>
+          <t>A 52795-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4516,10 +4501,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44886</v>
+        <v>45226</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4532,7 +4517,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>6.6</v>
+        <v>3.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4575,7 +4560,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 27399-2026</t>
+          <t>A 37045-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4585,14 +4570,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46189</v>
+        <v>46273</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4604,8 +4589,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>7.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4648,7 +4638,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 27400-2026</t>
+          <t>A 37054-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4658,14 +4648,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46189</v>
+        <v>46273</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4677,8 +4667,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>3</v>
+        <v>6.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4721,7 +4716,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 59609-2021</t>
+          <t>A 37865-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4735,10 +4730,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44491</v>
+        <v>46279</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4750,8 +4745,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>12.7</v>
+        <v>9.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 40607-2024</t>
+          <t>A 16735-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45556</v>
+        <v>45030</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4867,7 +4867,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 59805-2024</t>
+          <t>A 19082-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4881,10 +4881,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45639</v>
+        <v>45048</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4896,8 +4896,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>3</v>
+        <v>6.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4940,7 +4945,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 8193-2023</t>
+          <t>A 26029-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4954,10 +4959,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44974</v>
+        <v>44734</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4975,7 +4980,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>10.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5018,7 +5023,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 8228-2023</t>
+          <t>A 59612-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5032,10 +5037,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44974</v>
+        <v>44491</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5048,7 +5053,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>13.9</v>
+        <v>3.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5091,7 +5096,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 51096-2024</t>
+          <t>A 52802-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5105,10 +5110,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45603</v>
+        <v>44875</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5120,8 +5125,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>1.3</v>
+        <v>5.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5164,7 +5174,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 47123-2024</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5178,10 +5188,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45586</v>
+        <v>44491</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5194,7 +5204,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5237,7 +5247,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 38308-2023</t>
+          <t>A 39269-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5251,10 +5261,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45161</v>
+        <v>45166</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5267,7 +5277,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5310,7 +5320,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 35521-2026</t>
+          <t>A 59609-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5324,10 +5334,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46262</v>
+        <v>44491</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5339,13 +5349,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>6.2</v>
+        <v>12.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5388,7 +5393,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 35459-2026</t>
+          <t>A 19266-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5402,10 +5407,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46262</v>
+        <v>45428</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5418,7 +5423,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5461,7 +5466,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 50058-2021</t>
+          <t>A 52809-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5475,10 +5480,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44456</v>
+        <v>44875</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5496,7 +5501,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5539,7 +5544,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 26029-2022</t>
+          <t>A 3683-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5553,10 +5558,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44734</v>
+        <v>44950</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5574,7 +5579,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>9.699999999999999</v>
+        <v>6.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5617,7 +5622,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 31883-2022</t>
+          <t>A 1906-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5631,10 +5636,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44777</v>
+        <v>44575</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5647,7 +5652,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5690,7 +5695,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 37054-2026</t>
+          <t>A 59853-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5704,10 +5709,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46273</v>
+        <v>44908</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5719,13 +5724,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>6.3</v>
+        <v>0.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5768,7 +5768,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 37045-2026</t>
+          <t>A 8193-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5782,10 +5782,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46273</v>
+        <v>44974</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5846,7 +5846,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 52789-2024</t>
+          <t>A 8228-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5860,10 +5860,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45610</v>
+        <v>44974</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.4</v>
+        <v>13.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5919,7 +5919,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 24023-2025</t>
+          <t>A 31883-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5933,10 +5933,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45796</v>
+        <v>44777</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 19420-2024</t>
+          <t>A 23574-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6006,10 +6006,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45429</v>
+        <v>45077</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6065,7 +6065,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 60754-2024</t>
+          <t>A 26382-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6079,10 +6079,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45644</v>
+        <v>45092</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6094,119 +6094,197 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I71" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72" ht="15" customHeight="1">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>A 52789-2024</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D72" s="1" t="n">
+        <v>45610</v>
+      </c>
+      <c r="E72" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>KUNGSÖR</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
         <v>2.4</v>
       </c>
-      <c r="J71" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
-      <c r="R71" t="n">
-        <v>0</v>
-      </c>
-      <c r="S71" t="n">
-        <v>0</v>
-      </c>
-      <c r="T71" t="n">
-        <v>0</v>
-      </c>
-      <c r="U71" t="n">
-        <v>0</v>
-      </c>
-      <c r="V71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
           <t>S 1310-2022</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Skogsgödsling</t>
         </is>
       </c>
-      <c r="D72" s="1" t="n">
+      <c r="D73" s="1" t="n">
         <v>44628</v>
       </c>
-      <c r="E72" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>KUNGSÖR</t>
-        </is>
-      </c>
-      <c r="I72" t="n">
+      <c r="E73" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>KUNGSÖR</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
         <v>36.9</v>
       </c>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" t="n">
-        <v>0</v>
-      </c>
-      <c r="N72" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" t="n">
-        <v>0</v>
-      </c>
-      <c r="T72" t="n">
-        <v>0</v>
-      </c>
-      <c r="U72" t="n">
-        <v>0</v>
-      </c>
-      <c r="V72" s="2" t="inlineStr"/>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 37056-2026</t>
+          <t>A 8475-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46273</v>
+        <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         <v>15</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
@@ -793,46 +793,46 @@
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 37056-2026 artfynd.xlsx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 8475-2025 artfynd.xlsx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 37056-2026 karta.png", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 8475-2025 karta.png", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 37056-2026 georefererad karta.tif", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 8475-2025 georefererad karta.tif", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="Z3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 37056-2026 karta knärot.png", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 8475-2025 karta knärot.png", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 37056-2026 FSC-klagomål.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 8475-2025 FSC-klagomål.docx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 37056-2026 FSC-klagomål mail.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 8475-2025 FSC-klagomål mail.docx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 37056-2026 tillsynsbegäran.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 8475-2025 tillsynsbegäran.docx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 37056-2026 tillsynsbegäran mail.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 8475-2025 tillsynsbegäran mail.docx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/fåglar/A 37056-2026 prioriterade fågelarter.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/fåglar/A 8475-2025 prioriterade fågelarter.docx", "A 8475-2025")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 8475-2025</t>
+          <t>A 37056-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45709</v>
+        <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>15</v>
       </c>
       <c r="U4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
@@ -913,39 +913,39 @@
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 8475-2025 artfynd.xlsx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 37056-2026 artfynd.xlsx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 8475-2025 karta.png", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 37056-2026 karta.png", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 8475-2025 georefererad karta.tif", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 37056-2026 georefererad karta.tif", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="Z4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 8475-2025 karta knärot.png", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 37056-2026 karta knärot.png", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 8475-2025 FSC-klagomål.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 37056-2026 FSC-klagomål.docx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 8475-2025 FSC-klagomål mail.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 37056-2026 FSC-klagomål mail.docx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 8475-2025 tillsynsbegäran.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 37056-2026 tillsynsbegäran.docx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 8475-2025 tillsynsbegäran mail.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 37056-2026 tillsynsbegäran mail.docx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/fåglar/A 8475-2025 prioriterade fågelarter.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/fåglar/A 37056-2026 prioriterade fågelarter.docx", "A 37056-2026")</f>
         <v/>
       </c>
     </row>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44880</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>46181</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44470</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44545</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44600</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>44620</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 41446-2023</t>
+          <t>A 40815-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2150,10 +2150,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45175</v>
+        <v>44824</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2165,13 +2165,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>8.4</v>
+        <v>15.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2214,7 +2209,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 30621-2023</t>
+          <t>A 19082-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2228,10 +2223,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45112</v>
+        <v>45048</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2243,8 +2238,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2287,7 +2287,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 30623-2023</t>
+          <t>A 55072-2021</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2301,10 +2301,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45112</v>
+        <v>44474</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2360,7 +2360,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 51096-2024</t>
+          <t>A 52795-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45603</v>
+        <v>45226</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2433,7 +2433,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 40607-2024</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45556</v>
+        <v>44491</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.2</v>
+        <v>6.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2506,7 +2506,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 19420-2024</t>
+          <t>A 55003-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45429</v>
+        <v>44886</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.8</v>
+        <v>6.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2579,7 +2579,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 60754-2024</t>
+          <t>A 10298-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45644</v>
+        <v>46076</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2652,7 +2652,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 24023-2025</t>
+          <t>A 52802-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45796</v>
+        <v>44875</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2681,8 +2681,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.5</v>
+        <v>5.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2725,7 +2730,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 11771-2025</t>
+          <t>A 6734-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2739,10 +2744,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45727</v>
+        <v>44602</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2755,7 +2760,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>32.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2798,7 +2803,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 30621-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2812,10 +2817,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44491</v>
+        <v>45112</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2828,7 +2833,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>6.8</v>
+        <v>3.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2871,7 +2876,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 1040-2025</t>
+          <t>A 30623-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2885,10 +2890,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45666</v>
+        <v>45112</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2901,7 +2906,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2944,7 +2949,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 59805-2024</t>
+          <t>A 59853-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2958,10 +2963,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45639</v>
+        <v>44908</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2974,7 +2979,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3017,7 +3022,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 10298-2026</t>
+          <t>A 3683-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3031,10 +3036,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46076</v>
+        <v>44950</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3046,8 +3051,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>6.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3090,7 +3100,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 39717-2023</t>
+          <t>A 61260-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3104,10 +3114,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45167</v>
+        <v>46000</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3120,7 +3130,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3163,7 +3173,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 38308-2023</t>
+          <t>A 23574-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3177,10 +3187,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45161</v>
+        <v>45077</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3193,7 +3203,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3236,7 +3246,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 55003-2022</t>
+          <t>A 41446-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3250,10 +3260,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44886</v>
+        <v>45175</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3265,8 +3275,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3309,7 +3324,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 47123-2024</t>
+          <t>A 33022-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3323,10 +3338,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45586</v>
+        <v>45840</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3339,7 +3354,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>5.3</v>
+        <v>1.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3382,7 +3397,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 40815-2022</t>
+          <t>A 59609-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3396,10 +3411,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44824</v>
+        <v>44491</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3412,7 +3427,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>15.9</v>
+        <v>12.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3455,7 +3470,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 33022-2025</t>
+          <t>A 30634-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3469,10 +3484,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45840</v>
+        <v>45112</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3485,7 +3500,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.5</v>
+        <v>6.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3528,7 +3543,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 61260-2025</t>
+          <t>A 26382-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3542,10 +3557,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46000</v>
+        <v>45092</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3557,8 +3572,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>4.4</v>
+        <v>20.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3601,7 +3621,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 55072-2021</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3615,10 +3635,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44474</v>
+        <v>44491</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3631,7 +3651,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.4</v>
+        <v>6.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3674,7 +3694,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 10516-2022</t>
+          <t>A 11771-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3688,10 +3708,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44623</v>
+        <v>45727</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3704,7 +3724,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3747,7 +3767,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 10517-2022</t>
+          <t>A 52809-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3761,10 +3781,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44623</v>
+        <v>44875</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3776,8 +3796,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3820,7 +3845,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 50058-2021</t>
+          <t>A 26274-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3834,10 +3859,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44456</v>
+        <v>46182</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3849,13 +3874,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>6</v>
+        <v>0.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3898,7 +3918,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 26274-2026</t>
+          <t>A 26257-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3915,7 +3935,7 @@
         <v>46182</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3928,7 +3948,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3971,7 +3991,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 26257-2026</t>
+          <t>A 27399-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3981,14 +4001,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46182</v>
+        <v>46189</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4001,7 +4021,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4044,7 +4064,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 27399-2026</t>
+          <t>A 27400-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4061,7 +4081,7 @@
         <v>46189</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4074,7 +4094,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4117,7 +4137,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 27400-2026</t>
+          <t>A 40607-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4127,14 +4147,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46189</v>
+        <v>45556</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4147,7 +4167,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4190,7 +4210,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 6734-2022</t>
+          <t>A 16735-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4204,10 +4224,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44602</v>
+        <v>45030</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4220,7 +4240,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>32.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4263,7 +4283,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 30634-2023</t>
+          <t>A 59805-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4277,10 +4297,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45112</v>
+        <v>45639</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4293,7 +4313,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>6.2</v>
+        <v>3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4336,7 +4356,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 35521-2026</t>
+          <t>A 1906-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4350,10 +4370,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46262</v>
+        <v>44575</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4365,13 +4385,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>6.2</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4414,7 +4429,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 35459-2026</t>
+          <t>A 8193-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4428,10 +4443,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46262</v>
+        <v>44974</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4443,8 +4458,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>3.5</v>
+        <v>10.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4487,7 +4507,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 52795-2023</t>
+          <t>A 8228-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4501,10 +4521,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45226</v>
+        <v>44974</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4517,7 +4537,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.7</v>
+        <v>13.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4560,7 +4580,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 37045-2026</t>
+          <t>A 51096-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4574,10 +4594,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46273</v>
+        <v>45603</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4589,13 +4609,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>7.6</v>
+        <v>1.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4638,7 +4653,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 37054-2026</t>
+          <t>A 47123-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4652,10 +4667,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46273</v>
+        <v>45586</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4667,13 +4682,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>6.3</v>
+        <v>5.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4716,7 +4726,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 37865-2026</t>
+          <t>A 39269-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4730,10 +4740,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46279</v>
+        <v>45166</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4745,13 +4755,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>9.1</v>
+        <v>3.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4794,7 +4799,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 16735-2023</t>
+          <t>A 59612-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4808,10 +4813,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45030</v>
+        <v>44491</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4824,7 +4829,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>8.699999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4867,7 +4872,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 19082-2023</t>
+          <t>A 38308-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4881,10 +4886,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45048</v>
+        <v>45161</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4896,13 +4901,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>6.5</v>
+        <v>2.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4945,7 +4945,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 26029-2022</t>
+          <t>A 19266-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4959,10 +4959,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44734</v>
+        <v>45428</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4974,13 +4974,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>9.699999999999999</v>
+        <v>3.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5023,7 +5018,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 59612-2021</t>
+          <t>A 50058-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5037,10 +5032,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44491</v>
+        <v>44456</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5052,8 +5047,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 52802-2022</t>
+          <t>A 10516-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5110,10 +5110,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44875</v>
+        <v>44623</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5125,13 +5125,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>5.8</v>
+        <v>2.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5174,7 +5169,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 10517-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5188,10 +5183,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44491</v>
+        <v>44623</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5204,7 +5199,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>6.8</v>
+        <v>1.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5247,7 +5242,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 39269-2023</t>
+          <t>A 39717-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5261,10 +5256,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45166</v>
+        <v>45167</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5277,7 +5272,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5320,7 +5315,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 59609-2021</t>
+          <t>A 26029-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5334,10 +5329,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44491</v>
+        <v>44734</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5349,8 +5344,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>12.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5393,7 +5393,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 19266-2024</t>
+          <t>A 35521-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5407,10 +5407,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45428</v>
+        <v>46262</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5422,8 +5422,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>3.8</v>
+        <v>6.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5466,7 +5471,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 52809-2022</t>
+          <t>A 35459-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5480,10 +5485,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44875</v>
+        <v>46262</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5495,13 +5500,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5544,7 +5544,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 3683-2023</t>
+          <t>A 31883-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5558,10 +5558,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44950</v>
+        <v>44777</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5573,13 +5573,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>6.3</v>
+        <v>1.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5622,7 +5617,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 1906-2022</t>
+          <t>A 37054-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5636,10 +5631,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44575</v>
+        <v>46273</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5651,8 +5646,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>6.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5695,7 +5695,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 59853-2022</t>
+          <t>A 37045-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5709,10 +5709,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44908</v>
+        <v>46273</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5724,8 +5724,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>7.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5768,7 +5773,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 8193-2023</t>
+          <t>A 37865-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5782,10 +5787,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44974</v>
+        <v>46279</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5803,7 +5808,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>10.5</v>
+        <v>9.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5846,7 +5851,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 8228-2023</t>
+          <t>A 52789-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5860,10 +5865,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44974</v>
+        <v>45610</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5876,7 +5881,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>13.9</v>
+        <v>2.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5919,7 +5924,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 31883-2022</t>
+          <t>A 24023-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5933,10 +5938,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44777</v>
+        <v>45796</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5992,7 +5997,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 23574-2023</t>
+          <t>A 19420-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6006,10 +6011,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45077</v>
+        <v>45429</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6022,7 +6027,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6065,7 +6070,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 26382-2023</t>
+          <t>A 60754-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6079,10 +6084,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45092</v>
+        <v>45644</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6094,13 +6099,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>20.3</v>
+        <v>2.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6143,7 +6143,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 52789-2024</t>
+          <t>A 1040-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6157,10 +6157,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45610</v>
+        <v>45666</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6233,7 +6233,7 @@
         <v>44628</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44880</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>46181</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44470</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44545</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44600</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>44620</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 40815-2022</t>
+          <t>A 41446-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2150,10 +2150,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44824</v>
+        <v>45175</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2165,8 +2165,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>15.9</v>
+        <v>8.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2209,7 +2214,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 19082-2023</t>
+          <t>A 30621-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2223,10 +2228,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45048</v>
+        <v>45112</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2238,13 +2243,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>6.5</v>
+        <v>3.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2287,7 +2287,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 55072-2021</t>
+          <t>A 30623-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2301,10 +2301,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44474</v>
+        <v>45112</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2360,7 +2360,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 52795-2023</t>
+          <t>A 51096-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45226</v>
+        <v>45603</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2433,7 +2433,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 40607-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44491</v>
+        <v>45556</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>6.8</v>
+        <v>3.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2506,7 +2506,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 55003-2022</t>
+          <t>A 11771-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44886</v>
+        <v>45727</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>6.6</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2579,7 +2579,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 10298-2026</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46076</v>
+        <v>44491</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.5</v>
+        <v>6.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2652,7 +2652,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 52802-2022</t>
+          <t>A 1040-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44875</v>
+        <v>45666</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2681,13 +2681,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>5.8</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2730,7 +2725,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 6734-2022</t>
+          <t>A 59805-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2744,10 +2739,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44602</v>
+        <v>45639</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2760,7 +2755,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>32.3</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2803,7 +2798,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 30621-2023</t>
+          <t>A 39717-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2817,10 +2812,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45112</v>
+        <v>45167</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2833,7 +2828,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2876,7 +2871,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 30623-2023</t>
+          <t>A 38308-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2890,10 +2885,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45112</v>
+        <v>45161</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2906,7 +2901,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2949,7 +2944,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 59853-2022</t>
+          <t>A 55003-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2963,10 +2958,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44908</v>
+        <v>44886</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2979,7 +2974,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.7</v>
+        <v>6.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3022,7 +3017,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 3683-2023</t>
+          <t>A 47123-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3036,10 +3031,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44950</v>
+        <v>45586</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3051,13 +3046,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>6.3</v>
+        <v>5.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3100,7 +3090,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 61260-2025</t>
+          <t>A 40815-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3114,10 +3104,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46000</v>
+        <v>44824</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3130,7 +3120,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4.4</v>
+        <v>15.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3173,7 +3163,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 23574-2023</t>
+          <t>A 55072-2021</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3187,10 +3177,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45077</v>
+        <v>44474</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3203,7 +3193,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3246,7 +3236,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 41446-2023</t>
+          <t>A 10298-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3260,10 +3250,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45175</v>
+        <v>46076</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3275,13 +3265,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>8.4</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3324,7 +3309,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 33022-2025</t>
+          <t>A 10516-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3338,10 +3323,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45840</v>
+        <v>44623</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3354,7 +3339,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3397,7 +3382,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 59609-2021</t>
+          <t>A 10517-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3411,10 +3396,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44491</v>
+        <v>44623</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3427,7 +3412,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>12.7</v>
+        <v>1.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3470,7 +3455,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 30634-2023</t>
+          <t>A 50058-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3484,10 +3469,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45112</v>
+        <v>44456</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3499,8 +3484,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3543,7 +3533,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 26382-2023</t>
+          <t>A 6734-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3557,10 +3547,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45092</v>
+        <v>44602</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3572,13 +3562,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>20.3</v>
+        <v>32.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3621,7 +3606,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 30634-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3635,10 +3620,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44491</v>
+        <v>45112</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3651,7 +3636,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3694,7 +3679,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 11771-2025</t>
+          <t>A 33022-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3708,10 +3693,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45727</v>
+        <v>45840</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3724,7 +3709,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3767,7 +3752,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 52809-2022</t>
+          <t>A 61260-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3781,10 +3766,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44875</v>
+        <v>46000</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3796,13 +3781,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3845,7 +3825,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 26274-2026</t>
+          <t>A 52795-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3859,10 +3839,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46182</v>
+        <v>45226</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3875,7 +3855,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3918,7 +3898,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 26257-2026</t>
+          <t>A 16735-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3932,10 +3912,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46182</v>
+        <v>45030</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3948,7 +3928,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3991,7 +3971,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 27399-2026</t>
+          <t>A 19082-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4001,14 +3981,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46189</v>
+        <v>45048</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4020,8 +4000,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>6.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4064,7 +4049,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 27400-2026</t>
+          <t>A 26029-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4074,14 +4059,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46189</v>
+        <v>44734</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4093,8 +4078,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4137,7 +4127,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 40607-2024</t>
+          <t>A 59612-2021</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4151,10 +4141,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45556</v>
+        <v>44491</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4210,7 +4200,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 16735-2023</t>
+          <t>A 52802-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4224,10 +4214,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45030</v>
+        <v>44875</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4239,8 +4229,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>8.699999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4283,7 +4278,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 59805-2024</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4297,10 +4292,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45639</v>
+        <v>44491</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4313,7 +4308,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3</v>
+        <v>6.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4356,7 +4351,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 1906-2022</t>
+          <t>A 26274-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4370,10 +4365,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44575</v>
+        <v>46182</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4386,7 +4381,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4429,7 +4424,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 8193-2023</t>
+          <t>A 26257-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4443,10 +4438,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44974</v>
+        <v>46182</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4458,13 +4453,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>10.5</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4507,7 +4497,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 8228-2023</t>
+          <t>A 39269-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4521,10 +4511,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44974</v>
+        <v>45166</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4537,7 +4527,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>13.9</v>
+        <v>3.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4580,7 +4570,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 51096-2024</t>
+          <t>A 27399-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4590,14 +4580,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45603</v>
+        <v>46189</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4610,7 +4600,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4653,7 +4643,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 47123-2024</t>
+          <t>A 27400-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4663,14 +4653,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45586</v>
+        <v>46189</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4683,7 +4673,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>5.3</v>
+        <v>3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4726,7 +4716,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 39269-2023</t>
+          <t>A 59609-2021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4740,10 +4730,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45166</v>
+        <v>44491</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4756,7 +4746,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.3</v>
+        <v>12.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4799,7 +4789,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 59612-2021</t>
+          <t>A 19266-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4813,10 +4803,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44491</v>
+        <v>45428</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4829,7 +4819,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4872,7 +4862,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 38308-2023</t>
+          <t>A 52809-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4886,10 +4876,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45161</v>
+        <v>44875</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4901,8 +4891,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4945,7 +4940,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 19266-2024</t>
+          <t>A 3683-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4959,10 +4954,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45428</v>
+        <v>44950</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4974,8 +4969,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>3.8</v>
+        <v>6.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5018,7 +5018,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 50058-2021</t>
+          <t>A 1906-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5032,10 +5032,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44456</v>
+        <v>44575</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5047,13 +5047,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5096,7 +5091,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 10516-2022</t>
+          <t>A 35521-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5110,10 +5105,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44623</v>
+        <v>46262</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5125,8 +5120,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>2.1</v>
+        <v>6.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5169,7 +5169,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 10517-2022</t>
+          <t>A 35459-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5183,10 +5183,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44623</v>
+        <v>46262</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5242,7 +5242,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 39717-2023</t>
+          <t>A 59853-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5256,10 +5256,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45167</v>
+        <v>44908</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5315,7 +5315,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 26029-2022</t>
+          <t>A 8193-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5329,10 +5329,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44734</v>
+        <v>44974</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>9.699999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5393,7 +5393,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 35521-2026</t>
+          <t>A 8228-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5407,10 +5407,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46262</v>
+        <v>44974</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5422,13 +5422,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>6.2</v>
+        <v>13.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5471,7 +5466,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 35459-2026</t>
+          <t>A 31883-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5485,10 +5480,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46262</v>
+        <v>44777</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5501,7 +5496,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5544,7 +5539,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 31883-2022</t>
+          <t>A 37045-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5558,10 +5553,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44777</v>
+        <v>46273</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5573,8 +5568,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>1.5</v>
+        <v>7.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5634,7 +5634,7 @@
         <v>46273</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 37045-2026</t>
+          <t>A 23574-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5709,10 +5709,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46273</v>
+        <v>45077</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5724,13 +5724,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>7.6</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5773,7 +5768,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 37865-2026</t>
+          <t>A 26382-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5787,10 +5782,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46279</v>
+        <v>45092</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5808,7 +5803,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>9.1</v>
+        <v>20.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5851,7 +5846,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 52789-2024</t>
+          <t>A 37865-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5865,10 +5860,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45610</v>
+        <v>46279</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5880,8 +5875,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>2.4</v>
+        <v>9.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5924,7 +5924,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 24023-2025</t>
+          <t>A 52789-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5938,10 +5938,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45796</v>
+        <v>45610</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6014,7 +6014,7 @@
         <v>45429</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>45644</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 1040-2025</t>
+          <t>A 24023-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6157,10 +6157,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45666</v>
+        <v>45796</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6233,7 +6233,7 @@
         <v>44628</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE73"/>
+  <dimension ref="A1:AE72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 53870-2022</t>
+          <t>A 25961-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44880</v>
+        <v>46181</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1430,13 +1430,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>2.3</v>
+        <v>7.3</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1448,7 +1443,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1460,10 +1455,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1472,46 +1467,50 @@
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 25961-2026</t>
+          <t>A 53870-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1525,10 +1524,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46181</v>
+        <v>44880</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1540,8 +1539,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>7.3</v>
+        <v>2.3</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1553,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1565,10 +1569,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1577,43 +1581,39 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
-        <v/>
-      </c>
-      <c r="Z10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44470</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44545</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44600</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>44620</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 41446-2023</t>
+          <t>A 19082-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2150,10 +2150,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45175</v>
+        <v>45048</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>8.4</v>
+        <v>6.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2214,7 +2214,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 30621-2023</t>
+          <t>A 40815-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45112</v>
+        <v>44824</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.2</v>
+        <v>15.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2287,7 +2287,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 30623-2023</t>
+          <t>A 55072-2021</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2301,10 +2301,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45112</v>
+        <v>44474</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2360,7 +2360,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 51096-2024</t>
+          <t>A 52795-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45603</v>
+        <v>45226</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2433,7 +2433,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 40607-2024</t>
+          <t>A 6734-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45556</v>
+        <v>44602</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.2</v>
+        <v>32.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2506,7 +2506,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 11771-2025</t>
+          <t>A 52802-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45727</v>
+        <v>44875</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2535,8 +2535,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>0.9</v>
+        <v>5.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2579,7 +2584,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 30621-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2593,10 +2598,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44491</v>
+        <v>45112</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2609,7 +2614,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>6.8</v>
+        <v>3.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2652,7 +2657,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 1040-2025</t>
+          <t>A 30623-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2666,10 +2671,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45666</v>
+        <v>45112</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2682,7 +2687,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2725,7 +2730,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 59805-2024</t>
+          <t>A 59853-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2739,10 +2744,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45639</v>
+        <v>44908</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2755,7 +2760,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2798,7 +2803,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 39717-2023</t>
+          <t>A 1040-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2812,10 +2817,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45167</v>
+        <v>45666</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2828,7 +2833,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2871,7 +2876,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 38308-2023</t>
+          <t>A 3683-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2885,10 +2890,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45161</v>
+        <v>44950</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2900,8 +2905,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>2.9</v>
+        <v>6.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2944,7 +2954,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 55003-2022</t>
+          <t>A 10298-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2958,10 +2968,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44886</v>
+        <v>46076</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2974,7 +2984,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>6.6</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3017,7 +3027,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 47123-2024</t>
+          <t>A 23574-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3031,10 +3041,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45586</v>
+        <v>45077</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3047,7 +3057,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>5.3</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3090,7 +3100,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 40815-2022</t>
+          <t>A 41446-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3104,10 +3114,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44824</v>
+        <v>45175</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3119,8 +3129,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>15.9</v>
+        <v>8.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3163,7 +3178,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 55072-2021</t>
+          <t>A 30634-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3177,10 +3192,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44474</v>
+        <v>45112</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3193,7 +3208,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.4</v>
+        <v>6.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3236,7 +3251,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 10298-2026</t>
+          <t>A 26382-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3250,10 +3265,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46076</v>
+        <v>45092</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3265,8 +3280,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>20.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3309,7 +3329,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 10516-2022</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3323,10 +3343,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44623</v>
+        <v>44491</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3339,7 +3359,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.1</v>
+        <v>6.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3382,7 +3402,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10517-2022</t>
+          <t>A 61260-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3396,10 +3416,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44623</v>
+        <v>46000</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3412,7 +3432,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3455,7 +3475,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 50058-2021</t>
+          <t>A 33022-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3469,10 +3489,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44456</v>
+        <v>45840</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3484,13 +3504,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3533,7 +3548,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 6734-2022</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3547,10 +3562,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44602</v>
+        <v>44491</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3563,7 +3578,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>32.3</v>
+        <v>6.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3606,7 +3621,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 30634-2023</t>
+          <t>A 11771-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3620,10 +3635,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45112</v>
+        <v>45727</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3636,7 +3651,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6.2</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3679,7 +3694,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 33022-2025</t>
+          <t>A 52809-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3693,10 +3708,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45840</v>
+        <v>44875</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3708,8 +3723,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3752,7 +3772,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 61260-2025</t>
+          <t>A 16735-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3766,10 +3786,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46000</v>
+        <v>45030</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3782,7 +3802,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3825,7 +3845,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 52795-2023</t>
+          <t>A 1906-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3839,10 +3859,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45226</v>
+        <v>44575</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3855,7 +3875,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3898,7 +3918,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 16735-2023</t>
+          <t>A 39269-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3912,10 +3932,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45030</v>
+        <v>45166</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3928,7 +3948,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>8.699999999999999</v>
+        <v>3.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3971,7 +3991,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 19082-2023</t>
+          <t>A 26274-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3985,10 +4005,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45048</v>
+        <v>46182</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4000,13 +4020,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>6.5</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4049,7 +4064,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 26029-2022</t>
+          <t>A 59612-2021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4063,10 +4078,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44734</v>
+        <v>44491</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4078,13 +4093,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>9.699999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4127,7 +4137,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 59612-2021</t>
+          <t>A 26257-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4141,10 +4151,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44491</v>
+        <v>46182</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4157,7 +4167,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4200,7 +4210,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 52802-2022</t>
+          <t>A 27399-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4210,14 +4220,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44875</v>
+        <v>46189</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4229,13 +4239,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>5.8</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4278,7 +4283,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 27400-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4288,14 +4293,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44491</v>
+        <v>46189</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4308,7 +4313,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>6.8</v>
+        <v>3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4351,7 +4356,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 26274-2026</t>
+          <t>A 19266-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4365,10 +4370,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46182</v>
+        <v>45428</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4381,7 +4386,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4424,7 +4429,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 26257-2026</t>
+          <t>A 10516-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4438,10 +4443,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46182</v>
+        <v>44623</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4454,7 +4459,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4497,7 +4502,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 39269-2023</t>
+          <t>A 10517-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4511,10 +4516,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45166</v>
+        <v>44623</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4527,7 +4532,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4570,7 +4575,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 27399-2026</t>
+          <t>A 39717-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4580,14 +4585,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46189</v>
+        <v>45167</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4600,7 +4605,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4643,7 +4648,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 27400-2026</t>
+          <t>A 35521-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4653,14 +4658,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46189</v>
+        <v>46262</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4672,8 +4677,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>3</v>
+        <v>6.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4716,7 +4726,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 59609-2021</t>
+          <t>A 35459-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4730,10 +4740,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44491</v>
+        <v>46262</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4746,7 +4756,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>12.7</v>
+        <v>3.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4789,7 +4799,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 19266-2024</t>
+          <t>A 55003-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4803,10 +4813,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45428</v>
+        <v>44886</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4819,7 +4829,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.8</v>
+        <v>6.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4862,7 +4872,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 52809-2022</t>
+          <t>A 37054-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4876,10 +4886,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44875</v>
+        <v>46273</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4897,7 +4907,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.5</v>
+        <v>6.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4940,7 +4950,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 3683-2023</t>
+          <t>A 37045-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4954,10 +4964,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44950</v>
+        <v>46273</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4975,7 +4985,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>6.3</v>
+        <v>7.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5018,7 +5028,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 1906-2022</t>
+          <t>A 59609-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5032,10 +5042,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44575</v>
+        <v>44491</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5048,7 +5058,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>12.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5091,7 +5101,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 35521-2026</t>
+          <t>A 37865-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5105,10 +5115,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46262</v>
+        <v>46279</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5126,7 +5136,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>6.2</v>
+        <v>9.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5169,7 +5179,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 35459-2026</t>
+          <t>A 40607-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5183,10 +5193,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46262</v>
+        <v>45556</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5199,7 +5209,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5242,7 +5252,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 59853-2022</t>
+          <t>A 59805-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5256,10 +5266,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44908</v>
+        <v>45639</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5272,7 +5282,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5332,7 +5342,7 @@
         <v>44974</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5410,7 +5420,7 @@
         <v>44974</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5466,7 +5476,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 31883-2022</t>
+          <t>A 51096-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5480,10 +5490,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44777</v>
+        <v>45603</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5496,7 +5506,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5539,7 +5549,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 37045-2026</t>
+          <t>A 47123-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5553,10 +5563,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46273</v>
+        <v>45586</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5568,13 +5578,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5617,7 +5622,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 37054-2026</t>
+          <t>A 38308-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5631,10 +5636,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46273</v>
+        <v>45161</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5646,13 +5651,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>6.3</v>
+        <v>2.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5695,7 +5695,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 23574-2023</t>
+          <t>A 26029-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5709,10 +5709,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45077</v>
+        <v>44734</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5724,8 +5724,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5768,7 +5773,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 26382-2023</t>
+          <t>A 31883-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5782,10 +5787,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45092</v>
+        <v>44777</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5797,13 +5802,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>20.3</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5846,7 +5846,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 37865-2026</t>
+          <t>A 52789-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5860,10 +5860,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46279</v>
+        <v>45610</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5875,13 +5875,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>9.1</v>
+        <v>2.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5924,7 +5919,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 52789-2024</t>
+          <t>A 24023-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5938,10 +5933,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45610</v>
+        <v>45796</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5954,7 +5949,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6014,7 +6009,7 @@
         <v>45429</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6087,7 +6082,7 @@
         <v>45644</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6140,27 +6135,27 @@
       </c>
       <c r="V71" s="2" t="inlineStr"/>
     </row>
-    <row r="72" ht="15" customHeight="1">
+    <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 24023-2025</t>
+          <t>S 1310-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45796</v>
+        <v>44628</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6173,7 +6168,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.5</v>
+        <v>36.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6212,79 +6207,6 @@
         <v>0</v>
       </c>
       <c r="V72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>S 1310-2022</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Skogsgödsling</t>
-        </is>
-      </c>
-      <c r="D73" s="1" t="n">
-        <v>44628</v>
-      </c>
-      <c r="E73" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>KUNGSÖR</t>
-        </is>
-      </c>
-      <c r="I73" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" t="n">
-        <v>0</v>
-      </c>
-      <c r="P73" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
-      <c r="R73" t="n">
-        <v>0</v>
-      </c>
-      <c r="S73" t="n">
-        <v>0</v>
-      </c>
-      <c r="T73" t="n">
-        <v>0</v>
-      </c>
-      <c r="U73" t="n">
-        <v>0</v>
-      </c>
-      <c r="V73" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25961-2026</t>
+          <t>A 53870-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46181</v>
+        <v>44880</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1430,8 +1430,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>7.3</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1443,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1455,10 +1460,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1467,50 +1472,46 @@
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
-        <v/>
-      </c>
-      <c r="Z9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 53870-2022</t>
+          <t>A 25961-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1524,10 +1525,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44880</v>
+        <v>46181</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1539,13 +1540,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>2.3</v>
+        <v>7.3</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1557,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1569,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1581,39 +1577,43 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
+        <v/>
+      </c>
+      <c r="Z10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44470</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44545</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44600</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>44620</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 19082-2023</t>
+          <t>A 41446-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2150,10 +2150,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45048</v>
+        <v>45175</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>6.5</v>
+        <v>8.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2214,7 +2214,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 40815-2022</t>
+          <t>A 30621-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44824</v>
+        <v>45112</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>15.9</v>
+        <v>3.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2287,7 +2287,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 55072-2021</t>
+          <t>A 30623-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2301,10 +2301,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44474</v>
+        <v>45112</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2360,7 +2360,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 52795-2023</t>
+          <t>A 51096-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45226</v>
+        <v>45603</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2433,7 +2433,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 6734-2022</t>
+          <t>A 11771-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44602</v>
+        <v>45727</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>32.3</v>
+        <v>0.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2506,7 +2506,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 52802-2022</t>
+          <t>A 40607-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44875</v>
+        <v>45556</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2535,13 +2535,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>5.8</v>
+        <v>3.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2584,7 +2579,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 30621-2023</t>
+          <t>A 59805-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2598,10 +2593,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45112</v>
+        <v>45639</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2614,7 +2609,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2657,7 +2652,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 30623-2023</t>
+          <t>A 55003-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2671,10 +2666,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45112</v>
+        <v>44886</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2687,7 +2682,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.6</v>
+        <v>6.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2730,7 +2725,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 59853-2022</t>
+          <t>A 39717-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2744,10 +2739,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44908</v>
+        <v>45167</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2760,7 +2755,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2803,7 +2798,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 1040-2025</t>
+          <t>A 38308-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2817,10 +2812,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45666</v>
+        <v>45161</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2833,7 +2828,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2876,7 +2871,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 3683-2023</t>
+          <t>A 47123-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2890,10 +2885,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44950</v>
+        <v>45586</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2905,13 +2900,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>6.3</v>
+        <v>5.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2954,7 +2944,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 10298-2026</t>
+          <t>A 40815-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2968,10 +2958,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46076</v>
+        <v>44824</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2984,7 +2974,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>15.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3027,7 +3017,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 23574-2023</t>
+          <t>A 33022-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3041,10 +3031,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45077</v>
+        <v>45840</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3057,7 +3047,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3100,7 +3090,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 41446-2023</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3114,10 +3104,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45175</v>
+        <v>44491</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3129,13 +3119,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3178,7 +3163,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 30634-2023</t>
+          <t>A 61260-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3192,10 +3177,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45112</v>
+        <v>46000</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3208,7 +3193,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3251,7 +3236,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 26382-2023</t>
+          <t>A 55072-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3265,10 +3250,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45092</v>
+        <v>44474</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3280,13 +3265,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>20.3</v>
+        <v>3.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3329,7 +3309,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 10516-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3343,10 +3323,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44491</v>
+        <v>44623</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3359,7 +3339,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>6.8</v>
+        <v>2.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3402,7 +3382,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 61260-2025</t>
+          <t>A 10517-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3416,10 +3396,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46000</v>
+        <v>44623</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3432,7 +3412,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.4</v>
+        <v>1.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3475,7 +3455,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 33022-2025</t>
+          <t>A 6734-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3489,10 +3469,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45840</v>
+        <v>44602</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3505,7 +3485,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.5</v>
+        <v>32.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3548,7 +3528,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 30634-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3562,10 +3542,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44491</v>
+        <v>45112</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3578,7 +3558,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3621,7 +3601,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 11771-2025</t>
+          <t>A 52795-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3635,10 +3615,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45727</v>
+        <v>45226</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3651,7 +3631,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3694,7 +3674,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 52809-2022</t>
+          <t>A 16735-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3708,10 +3688,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44875</v>
+        <v>45030</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3723,13 +3703,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>2.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3772,7 +3747,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 16735-2023</t>
+          <t>A 19082-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3786,10 +3761,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45030</v>
+        <v>45048</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3801,8 +3776,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>8.699999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3845,7 +3825,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 1906-2022</t>
+          <t>A 26029-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3859,10 +3839,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44575</v>
+        <v>44734</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3874,8 +3854,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3918,7 +3903,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 39269-2023</t>
+          <t>A 59612-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3932,10 +3917,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45166</v>
+        <v>44491</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3948,7 +3933,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3991,7 +3976,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 26274-2026</t>
+          <t>A 52802-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4005,10 +3990,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46182</v>
+        <v>44875</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4020,8 +4005,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>5.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4064,7 +4054,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 59612-2021</t>
+          <t>A 26274-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4078,10 +4068,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44491</v>
+        <v>46182</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4094,7 +4084,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4154,7 +4144,7 @@
         <v>46182</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4210,7 +4200,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 27399-2026</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4220,14 +4210,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46189</v>
+        <v>44491</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4240,7 +4230,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>6.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4283,7 +4273,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 27400-2026</t>
+          <t>A 10298-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4293,14 +4283,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46189</v>
+        <v>46076</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4313,7 +4303,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4356,7 +4346,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 19266-2024</t>
+          <t>A 39269-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4370,10 +4360,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45428</v>
+        <v>45166</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4386,7 +4376,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4429,7 +4419,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 10516-2022</t>
+          <t>A 27399-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4439,14 +4429,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44623</v>
+        <v>46189</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4459,7 +4449,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4502,7 +4492,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 10517-2022</t>
+          <t>A 27400-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4512,14 +4502,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44623</v>
+        <v>46189</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4532,7 +4522,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4575,7 +4565,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 39717-2023</t>
+          <t>A 59609-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4589,10 +4579,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45167</v>
+        <v>44491</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4605,7 +4595,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.3</v>
+        <v>12.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4648,7 +4638,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 35521-2026</t>
+          <t>A 19266-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4662,10 +4652,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46262</v>
+        <v>45428</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4677,13 +4667,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>6.2</v>
+        <v>3.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4726,7 +4711,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 35459-2026</t>
+          <t>A 52809-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4740,10 +4725,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46262</v>
+        <v>44875</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4755,8 +4740,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4799,7 +4789,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 55003-2022</t>
+          <t>A 3683-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4813,10 +4803,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44886</v>
+        <v>44950</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4828,8 +4818,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4872,7 +4867,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 37054-2026</t>
+          <t>A 1906-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4886,10 +4881,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46273</v>
+        <v>44575</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4901,13 +4896,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>6.3</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4950,7 +4940,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 37045-2026</t>
+          <t>A 59853-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4964,10 +4954,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46273</v>
+        <v>44908</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4979,13 +4969,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>7.6</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5028,7 +5013,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 59609-2021</t>
+          <t>A 8193-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5042,10 +5027,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44491</v>
+        <v>44974</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5057,8 +5042,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>12.7</v>
+        <v>10.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5101,7 +5091,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 37865-2026</t>
+          <t>A 8228-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5115,10 +5105,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46279</v>
+        <v>44974</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5130,13 +5120,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>9.1</v>
+        <v>13.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5179,7 +5164,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 40607-2024</t>
+          <t>A 31883-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5193,10 +5178,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45556</v>
+        <v>44777</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5209,7 +5194,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5252,7 +5237,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 59805-2024</t>
+          <t>A 35521-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5266,10 +5251,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45639</v>
+        <v>46262</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5281,8 +5266,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>3</v>
+        <v>6.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5325,7 +5315,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 8193-2023</t>
+          <t>A 35459-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5339,10 +5329,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44974</v>
+        <v>46262</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5354,13 +5344,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>10.5</v>
+        <v>3.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5403,7 +5388,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 8228-2023</t>
+          <t>A 23574-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5417,10 +5402,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44974</v>
+        <v>45077</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5433,7 +5418,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>13.9</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5476,7 +5461,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 51096-2024</t>
+          <t>A 26382-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5490,10 +5475,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45603</v>
+        <v>45092</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5505,8 +5490,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>20.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5549,7 +5539,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 47123-2024</t>
+          <t>A 37045-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5563,10 +5553,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45586</v>
+        <v>46273</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5578,8 +5568,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5622,7 +5617,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 38308-2023</t>
+          <t>A 37054-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5636,10 +5631,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45161</v>
+        <v>46273</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5651,8 +5646,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>2.9</v>
+        <v>6.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5695,7 +5695,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 26029-2022</t>
+          <t>A 37865-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5709,10 +5709,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44734</v>
+        <v>46279</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>9.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5773,7 +5773,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 31883-2022</t>
+          <t>A 52789-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44777</v>
+        <v>45610</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5846,7 +5846,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 52789-2024</t>
+          <t>A 19420-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5860,10 +5860,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45610</v>
+        <v>45429</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5919,7 +5919,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 24023-2025</t>
+          <t>A 60754-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5933,10 +5933,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45796</v>
+        <v>45644</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5992,7 +5992,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 19420-2024</t>
+          <t>A 24023-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6006,10 +6006,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45429</v>
+        <v>45796</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6065,7 +6065,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 60754-2024</t>
+          <t>A 1040-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6079,10 +6079,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45644</v>
+        <v>45666</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6155,7 +6155,7 @@
         <v>44628</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44880</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>46181</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44470</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44545</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44600</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>44620</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>45175</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>45112</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>45112</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>45603</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>45727</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>45556</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>45639</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         <v>44886</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>45167</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>45161</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>45586</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>44824</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>45840</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         <v>44491</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>46000</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>44474</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>44623</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>44623</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>44602</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>45112</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>45226</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>45030</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>45048</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>44734</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>44491</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>44875</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>46182</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>46182</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>44491</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>46076</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>45166</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>46189</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>46189</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>44491</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>45428</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>44875</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>44950</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>44575</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>44908</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>44974</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>44974</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         <v>44777</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>46262</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>46262</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>45077</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         <v>45092</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>46273</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>46273</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>46279</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>45610</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>45429</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>45644</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>45796</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>45666</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         <v>44628</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44880</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>46181</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44470</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44545</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44600</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>44620</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>45175</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>45112</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>45112</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>45603</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 11771-2025</t>
+          <t>A 40607-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45727</v>
+        <v>45556</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2506,7 +2506,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 40607-2024</t>
+          <t>A 11771-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45556</v>
+        <v>45727</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2596,7 +2596,7 @@
         <v>45639</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 55003-2022</t>
+          <t>A 39717-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44886</v>
+        <v>45167</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>6.6</v>
+        <v>2.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2725,7 +2725,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 39717-2023</t>
+          <t>A 38308-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45167</v>
+        <v>45161</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2798,7 +2798,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 38308-2023</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2812,10 +2812,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45161</v>
+        <v>44491</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.9</v>
+        <v>6.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2871,7 +2871,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 47123-2024</t>
+          <t>A 55003-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2885,10 +2885,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45586</v>
+        <v>44886</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2944,7 +2944,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 40815-2022</t>
+          <t>A 47123-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2958,10 +2958,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44824</v>
+        <v>45586</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>15.9</v>
+        <v>5.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3034,7 +3034,7 @@
         <v>45840</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 40815-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3104,10 +3104,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44491</v>
+        <v>44824</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>6.8</v>
+        <v>15.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3180,7 +3180,7 @@
         <v>46000</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>44474</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>44623</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>44623</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>44602</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>45112</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>45226</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 16735-2023</t>
+          <t>A 26274-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45030</v>
+        <v>46182</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>8.699999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3747,7 +3747,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 19082-2023</t>
+          <t>A 26257-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45048</v>
+        <v>46182</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3776,13 +3776,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>6.5</v>
+        <v>1.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3825,7 +3820,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 26029-2022</t>
+          <t>A 27399-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3835,14 +3830,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44734</v>
+        <v>46189</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3854,13 +3849,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>9.699999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3903,7 +3893,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 59612-2021</t>
+          <t>A 27400-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3913,14 +3903,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44491</v>
+        <v>46189</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3933,7 +3923,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3976,7 +3966,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 52802-2022</t>
+          <t>A 16735-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3990,10 +3980,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44875</v>
+        <v>45030</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4005,13 +3995,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>5.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4054,7 +4039,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 26274-2026</t>
+          <t>A 19082-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4068,10 +4053,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46182</v>
+        <v>45048</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4083,8 +4068,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>6.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4127,7 +4117,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 26257-2026</t>
+          <t>A 10298-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4141,10 +4131,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46182</v>
+        <v>46076</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4157,7 +4147,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4200,7 +4190,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 26029-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4214,10 +4204,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44491</v>
+        <v>44734</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4229,8 +4219,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>6.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4273,7 +4268,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 10298-2026</t>
+          <t>A 59612-2021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4287,10 +4282,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46076</v>
+        <v>44491</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4303,7 +4298,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4346,7 +4341,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 39269-2023</t>
+          <t>A 52802-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4360,10 +4355,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45166</v>
+        <v>44875</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4375,8 +4370,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>3.3</v>
+        <v>5.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4419,7 +4419,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 27399-2026</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4429,14 +4429,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46189</v>
+        <v>44491</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>6.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4492,7 +4492,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 27400-2026</t>
+          <t>A 39269-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4502,14 +4502,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46189</v>
+        <v>45166</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4565,7 +4565,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 59609-2021</t>
+          <t>A 35521-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4579,10 +4579,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44491</v>
+        <v>46262</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4594,8 +4594,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>12.7</v>
+        <v>6.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4638,7 +4643,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 19266-2024</t>
+          <t>A 35459-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4652,10 +4657,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45428</v>
+        <v>46262</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4668,7 +4673,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4711,7 +4716,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 52809-2022</t>
+          <t>A 59609-2021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4725,10 +4730,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44875</v>
+        <v>44491</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4740,13 +4745,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>2.5</v>
+        <v>12.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4789,7 +4789,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 3683-2023</t>
+          <t>A 19266-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4803,10 +4803,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44950</v>
+        <v>45428</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4818,13 +4818,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>6.3</v>
+        <v>3.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4867,7 +4862,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 1906-2022</t>
+          <t>A 37045-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4881,10 +4876,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44575</v>
+        <v>46273</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4896,8 +4891,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>7.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4940,7 +4940,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 59853-2022</t>
+          <t>A 37054-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4954,10 +4954,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44908</v>
+        <v>46273</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4969,8 +4969,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>6.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5013,7 +5018,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 8193-2023</t>
+          <t>A 52809-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5027,10 +5032,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44974</v>
+        <v>44875</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5048,7 +5053,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>10.5</v>
+        <v>2.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5091,7 +5096,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 8228-2023</t>
+          <t>A 3683-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5105,10 +5110,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44974</v>
+        <v>44950</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5120,8 +5125,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>13.9</v>
+        <v>6.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5164,7 +5174,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 31883-2022</t>
+          <t>A 1906-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5178,10 +5188,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44777</v>
+        <v>44575</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5194,7 +5204,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5237,7 +5247,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 35521-2026</t>
+          <t>A 37865-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5251,10 +5261,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46262</v>
+        <v>46279</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5272,7 +5282,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>6.2</v>
+        <v>9.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5315,7 +5325,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 35459-2026</t>
+          <t>A 59853-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5329,10 +5339,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46262</v>
+        <v>44908</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5345,7 +5355,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5388,7 +5398,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 23574-2023</t>
+          <t>A 8193-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5402,10 +5412,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45077</v>
+        <v>44974</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5417,8 +5427,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>10.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5461,7 +5476,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 26382-2023</t>
+          <t>A 8228-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5475,10 +5490,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45092</v>
+        <v>44974</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5490,13 +5505,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>20.3</v>
+        <v>13.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5539,7 +5549,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 37045-2026</t>
+          <t>A 31883-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5553,10 +5563,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46273</v>
+        <v>44777</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5568,13 +5578,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>7.6</v>
+        <v>1.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5617,7 +5622,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 37054-2026</t>
+          <t>A 23574-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5631,10 +5636,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46273</v>
+        <v>45077</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5646,13 +5651,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>6.3</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5695,7 +5695,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 37865-2026</t>
+          <t>A 26382-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5709,10 +5709,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46279</v>
+        <v>45092</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>9.1</v>
+        <v>20.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5790,7 +5790,7 @@
         <v>45610</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>45429</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>45644</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>45796</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>45666</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         <v>44628</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44880</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>46181</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44470</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44545</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44600</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>44620</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 41446-2023</t>
+          <t>A 19082-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2150,10 +2150,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45175</v>
+        <v>45048</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>8.4</v>
+        <v>6.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2214,7 +2214,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 30621-2023</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45112</v>
+        <v>44491</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.2</v>
+        <v>6.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2287,7 +2287,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 30623-2023</t>
+          <t>A 40815-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2301,10 +2301,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45112</v>
+        <v>44824</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.6</v>
+        <v>15.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2360,7 +2360,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 51096-2024</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45603</v>
+        <v>44491</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.3</v>
+        <v>6.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2433,7 +2433,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 40607-2024</t>
+          <t>A 24023-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45556</v>
+        <v>45796</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2506,7 +2506,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 11771-2025</t>
+          <t>A 19420-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45727</v>
+        <v>45429</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2579,7 +2579,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 59805-2024</t>
+          <t>A 60754-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45639</v>
+        <v>45644</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2652,7 +2652,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 39717-2023</t>
+          <t>A 55072-2021</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45167</v>
+        <v>44474</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2725,7 +2725,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 38308-2023</t>
+          <t>A 11771-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45161</v>
+        <v>45727</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2798,7 +2798,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 52795-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2812,10 +2812,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44491</v>
+        <v>45226</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>6.8</v>
+        <v>3.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2871,7 +2871,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 55003-2022</t>
+          <t>A 52809-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2885,10 +2885,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44886</v>
+        <v>44875</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2900,8 +2900,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>6.6</v>
+        <v>2.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2944,7 +2949,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 47123-2024</t>
+          <t>A 16735-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2958,10 +2963,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45586</v>
+        <v>45030</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2974,7 +2979,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>5.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3017,7 +3022,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33022-2025</t>
+          <t>A 52802-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3031,10 +3036,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45840</v>
+        <v>44875</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3046,8 +3051,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>5.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3090,7 +3100,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 40815-2022</t>
+          <t>A 6734-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3104,10 +3114,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44824</v>
+        <v>44602</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3120,7 +3130,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>15.9</v>
+        <v>32.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3163,7 +3173,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 61260-2025</t>
+          <t>A 1906-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3177,10 +3187,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46000</v>
+        <v>44575</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3193,7 +3203,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3236,7 +3246,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 55072-2021</t>
+          <t>A 30621-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3250,10 +3260,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44474</v>
+        <v>45112</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3266,7 +3276,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3309,7 +3319,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 10516-2022</t>
+          <t>A 30623-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3323,10 +3333,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44623</v>
+        <v>45112</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3339,7 +3349,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3382,7 +3392,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10517-2022</t>
+          <t>A 59853-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3396,10 +3406,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44623</v>
+        <v>44908</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3412,7 +3422,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3455,7 +3465,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 6734-2022</t>
+          <t>A 39269-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3469,10 +3479,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44602</v>
+        <v>45166</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3485,7 +3495,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>32.3</v>
+        <v>3.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3528,7 +3538,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 30634-2023</t>
+          <t>A 59612-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3542,10 +3552,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45112</v>
+        <v>44491</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3558,7 +3568,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>6.2</v>
+        <v>3.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3601,7 +3611,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 52795-2023</t>
+          <t>A 3683-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3615,10 +3625,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45226</v>
+        <v>44950</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3630,8 +3640,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>3.7</v>
+        <v>6.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3674,7 +3689,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 26274-2026</t>
+          <t>A 19266-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3688,10 +3703,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46182</v>
+        <v>45428</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3704,7 +3719,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3747,7 +3762,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 26257-2026</t>
+          <t>A 23574-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3761,10 +3776,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46182</v>
+        <v>45077</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3777,7 +3792,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3820,7 +3835,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 27399-2026</t>
+          <t>A 10516-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3830,14 +3845,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46189</v>
+        <v>44623</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3850,7 +3865,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3893,7 +3908,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 27400-2026</t>
+          <t>A 10517-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3903,14 +3918,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46189</v>
+        <v>44623</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3923,7 +3938,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3966,7 +3981,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 16735-2023</t>
+          <t>A 39717-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3980,10 +3995,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45030</v>
+        <v>45167</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3996,7 +4011,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>8.699999999999999</v>
+        <v>2.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4039,7 +4054,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 19082-2023</t>
+          <t>A 41446-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4053,10 +4068,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45048</v>
+        <v>45175</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4074,7 +4089,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>6.5</v>
+        <v>8.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4117,7 +4132,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 10298-2026</t>
+          <t>A 1040-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4131,10 +4146,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46076</v>
+        <v>45666</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4147,7 +4162,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4190,7 +4205,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 26029-2022</t>
+          <t>A 30634-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4204,10 +4219,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44734</v>
+        <v>45112</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4219,13 +4234,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>9.699999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4268,7 +4278,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 59612-2021</t>
+          <t>A 26382-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4282,10 +4292,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44491</v>
+        <v>45092</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4297,8 +4307,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>3.2</v>
+        <v>20.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4341,7 +4356,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 52802-2022</t>
+          <t>A 55003-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4355,10 +4370,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44875</v>
+        <v>44886</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4370,13 +4385,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4419,7 +4429,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 59609-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4436,7 +4446,7 @@
         <v>44491</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4449,7 +4459,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>6.8</v>
+        <v>12.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4492,7 +4502,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 39269-2023</t>
+          <t>A 10298-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4506,10 +4516,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45166</v>
+        <v>46076</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4522,7 +4532,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4565,7 +4575,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 35521-2026</t>
+          <t>A 40607-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4579,10 +4589,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46262</v>
+        <v>45556</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4594,13 +4604,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>6.2</v>
+        <v>3.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4643,7 +4648,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 35459-2026</t>
+          <t>A 59805-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4657,10 +4662,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46262</v>
+        <v>45639</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4673,7 +4678,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4716,7 +4721,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 59609-2021</t>
+          <t>A 8193-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4730,10 +4735,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44491</v>
+        <v>44974</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4745,8 +4750,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>12.7</v>
+        <v>10.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4789,7 +4799,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 19266-2024</t>
+          <t>A 8228-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4803,10 +4813,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45428</v>
+        <v>44974</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4819,7 +4829,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.8</v>
+        <v>13.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4862,7 +4872,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 37045-2026</t>
+          <t>A 51096-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4876,10 +4886,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46273</v>
+        <v>45603</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4891,13 +4901,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>7.6</v>
+        <v>1.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4940,7 +4945,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 37054-2026</t>
+          <t>A 47123-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4954,10 +4959,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46273</v>
+        <v>45586</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4969,13 +4974,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>6.3</v>
+        <v>5.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5018,7 +5018,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 52809-2022</t>
+          <t>A 38308-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5032,10 +5032,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44875</v>
+        <v>45161</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5047,13 +5047,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5096,7 +5091,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 3683-2023</t>
+          <t>A 61260-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5110,10 +5105,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44950</v>
+        <v>46000</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5125,13 +5120,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>6.3</v>
+        <v>4.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5174,7 +5164,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 1906-2022</t>
+          <t>A 26029-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5188,10 +5178,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44575</v>
+        <v>44734</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5203,8 +5193,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5247,7 +5242,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 37865-2026</t>
+          <t>A 33022-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5261,10 +5256,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46279</v>
+        <v>45840</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5276,13 +5271,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>9.1</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5325,7 +5315,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 59853-2022</t>
+          <t>A 31883-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5339,10 +5329,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44908</v>
+        <v>44777</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5355,7 +5345,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5398,7 +5388,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 8193-2023</t>
+          <t>A 52789-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5412,10 +5402,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44974</v>
+        <v>45610</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5427,13 +5417,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>10.5</v>
+        <v>2.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5476,7 +5461,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 8228-2023</t>
+          <t>A 26274-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5490,10 +5475,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44974</v>
+        <v>46182</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5506,7 +5491,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>13.9</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5549,7 +5534,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 31883-2022</t>
+          <t>A 26257-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5563,10 +5548,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44777</v>
+        <v>46182</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5579,7 +5564,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5622,7 +5607,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 23574-2023</t>
+          <t>A 27399-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5632,14 +5617,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45077</v>
+        <v>46189</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5652,7 +5637,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5695,7 +5680,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 26382-2023</t>
+          <t>A 27400-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5705,14 +5690,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45092</v>
+        <v>46189</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5724,13 +5709,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>20.3</v>
+        <v>3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5773,7 +5753,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 52789-2024</t>
+          <t>A 35521-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5787,10 +5767,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45610</v>
+        <v>46262</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5802,8 +5782,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>2.4</v>
+        <v>6.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5846,7 +5831,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 19420-2024</t>
+          <t>A 35459-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5860,10 +5845,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45429</v>
+        <v>46262</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5876,7 +5861,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5919,7 +5904,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 60754-2024</t>
+          <t>A 37054-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5933,10 +5918,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45644</v>
+        <v>46273</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5948,8 +5933,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>2.4</v>
+        <v>6.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5992,7 +5982,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 24023-2025</t>
+          <t>A 37045-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6006,10 +5996,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45796</v>
+        <v>46273</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6021,8 +6011,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1.5</v>
+        <v>7.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6065,7 +6060,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 1040-2025</t>
+          <t>A 37865-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6079,10 +6074,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45666</v>
+        <v>46279</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6094,8 +6089,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>1.6</v>
+        <v>9.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6155,7 +6155,7 @@
         <v>44628</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44880</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>46181</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44470</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44545</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44600</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>44620</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 19082-2023</t>
+          <t>A 41446-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2150,10 +2150,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45048</v>
+        <v>45175</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>6.5</v>
+        <v>8.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2214,7 +2214,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 30621-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44491</v>
+        <v>45112</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>6.8</v>
+        <v>3.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2287,7 +2287,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 40815-2022</t>
+          <t>A 30623-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2301,10 +2301,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44824</v>
+        <v>45112</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>15.9</v>
+        <v>2.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2360,7 +2360,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 51096-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44491</v>
+        <v>45603</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>6.8</v>
+        <v>1.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2433,7 +2433,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 24023-2025</t>
+          <t>A 40607-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45796</v>
+        <v>45556</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2506,7 +2506,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 19420-2024</t>
+          <t>A 11771-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45429</v>
+        <v>45727</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2579,7 +2579,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 60754-2024</t>
+          <t>A 59805-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45644</v>
+        <v>45639</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2652,7 +2652,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 55072-2021</t>
+          <t>A 39717-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44474</v>
+        <v>45167</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2725,7 +2725,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 11771-2025</t>
+          <t>A 38308-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45727</v>
+        <v>45161</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2798,7 +2798,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 52795-2023</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2812,10 +2812,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45226</v>
+        <v>44491</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.7</v>
+        <v>6.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2871,7 +2871,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 52809-2022</t>
+          <t>A 55003-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2885,10 +2885,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44875</v>
+        <v>44886</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2900,13 +2900,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>2.5</v>
+        <v>6.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2949,7 +2944,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 16735-2023</t>
+          <t>A 47123-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2963,10 +2958,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45030</v>
+        <v>45586</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2979,7 +2974,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>8.699999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3022,7 +3017,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 52802-2022</t>
+          <t>A 40815-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3036,10 +3031,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44875</v>
+        <v>44824</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3051,13 +3046,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>5.8</v>
+        <v>15.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3100,7 +3090,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 6734-2022</t>
+          <t>A 33022-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3114,10 +3104,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44602</v>
+        <v>45840</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3130,7 +3120,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>32.3</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3173,7 +3163,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 1906-2022</t>
+          <t>A 55072-2021</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3187,10 +3177,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44575</v>
+        <v>44474</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3203,7 +3193,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3246,7 +3236,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 30621-2023</t>
+          <t>A 61260-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3260,10 +3250,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45112</v>
+        <v>46000</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3276,7 +3266,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3319,7 +3309,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 30623-2023</t>
+          <t>A 10516-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3333,10 +3323,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45112</v>
+        <v>44623</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3349,7 +3339,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3392,7 +3382,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 59853-2022</t>
+          <t>A 10517-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3406,10 +3396,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44908</v>
+        <v>44623</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3422,7 +3412,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3465,7 +3455,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 39269-2023</t>
+          <t>A 6734-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3479,10 +3469,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45166</v>
+        <v>44602</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3495,7 +3485,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.3</v>
+        <v>32.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3538,7 +3528,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 59612-2021</t>
+          <t>A 30634-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3552,10 +3542,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44491</v>
+        <v>45112</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3568,7 +3558,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3611,7 +3601,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 3683-2023</t>
+          <t>A 52795-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3625,10 +3615,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44950</v>
+        <v>45226</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3640,13 +3630,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>6.3</v>
+        <v>3.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3689,7 +3674,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 19266-2024</t>
+          <t>A 16735-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3703,10 +3688,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45428</v>
+        <v>45030</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3719,7 +3704,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3762,7 +3747,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 23574-2023</t>
+          <t>A 19082-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3776,10 +3761,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45077</v>
+        <v>45048</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3791,8 +3776,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3835,7 +3825,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 10516-2022</t>
+          <t>A 10298-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3849,10 +3839,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44623</v>
+        <v>46076</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3865,7 +3855,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3908,7 +3898,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 10517-2022</t>
+          <t>A 26274-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3922,10 +3912,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44623</v>
+        <v>46182</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3938,7 +3928,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3981,7 +3971,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 39717-2023</t>
+          <t>A 26257-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3995,10 +3985,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45167</v>
+        <v>46182</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4011,7 +4001,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4054,7 +4044,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 41446-2023</t>
+          <t>A 27399-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4064,14 +4054,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45175</v>
+        <v>46189</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4083,13 +4073,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>8.4</v>
+        <v>1.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4132,7 +4117,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 1040-2025</t>
+          <t>A 27400-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4142,14 +4127,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45666</v>
+        <v>46189</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4162,7 +4147,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4205,7 +4190,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 30634-2023</t>
+          <t>A 26029-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4219,10 +4204,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45112</v>
+        <v>44734</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4234,8 +4219,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>6.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4278,7 +4268,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 26382-2023</t>
+          <t>A 59612-2021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4292,10 +4282,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45092</v>
+        <v>44491</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4307,13 +4297,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>20.3</v>
+        <v>3.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4356,7 +4341,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 55003-2022</t>
+          <t>A 52802-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4370,10 +4355,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44886</v>
+        <v>44875</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4385,8 +4370,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4429,7 +4419,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 59609-2021</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4446,7 +4436,7 @@
         <v>44491</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4459,7 +4449,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>12.7</v>
+        <v>6.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4502,7 +4492,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 10298-2026</t>
+          <t>A 39269-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4516,10 +4506,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46076</v>
+        <v>45166</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4532,7 +4522,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4575,7 +4565,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 40607-2024</t>
+          <t>A 59609-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4589,10 +4579,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45556</v>
+        <v>44491</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4605,7 +4595,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.2</v>
+        <v>12.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4648,7 +4638,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 59805-2024</t>
+          <t>A 19266-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4662,10 +4652,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45639</v>
+        <v>45428</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4678,7 +4668,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4721,7 +4711,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 8193-2023</t>
+          <t>A 52809-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4735,10 +4725,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44974</v>
+        <v>44875</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4756,7 +4746,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>10.5</v>
+        <v>2.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4799,7 +4789,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 8228-2023</t>
+          <t>A 3683-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4813,10 +4803,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44974</v>
+        <v>44950</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4828,8 +4818,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>13.9</v>
+        <v>6.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4872,7 +4867,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 51096-2024</t>
+          <t>A 35521-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4886,10 +4881,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45603</v>
+        <v>46262</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4901,8 +4896,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>1.3</v>
+        <v>6.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4945,7 +4945,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 47123-2024</t>
+          <t>A 35459-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4959,10 +4959,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45586</v>
+        <v>46262</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5.3</v>
+        <v>3.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5018,7 +5018,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 38308-2023</t>
+          <t>A 1906-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5032,10 +5032,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45161</v>
+        <v>44575</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5091,7 +5091,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 61260-2025</t>
+          <t>A 37045-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5105,10 +5105,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46000</v>
+        <v>46273</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5120,8 +5120,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5164,7 +5169,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 26029-2022</t>
+          <t>A 59853-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5178,10 +5183,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44734</v>
+        <v>44908</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5193,13 +5198,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>9.699999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5242,7 +5242,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 33022-2025</t>
+          <t>A 37054-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5256,10 +5256,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45840</v>
+        <v>46273</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5271,8 +5271,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>6.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5315,7 +5320,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 31883-2022</t>
+          <t>A 8193-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5329,10 +5334,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44777</v>
+        <v>44974</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5344,8 +5349,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>1.5</v>
+        <v>10.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5388,7 +5398,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 52789-2024</t>
+          <t>A 8228-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5402,10 +5412,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45610</v>
+        <v>44974</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5418,7 +5428,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.4</v>
+        <v>13.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5461,7 +5471,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 26274-2026</t>
+          <t>A 31883-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5475,10 +5485,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46182</v>
+        <v>44777</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5491,7 +5501,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5534,7 +5544,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 26257-2026</t>
+          <t>A 37865-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5548,10 +5558,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46182</v>
+        <v>46279</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5563,8 +5573,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>1.3</v>
+        <v>9.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5607,7 +5622,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 27399-2026</t>
+          <t>A 23574-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5617,14 +5632,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46189</v>
+        <v>45077</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5637,7 +5652,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5680,7 +5695,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 27400-2026</t>
+          <t>A 26382-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5690,14 +5705,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46189</v>
+        <v>45092</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5709,8 +5724,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>3</v>
+        <v>20.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5753,7 +5773,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 35521-2026</t>
+          <t>A 52789-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5767,10 +5787,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46262</v>
+        <v>45610</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5782,13 +5802,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>6.2</v>
+        <v>2.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5831,7 +5846,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 35459-2026</t>
+          <t>A 19420-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5845,10 +5860,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46262</v>
+        <v>45429</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5861,7 +5876,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5904,7 +5919,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 37054-2026</t>
+          <t>A 60754-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5918,10 +5933,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46273</v>
+        <v>45644</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5933,13 +5948,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>6.3</v>
+        <v>2.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5982,7 +5992,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 37045-2026</t>
+          <t>A 24023-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5996,10 +6006,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46273</v>
+        <v>45796</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6011,13 +6021,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>7.6</v>
+        <v>1.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6060,7 +6065,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 37865-2026</t>
+          <t>A 1040-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6074,10 +6079,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46279</v>
+        <v>45666</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6089,13 +6094,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>9.1</v>
+        <v>1.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6155,7 +6155,7 @@
         <v>44628</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 53870-2022</t>
+          <t>A 25961-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44880</v>
+        <v>46181</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1430,13 +1430,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>2.3</v>
+        <v>7.3</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1448,7 +1443,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1460,10 +1455,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1472,46 +1467,50 @@
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 25961-2026</t>
+          <t>A 53870-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1525,10 +1524,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46181</v>
+        <v>44880</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1540,8 +1539,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>7.3</v>
+        <v>2.3</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1553,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1565,10 +1569,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1577,43 +1581,39 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
-        <v/>
-      </c>
-      <c r="Z10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44470</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44545</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44600</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>44620</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 41446-2023</t>
+          <t>A 19082-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2150,10 +2150,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45175</v>
+        <v>45048</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>8.4</v>
+        <v>6.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2214,7 +2214,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 30621-2023</t>
+          <t>A 40815-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45112</v>
+        <v>44824</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.2</v>
+        <v>15.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2287,7 +2287,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 30623-2023</t>
+          <t>A 55072-2021</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2301,10 +2301,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45112</v>
+        <v>44474</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2360,7 +2360,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 51096-2024</t>
+          <t>A 52795-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45603</v>
+        <v>45226</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2433,7 +2433,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 40607-2024</t>
+          <t>A 24023-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45556</v>
+        <v>45796</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2506,7 +2506,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 11771-2025</t>
+          <t>A 19420-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45727</v>
+        <v>45429</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2579,7 +2579,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 59805-2024</t>
+          <t>A 60754-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45639</v>
+        <v>45644</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2652,7 +2652,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 39717-2023</t>
+          <t>A 52802-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45167</v>
+        <v>44875</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2681,8 +2681,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>2.3</v>
+        <v>5.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2725,7 +2730,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 38308-2023</t>
+          <t>A 6734-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2739,10 +2744,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45161</v>
+        <v>44602</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2755,7 +2760,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.9</v>
+        <v>32.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2798,7 +2803,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 30621-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2812,10 +2817,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44491</v>
+        <v>45112</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2828,7 +2833,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>6.8</v>
+        <v>3.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2871,7 +2876,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 55003-2022</t>
+          <t>A 30623-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2885,10 +2890,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44886</v>
+        <v>45112</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2901,7 +2906,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>6.6</v>
+        <v>2.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2944,7 +2949,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 47123-2024</t>
+          <t>A 59853-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2958,10 +2963,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45586</v>
+        <v>44908</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2974,7 +2979,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>5.3</v>
+        <v>0.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3017,7 +3022,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 40815-2022</t>
+          <t>A 10298-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3031,10 +3036,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44824</v>
+        <v>46076</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3047,7 +3052,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>15.9</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3090,7 +3095,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33022-2025</t>
+          <t>A 3683-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3104,10 +3109,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45840</v>
+        <v>44950</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3119,8 +3124,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>6.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3163,7 +3173,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 55072-2021</t>
+          <t>A 23574-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3177,10 +3187,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44474</v>
+        <v>45077</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3193,7 +3203,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3236,7 +3246,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 61260-2025</t>
+          <t>A 41446-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3250,10 +3260,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46000</v>
+        <v>45175</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3265,8 +3275,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>4.4</v>
+        <v>8.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3309,7 +3324,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 10516-2022</t>
+          <t>A 30634-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3323,10 +3338,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44623</v>
+        <v>45112</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3339,7 +3354,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.1</v>
+        <v>6.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3382,7 +3397,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10517-2022</t>
+          <t>A 26382-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3396,10 +3411,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44623</v>
+        <v>45092</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3411,8 +3426,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>1.2</v>
+        <v>20.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3455,7 +3475,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 6734-2022</t>
+          <t>A 61260-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3469,10 +3489,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44602</v>
+        <v>46000</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3485,7 +3505,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>32.3</v>
+        <v>4.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3528,7 +3548,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 30634-2023</t>
+          <t>A 33022-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3542,10 +3562,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45112</v>
+        <v>45840</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3558,7 +3578,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>6.2</v>
+        <v>1.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3601,7 +3621,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 52795-2023</t>
+          <t>A 1040-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3615,10 +3635,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45226</v>
+        <v>45666</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3631,7 +3651,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3674,7 +3694,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 16735-2023</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3688,10 +3708,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45030</v>
+        <v>44491</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3704,7 +3724,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>8.699999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3747,7 +3767,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 19082-2023</t>
+          <t>A 11771-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3761,10 +3781,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45048</v>
+        <v>45727</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3776,13 +3796,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>6.5</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3825,7 +3840,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 10298-2026</t>
+          <t>A 52809-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3839,10 +3854,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46076</v>
+        <v>44875</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3854,8 +3869,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3898,7 +3918,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 26274-2026</t>
+          <t>A 16735-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3912,10 +3932,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46182</v>
+        <v>45030</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3928,7 +3948,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3971,7 +3991,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 26257-2026</t>
+          <t>A 1906-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3985,10 +4005,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46182</v>
+        <v>44575</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4001,7 +4021,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4044,7 +4064,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 27399-2026</t>
+          <t>A 26274-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4054,14 +4074,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46189</v>
+        <v>46182</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4074,7 +4094,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4117,7 +4137,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 27400-2026</t>
+          <t>A 26257-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4127,14 +4147,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46189</v>
+        <v>46182</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4147,7 +4167,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4190,7 +4210,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 26029-2022</t>
+          <t>A 27399-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4200,14 +4220,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44734</v>
+        <v>46189</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4219,13 +4239,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>9.699999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4268,7 +4283,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 59612-2021</t>
+          <t>A 27400-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4278,14 +4293,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44491</v>
+        <v>46189</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4298,7 +4313,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4341,7 +4356,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 52802-2022</t>
+          <t>A 39269-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4355,10 +4370,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44875</v>
+        <v>45166</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4370,13 +4385,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>5.8</v>
+        <v>3.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4419,7 +4429,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 59612-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4436,7 +4446,7 @@
         <v>44491</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4449,7 +4459,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>6.8</v>
+        <v>3.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4492,7 +4502,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 39269-2023</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4506,10 +4516,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45166</v>
+        <v>44491</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4522,7 +4532,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.3</v>
+        <v>6.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4565,7 +4575,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 59609-2021</t>
+          <t>A 19266-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4579,10 +4589,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44491</v>
+        <v>45428</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4595,7 +4605,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>12.7</v>
+        <v>3.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4638,7 +4648,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 19266-2024</t>
+          <t>A 10516-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4652,10 +4662,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45428</v>
+        <v>44623</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4668,7 +4678,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4711,7 +4721,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 52809-2022</t>
+          <t>A 10517-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4725,10 +4735,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44875</v>
+        <v>44623</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4740,13 +4750,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4789,7 +4794,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 3683-2023</t>
+          <t>A 39717-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4803,10 +4808,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44950</v>
+        <v>45167</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4818,13 +4823,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>6.3</v>
+        <v>2.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4884,7 +4884,7 @@
         <v>46262</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>46262</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 1906-2022</t>
+          <t>A 55003-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5032,10 +5032,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44575</v>
+        <v>44886</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>6.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5091,7 +5091,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 37045-2026</t>
+          <t>A 37054-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5108,7 +5108,7 @@
         <v>46273</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>7.6</v>
+        <v>6.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5169,7 +5169,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 59853-2022</t>
+          <t>A 37045-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5183,10 +5183,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44908</v>
+        <v>46273</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5198,8 +5198,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>7.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5242,7 +5247,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 37054-2026</t>
+          <t>A 37865-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5256,10 +5261,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46273</v>
+        <v>46279</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5277,7 +5282,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>6.3</v>
+        <v>9.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5320,7 +5325,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 8193-2023</t>
+          <t>A 59609-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5334,10 +5339,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44974</v>
+        <v>44491</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5349,13 +5354,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>10.5</v>
+        <v>12.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 8228-2023</t>
+          <t>A 40607-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5412,10 +5412,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44974</v>
+        <v>45556</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>13.9</v>
+        <v>3.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5471,7 +5471,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 31883-2022</t>
+          <t>A 59805-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44777</v>
+        <v>45639</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5544,7 +5544,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 37865-2026</t>
+          <t>A 8193-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5558,10 +5558,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46279</v>
+        <v>44974</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>9.1</v>
+        <v>10.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5622,7 +5622,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 23574-2023</t>
+          <t>A 8228-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5636,10 +5636,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45077</v>
+        <v>44974</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>13.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5695,7 +5695,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 26382-2023</t>
+          <t>A 51096-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5709,10 +5709,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45092</v>
+        <v>45603</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5724,13 +5724,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>20.3</v>
+        <v>1.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5773,7 +5768,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 52789-2024</t>
+          <t>A 47123-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5787,10 +5782,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45610</v>
+        <v>45586</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5803,7 +5798,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.4</v>
+        <v>5.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5846,7 +5841,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 19420-2024</t>
+          <t>A 38308-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5860,10 +5855,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45429</v>
+        <v>45161</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5876,7 +5871,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5919,7 +5914,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 60754-2024</t>
+          <t>A 26029-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5933,10 +5928,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45644</v>
+        <v>44734</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5948,8 +5943,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>2.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5992,7 +5992,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 24023-2025</t>
+          <t>A 31883-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6006,10 +6006,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45796</v>
+        <v>44777</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 1040-2025</t>
+          <t>A 52789-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6079,10 +6079,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45666</v>
+        <v>45610</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6155,7 +6155,7 @@
         <v>44628</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>46181</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>44880</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44470</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44545</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44600</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>44620</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>45048</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>44824</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>44474</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>45226</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>45796</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>45429</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>45644</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         <v>44875</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>44602</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>45112</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>45112</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>44908</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>46076</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>44950</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>45077</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>45175</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>45112</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>45092</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         <v>46000</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>45840</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>45666</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>44491</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>45727</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>44875</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>45030</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>44575</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>46182</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>46182</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>46189</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>46189</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>45166</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>44491</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>44491</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>45428</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>44623</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>44623</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>45167</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>46262</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>46262</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>44886</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>46273</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46273</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>46279</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>44491</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>45556</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>45639</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>44974</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5639,7 +5639,7 @@
         <v>44974</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>45603</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v>45586</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>45161</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>44734</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>44777</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>45610</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         <v>44628</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>46181</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>44880</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44470</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44545</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44600</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>44620</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>45048</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>44824</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>44474</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>45226</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>45796</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>45429</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>45644</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         <v>44875</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>44602</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>45112</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>45112</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>44908</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>46076</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>44950</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>45077</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>45175</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>45112</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>45092</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         <v>46000</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>45840</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>45666</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>44491</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>45727</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>44875</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>45030</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>44575</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>46182</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>46182</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>46189</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>46189</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>45166</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>44491</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>44491</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>45428</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>44623</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>44623</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>45167</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>46262</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>46262</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>44886</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>46273</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46273</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>46279</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>44491</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>45556</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>45639</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>44974</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5639,7 +5639,7 @@
         <v>44974</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>45603</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v>45586</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>45161</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>44734</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>44777</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>45610</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         <v>44628</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25961-2026</t>
+          <t>A 53870-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46181</v>
+        <v>44880</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1430,8 +1430,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>7.3</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1443,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1455,10 +1460,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1467,50 +1472,46 @@
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
-        <v/>
-      </c>
-      <c r="Z9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 53870-2022</t>
+          <t>A 25961-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1524,10 +1525,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44880</v>
+        <v>46181</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1539,13 +1540,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>2.3</v>
+        <v>7.3</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1557,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1569,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1581,39 +1577,43 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
+        <v/>
+      </c>
+      <c r="Z10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44470</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44545</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44600</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>44620</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 19082-2023</t>
+          <t>A 41446-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2150,10 +2150,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45048</v>
+        <v>45175</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>6.5</v>
+        <v>8.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2214,7 +2214,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 40815-2022</t>
+          <t>A 30621-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44824</v>
+        <v>45112</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>15.9</v>
+        <v>3.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2287,7 +2287,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 55072-2021</t>
+          <t>A 30623-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2301,10 +2301,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44474</v>
+        <v>45112</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2360,7 +2360,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 52795-2023</t>
+          <t>A 51096-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45226</v>
+        <v>45603</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2433,7 +2433,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 24023-2025</t>
+          <t>A 52789-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45796</v>
+        <v>45610</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2506,7 +2506,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 19420-2024</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45429</v>
+        <v>44491</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.8</v>
+        <v>6.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2579,7 +2579,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 60754-2024</t>
+          <t>A 19420-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45644</v>
+        <v>45429</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2652,7 +2652,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 52802-2022</t>
+          <t>A 60754-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44875</v>
+        <v>45644</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2681,13 +2681,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>5.8</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2730,7 +2725,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 6734-2022</t>
+          <t>A 40607-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2744,10 +2739,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44602</v>
+        <v>45556</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2760,7 +2755,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>32.3</v>
+        <v>3.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2803,7 +2798,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 30621-2023</t>
+          <t>A 24023-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2817,10 +2812,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45112</v>
+        <v>45796</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2833,7 +2828,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2876,7 +2871,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 30623-2023</t>
+          <t>A 11771-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2890,10 +2885,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45112</v>
+        <v>45727</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2906,7 +2901,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2949,7 +2944,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 59853-2022</t>
+          <t>A 1040-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2963,10 +2958,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44908</v>
+        <v>45666</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2979,7 +2974,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3022,7 +3017,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 10298-2026</t>
+          <t>A 59805-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3036,10 +3031,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46076</v>
+        <v>45639</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3052,7 +3047,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3095,7 +3090,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 3683-2023</t>
+          <t>A 39717-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3109,10 +3104,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44950</v>
+        <v>45167</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3124,13 +3119,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>6.3</v>
+        <v>2.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3173,7 +3163,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 23574-2023</t>
+          <t>A 38308-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3187,10 +3177,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45077</v>
+        <v>45161</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3203,7 +3193,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3246,7 +3236,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 41446-2023</t>
+          <t>A 55003-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3260,10 +3250,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45175</v>
+        <v>44886</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3275,13 +3265,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3324,7 +3309,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 30634-2023</t>
+          <t>A 47123-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3338,10 +3323,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45112</v>
+        <v>45586</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3354,7 +3339,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3397,7 +3382,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 26382-2023</t>
+          <t>A 40815-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3411,10 +3396,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45092</v>
+        <v>44824</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3426,13 +3411,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>20.3</v>
+        <v>15.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3475,7 +3455,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 61260-2025</t>
+          <t>A 55072-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3489,10 +3469,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46000</v>
+        <v>44474</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3505,7 +3485,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3548,7 +3528,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33022-2025</t>
+          <t>A 10298-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3562,10 +3542,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45840</v>
+        <v>46076</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3621,7 +3601,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 1040-2025</t>
+          <t>A 10516-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3635,10 +3615,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45666</v>
+        <v>44623</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3651,7 +3631,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3694,7 +3674,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 10517-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3708,10 +3688,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44491</v>
+        <v>44623</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3724,7 +3704,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6.8</v>
+        <v>1.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3767,7 +3747,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 11771-2025</t>
+          <t>A 6734-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3781,10 +3761,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45727</v>
+        <v>44602</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3797,7 +3777,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>32.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3840,7 +3820,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 52809-2022</t>
+          <t>A 30634-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3854,10 +3834,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44875</v>
+        <v>45112</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3869,13 +3849,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>2.5</v>
+        <v>6.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3918,7 +3893,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 16735-2023</t>
+          <t>A 33022-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3932,10 +3907,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45030</v>
+        <v>45840</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3948,7 +3923,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>8.699999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3991,7 +3966,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 1906-2022</t>
+          <t>A 61260-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4005,10 +3980,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44575</v>
+        <v>46000</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4021,7 +3996,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4064,7 +4039,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 26274-2026</t>
+          <t>A 52795-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4078,10 +4053,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46182</v>
+        <v>45226</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4094,7 +4069,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4137,7 +4112,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 26257-2026</t>
+          <t>A 16735-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4151,10 +4126,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46182</v>
+        <v>45030</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4167,7 +4142,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4210,7 +4185,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 27399-2026</t>
+          <t>A 19082-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4220,14 +4195,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46189</v>
+        <v>45048</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4239,8 +4214,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>6.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4283,7 +4263,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 27400-2026</t>
+          <t>A 26029-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4293,14 +4273,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46189</v>
+        <v>44734</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4312,8 +4292,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4356,7 +4341,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 39269-2023</t>
+          <t>A 59612-2021</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4370,10 +4355,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45166</v>
+        <v>44491</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4386,7 +4371,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4429,7 +4414,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 59612-2021</t>
+          <t>A 52802-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4443,10 +4428,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44491</v>
+        <v>44875</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4458,8 +4443,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>3.2</v>
+        <v>5.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4502,7 +4492,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 26274-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4516,10 +4506,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44491</v>
+        <v>46182</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4532,7 +4522,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>6.8</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4575,7 +4565,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 19266-2024</t>
+          <t>A 26257-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4589,10 +4579,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45428</v>
+        <v>46182</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4605,7 +4595,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4648,7 +4638,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 10516-2022</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4662,10 +4652,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44623</v>
+        <v>44491</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4678,7 +4668,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.1</v>
+        <v>6.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4721,7 +4711,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 10517-2022</t>
+          <t>A 27399-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4731,14 +4721,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44623</v>
+        <v>46189</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4751,7 +4741,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4794,7 +4784,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 39717-2023</t>
+          <t>A 39269-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4808,10 +4798,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45167</v>
+        <v>45166</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4824,7 +4814,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4867,7 +4857,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 35521-2026</t>
+          <t>A 27400-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4877,14 +4867,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46262</v>
+        <v>46189</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4896,13 +4886,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>6.2</v>
+        <v>3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4945,7 +4930,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 35459-2026</t>
+          <t>A 59609-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4959,10 +4944,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46262</v>
+        <v>44491</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4975,7 +4960,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.5</v>
+        <v>12.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5018,7 +5003,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 55003-2022</t>
+          <t>A 19266-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5032,10 +5017,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44886</v>
+        <v>45428</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5048,7 +5033,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>6.6</v>
+        <v>3.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5091,7 +5076,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 37054-2026</t>
+          <t>A 52809-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5105,10 +5090,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46273</v>
+        <v>44875</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5126,7 +5111,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>6.3</v>
+        <v>2.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5169,7 +5154,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 37045-2026</t>
+          <t>A 3683-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5183,10 +5168,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46273</v>
+        <v>44950</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5204,7 +5189,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>7.6</v>
+        <v>6.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5247,7 +5232,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 37865-2026</t>
+          <t>A 1906-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5261,10 +5246,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46279</v>
+        <v>44575</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5276,13 +5261,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>9.1</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5325,7 +5305,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 59609-2021</t>
+          <t>A 35521-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5339,10 +5319,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44491</v>
+        <v>46262</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5354,8 +5334,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>12.7</v>
+        <v>6.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5398,7 +5383,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 40607-2024</t>
+          <t>A 35459-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5412,10 +5397,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45556</v>
+        <v>46262</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5428,7 +5413,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5471,7 +5456,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 59805-2024</t>
+          <t>A 59853-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5485,10 +5470,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45639</v>
+        <v>44908</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5501,7 +5486,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5561,7 +5546,7 @@
         <v>44974</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5639,7 +5624,7 @@
         <v>44974</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5695,7 +5680,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 51096-2024</t>
+          <t>A 37045-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5709,10 +5694,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45603</v>
+        <v>46273</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5724,8 +5709,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>1.3</v>
+        <v>7.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5768,7 +5758,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 47123-2024</t>
+          <t>A 31883-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5782,10 +5772,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45586</v>
+        <v>44777</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5798,7 +5788,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>5.3</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5841,7 +5831,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 38308-2023</t>
+          <t>A 37054-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5855,10 +5845,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45161</v>
+        <v>46273</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5870,8 +5860,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>2.9</v>
+        <v>6.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5914,7 +5909,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 26029-2022</t>
+          <t>A 23574-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5928,10 +5923,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44734</v>
+        <v>45077</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5943,13 +5938,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>9.699999999999999</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5992,7 +5982,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 31883-2022</t>
+          <t>A 37865-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6006,10 +5996,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44777</v>
+        <v>46279</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6021,8 +6011,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1.5</v>
+        <v>9.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6065,7 +6060,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 52789-2024</t>
+          <t>A 26382-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6079,10 +6074,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45610</v>
+        <v>45092</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6094,8 +6089,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>2.4</v>
+        <v>20.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6155,7 +6155,7 @@
         <v>44628</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 53870-2022</t>
+          <t>A 25961-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44880</v>
+        <v>46181</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1430,13 +1430,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>2.3</v>
+        <v>7.3</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1448,7 +1443,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1460,10 +1455,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1472,46 +1467,50 @@
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 25961-2026</t>
+          <t>A 53870-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1525,10 +1524,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46181</v>
+        <v>44880</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1540,8 +1539,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>7.3</v>
+        <v>2.3</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1553,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1565,10 +1569,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1577,43 +1581,39 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
-        <v/>
-      </c>
-      <c r="Z10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44470</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44545</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44600</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>44620</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 41446-2023</t>
+          <t>A 19082-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2150,10 +2150,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45175</v>
+        <v>45048</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>8.4</v>
+        <v>6.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2214,7 +2214,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 30621-2023</t>
+          <t>A 40815-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45112</v>
+        <v>44824</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.2</v>
+        <v>15.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2287,7 +2287,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 30623-2023</t>
+          <t>A 55072-2021</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2301,10 +2301,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45112</v>
+        <v>44474</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2360,7 +2360,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 51096-2024</t>
+          <t>A 52795-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45603</v>
+        <v>45226</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2433,7 +2433,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 52789-2024</t>
+          <t>A 24023-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45610</v>
+        <v>45796</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2506,7 +2506,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 19420-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44491</v>
+        <v>45429</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>6.8</v>
+        <v>3.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2579,7 +2579,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 19420-2024</t>
+          <t>A 60754-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45429</v>
+        <v>45644</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2652,7 +2652,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 60754-2024</t>
+          <t>A 52802-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45644</v>
+        <v>44875</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2681,8 +2681,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>5.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2725,7 +2730,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 40607-2024</t>
+          <t>A 6734-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2739,10 +2744,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45556</v>
+        <v>44602</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2755,7 +2760,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.2</v>
+        <v>32.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2798,7 +2803,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 24023-2025</t>
+          <t>A 30621-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2812,10 +2817,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45796</v>
+        <v>45112</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2828,7 +2833,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2871,7 +2876,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 11771-2025</t>
+          <t>A 30623-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2885,10 +2890,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45727</v>
+        <v>45112</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2901,7 +2906,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2944,7 +2949,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 1040-2025</t>
+          <t>A 59853-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2958,10 +2963,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45666</v>
+        <v>44908</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2974,7 +2979,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3017,7 +3022,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 59805-2024</t>
+          <t>A 1040-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3031,10 +3036,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45639</v>
+        <v>45666</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3047,7 +3052,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3090,7 +3095,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 39717-2023</t>
+          <t>A 3683-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3104,10 +3109,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45167</v>
+        <v>44950</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3119,8 +3124,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>2.3</v>
+        <v>6.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3163,7 +3173,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 38308-2023</t>
+          <t>A 23574-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3177,10 +3187,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45161</v>
+        <v>45077</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3193,7 +3203,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3236,7 +3246,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 55003-2022</t>
+          <t>A 41446-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3250,10 +3260,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44886</v>
+        <v>45175</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3265,8 +3275,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3309,7 +3324,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 47123-2024</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3323,10 +3338,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45586</v>
+        <v>44491</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3339,7 +3354,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3382,7 +3397,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 40815-2022</t>
+          <t>A 30634-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3396,10 +3411,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44824</v>
+        <v>45112</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3412,7 +3427,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>15.9</v>
+        <v>6.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3455,7 +3470,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 55072-2021</t>
+          <t>A 26382-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3469,10 +3484,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44474</v>
+        <v>45092</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3484,8 +3499,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>3.4</v>
+        <v>20.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3545,7 +3565,7 @@
         <v>46076</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3601,7 +3621,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 10516-2022</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3615,10 +3635,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44623</v>
+        <v>44491</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3631,7 +3651,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.1</v>
+        <v>6.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3674,7 +3694,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 10517-2022</t>
+          <t>A 11771-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3688,10 +3708,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44623</v>
+        <v>45727</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3704,7 +3724,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3747,7 +3767,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 6734-2022</t>
+          <t>A 52809-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3761,10 +3781,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44602</v>
+        <v>44875</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3776,8 +3796,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>32.3</v>
+        <v>2.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3820,7 +3845,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 30634-2023</t>
+          <t>A 61260-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3834,10 +3859,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45112</v>
+        <v>46000</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3850,7 +3875,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3893,7 +3918,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 33022-2025</t>
+          <t>A 16735-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3907,10 +3932,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45840</v>
+        <v>45030</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3923,7 +3948,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3966,7 +3991,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 61260-2025</t>
+          <t>A 1906-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3980,10 +4005,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46000</v>
+        <v>44575</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3996,7 +4021,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4039,7 +4064,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 52795-2023</t>
+          <t>A 33022-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4053,10 +4078,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45226</v>
+        <v>45840</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4069,7 +4094,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4112,7 +4137,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 16735-2023</t>
+          <t>A 39269-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4126,10 +4151,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45030</v>
+        <v>45166</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4142,7 +4167,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>8.699999999999999</v>
+        <v>3.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4185,7 +4210,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 19082-2023</t>
+          <t>A 59612-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4199,10 +4224,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45048</v>
+        <v>44491</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4214,13 +4239,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>6.5</v>
+        <v>3.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4263,7 +4283,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 26029-2022</t>
+          <t>A 19266-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4277,10 +4297,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44734</v>
+        <v>45428</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4292,13 +4312,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>9.699999999999999</v>
+        <v>3.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4341,7 +4356,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 59612-2021</t>
+          <t>A 10516-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4355,10 +4370,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44491</v>
+        <v>44623</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4371,7 +4386,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4414,7 +4429,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 52802-2022</t>
+          <t>A 10517-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4428,10 +4443,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44875</v>
+        <v>44623</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4443,13 +4458,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>5.8</v>
+        <v>1.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4492,7 +4502,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26274-2026</t>
+          <t>A 39717-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4506,10 +4516,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46182</v>
+        <v>45167</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4522,7 +4532,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4565,7 +4575,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 26257-2026</t>
+          <t>A 26274-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4582,7 +4592,7 @@
         <v>46182</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4595,7 +4605,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4638,7 +4648,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 26257-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4652,10 +4662,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44491</v>
+        <v>46182</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4668,7 +4678,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>6.8</v>
+        <v>1.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4728,7 +4738,7 @@
         <v>46189</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4784,7 +4794,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 39269-2023</t>
+          <t>A 27400-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4794,14 +4804,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45166</v>
+        <v>46189</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4814,7 +4824,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4857,7 +4867,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 27400-2026</t>
+          <t>A 55003-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4867,14 +4877,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46189</v>
+        <v>44886</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4887,7 +4897,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3</v>
+        <v>6.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4947,7 +4957,7 @@
         <v>44491</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5003,7 +5013,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 19266-2024</t>
+          <t>A 40607-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5017,10 +5027,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45428</v>
+        <v>45556</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5033,7 +5043,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5076,7 +5086,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 52809-2022</t>
+          <t>A 35521-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5090,10 +5100,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44875</v>
+        <v>46262</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5111,7 +5121,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.5</v>
+        <v>6.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5154,7 +5164,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 3683-2023</t>
+          <t>A 35459-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5168,10 +5178,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44950</v>
+        <v>46262</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5183,13 +5193,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>6.3</v>
+        <v>3.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5232,7 +5237,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 1906-2022</t>
+          <t>A 59805-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5246,10 +5251,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44575</v>
+        <v>45639</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5262,7 +5267,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5305,7 +5310,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 35521-2026</t>
+          <t>A 8193-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5319,10 +5324,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46262</v>
+        <v>44974</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5340,7 +5345,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5383,7 +5388,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 35459-2026</t>
+          <t>A 8228-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5397,10 +5402,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46262</v>
+        <v>44974</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5413,7 +5418,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.5</v>
+        <v>13.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5456,7 +5461,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 59853-2022</t>
+          <t>A 51096-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5470,10 +5475,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44908</v>
+        <v>45603</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5486,7 +5491,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5529,7 +5534,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 8193-2023</t>
+          <t>A 47123-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5543,10 +5548,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44974</v>
+        <v>45586</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5558,13 +5563,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5607,7 +5607,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 8228-2023</t>
+          <t>A 37054-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5621,10 +5621,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44974</v>
+        <v>46273</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5636,8 +5636,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>13.9</v>
+        <v>6.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5680,7 +5685,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 37045-2026</t>
+          <t>A 38308-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5694,10 +5699,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46273</v>
+        <v>45161</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5709,13 +5714,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>7.6</v>
+        <v>2.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5758,7 +5758,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 31883-2022</t>
+          <t>A 37045-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44777</v>
+        <v>46273</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5787,8 +5787,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>1.5</v>
+        <v>7.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5831,7 +5836,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 37054-2026</t>
+          <t>A 37865-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5845,10 +5850,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46273</v>
+        <v>46279</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5866,7 +5871,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>6.3</v>
+        <v>9.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5909,7 +5914,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 23574-2023</t>
+          <t>A 26029-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5923,10 +5928,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45077</v>
+        <v>44734</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5938,8 +5943,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5982,7 +5992,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 37865-2026</t>
+          <t>A 31883-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5996,10 +6006,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46279</v>
+        <v>44777</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6011,13 +6021,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>9.1</v>
+        <v>1.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6060,7 +6065,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 26382-2023</t>
+          <t>A 52789-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6074,10 +6079,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45092</v>
+        <v>45610</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6089,13 +6094,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>20.3</v>
+        <v>2.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6155,7 +6155,7 @@
         <v>44628</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25961-2026</t>
+          <t>A 53870-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46181</v>
+        <v>44880</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1430,8 +1430,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>7.3</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1443,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1455,10 +1460,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1467,50 +1472,46 @@
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
-        <v/>
-      </c>
-      <c r="Z9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 53870-2022</t>
+          <t>A 25961-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1524,10 +1525,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44880</v>
+        <v>46181</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1539,13 +1540,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>2.3</v>
+        <v>7.3</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1557,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1569,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1581,39 +1577,43 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
+        <v/>
+      </c>
+      <c r="Z10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 54188-2021</t>
+          <t>A 6319-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1858,10 +1858,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44470</v>
+        <v>44600</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1934,7 +1934,7 @@
         <v>44545</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 6319-2022</t>
+          <t>A 54188-2021</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44600</v>
+        <v>44470</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.8</v>
+        <v>6.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>44620</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 19082-2023</t>
+          <t>A 41446-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2150,10 +2150,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45048</v>
+        <v>45175</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>6.5</v>
+        <v>8.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2214,7 +2214,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 40815-2022</t>
+          <t>A 30621-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44824</v>
+        <v>45112</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>15.9</v>
+        <v>3.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2287,7 +2287,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 55072-2021</t>
+          <t>A 30623-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2301,10 +2301,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44474</v>
+        <v>45112</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2360,7 +2360,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 52795-2023</t>
+          <t>A 1906-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45226</v>
+        <v>44575</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2433,7 +2433,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 24023-2025</t>
+          <t>A 39717-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45796</v>
+        <v>45167</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2506,7 +2506,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 19420-2024</t>
+          <t>A 38308-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45429</v>
+        <v>45161</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2579,7 +2579,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 60754-2024</t>
+          <t>A 16735-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45644</v>
+        <v>45030</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2652,7 +2652,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 52802-2022</t>
+          <t>A 19082-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44875</v>
+        <v>45048</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2730,7 +2730,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 6734-2022</t>
+          <t>A 55003-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44602</v>
+        <v>44886</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>32.3</v>
+        <v>6.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2803,7 +2803,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 30621-2023</t>
+          <t>A 59853-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45112</v>
+        <v>44908</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2876,7 +2876,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 30623-2023</t>
+          <t>A 8193-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2890,10 +2890,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45112</v>
+        <v>44974</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2905,8 +2905,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>2.6</v>
+        <v>10.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2949,7 +2954,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 59853-2022</t>
+          <t>A 8228-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2963,10 +2968,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44908</v>
+        <v>44974</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2979,7 +2984,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.7</v>
+        <v>13.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3022,7 +3027,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 1040-2025</t>
+          <t>A 47123-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3036,10 +3041,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45666</v>
+        <v>45586</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3052,7 +3057,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3095,7 +3100,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 3683-2023</t>
+          <t>A 40815-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3109,10 +3114,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44950</v>
+        <v>44824</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3124,13 +3129,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>6.3</v>
+        <v>15.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3173,7 +3173,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 23574-2023</t>
+          <t>A 31883-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45077</v>
+        <v>44777</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3246,7 +3246,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 41446-2023</t>
+          <t>A 51096-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3260,10 +3260,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45175</v>
+        <v>45603</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3275,13 +3275,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>8.4</v>
+        <v>1.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3324,7 +3319,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 23574-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3338,10 +3333,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44491</v>
+        <v>45077</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3354,7 +3349,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>6.8</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3397,7 +3392,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 30634-2023</t>
+          <t>A 55072-2021</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3411,10 +3406,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45112</v>
+        <v>44474</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3427,7 +3422,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>6.2</v>
+        <v>3.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3470,7 +3465,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 26382-2023</t>
+          <t>A 26029-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3484,10 +3479,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45092</v>
+        <v>44734</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3505,7 +3500,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>20.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3548,7 +3543,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 10298-2026</t>
+          <t>A 59612-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3562,10 +3557,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46076</v>
+        <v>44491</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3578,7 +3573,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3621,7 +3616,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 26382-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3635,10 +3630,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44491</v>
+        <v>45092</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3650,8 +3645,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>6.8</v>
+        <v>20.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3694,7 +3694,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 11771-2025</t>
+          <t>A 52802-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3708,10 +3708,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45727</v>
+        <v>44875</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3723,8 +3723,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>5.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3767,7 +3772,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 52809-2022</t>
+          <t>A 10516-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3781,10 +3786,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44875</v>
+        <v>44623</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3796,13 +3801,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3845,7 +3845,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 61260-2025</t>
+          <t>A 10517-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46000</v>
+        <v>44623</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.4</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3918,7 +3918,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 16735-2023</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45030</v>
+        <v>44491</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>8.699999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3991,7 +3991,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 1906-2022</t>
+          <t>A 52789-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44575</v>
+        <v>45610</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4064,7 +4064,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 33022-2025</t>
+          <t>A 39269-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4078,10 +4078,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45840</v>
+        <v>45166</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4137,7 +4137,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 39269-2023</t>
+          <t>A 40607-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45166</v>
+        <v>45556</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4210,7 +4210,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 59612-2021</t>
+          <t>A 19420-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4224,10 +4224,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44491</v>
+        <v>45429</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4283,7 +4283,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 19266-2024</t>
+          <t>A 60754-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45428</v>
+        <v>45644</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4356,7 +4356,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 10516-2022</t>
+          <t>A 11771-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4370,10 +4370,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44623</v>
+        <v>45727</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 10517-2022</t>
+          <t>A 24023-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44623</v>
+        <v>45796</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4502,7 +4502,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 39717-2023</t>
+          <t>A 6734-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4516,10 +4516,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45167</v>
+        <v>44602</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.3</v>
+        <v>32.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4575,7 +4575,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 26274-2026</t>
+          <t>A 59609-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4589,10 +4589,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46182</v>
+        <v>44491</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>12.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4648,7 +4648,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 26257-2026</t>
+          <t>A 30634-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4662,10 +4662,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46182</v>
+        <v>45112</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.3</v>
+        <v>6.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4721,7 +4721,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 27399-2026</t>
+          <t>A 1040-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4731,14 +4731,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46189</v>
+        <v>45666</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 27400-2026</t>
+          <t>A 19266-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4804,14 +4804,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46189</v>
+        <v>45428</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4867,7 +4867,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 55003-2022</t>
+          <t>A 52809-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4881,10 +4881,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44886</v>
+        <v>44875</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4896,8 +4896,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>6.6</v>
+        <v>2.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4940,7 +4945,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 59609-2021</t>
+          <t>A 52795-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4954,10 +4959,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44491</v>
+        <v>45226</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4970,7 +4975,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>12.7</v>
+        <v>3.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5013,7 +5018,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 40607-2024</t>
+          <t>A 3683-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5027,10 +5032,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45556</v>
+        <v>44950</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5042,8 +5047,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>3.2</v>
+        <v>6.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5086,7 +5096,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 35521-2026</t>
+          <t>A 59805-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5100,10 +5110,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46262</v>
+        <v>45639</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5115,13 +5125,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>6.2</v>
+        <v>3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5164,7 +5169,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 35459-2026</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5178,10 +5183,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46262</v>
+        <v>44491</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5194,7 +5199,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.5</v>
+        <v>6.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5237,7 +5242,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 59805-2024</t>
+          <t>A 10298-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5251,10 +5256,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45639</v>
+        <v>46076</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5267,7 +5272,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5310,7 +5315,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 8193-2023</t>
+          <t>A 33022-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5324,10 +5329,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44974</v>
+        <v>45840</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5339,13 +5344,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>10.5</v>
+        <v>1.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5388,7 +5388,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 8228-2023</t>
+          <t>A 61260-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5402,10 +5402,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44974</v>
+        <v>46000</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>13.9</v>
+        <v>4.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5461,7 +5461,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 51096-2024</t>
+          <t>A 26274-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5475,10 +5475,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45603</v>
+        <v>46182</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5534,7 +5534,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 47123-2024</t>
+          <t>A 26257-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5548,10 +5548,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45586</v>
+        <v>46182</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5.3</v>
+        <v>1.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5607,7 +5607,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 37054-2026</t>
+          <t>A 27399-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5617,14 +5617,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46273</v>
+        <v>46189</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5636,13 +5636,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>6.3</v>
+        <v>1.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5685,7 +5680,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 38308-2023</t>
+          <t>A 27400-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5695,14 +5690,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45161</v>
+        <v>46189</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5715,7 +5710,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5758,7 +5753,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 37045-2026</t>
+          <t>A 35521-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5772,10 +5767,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46273</v>
+        <v>46262</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5793,7 +5788,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5836,7 +5831,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 37865-2026</t>
+          <t>A 35459-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5850,10 +5845,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46279</v>
+        <v>46262</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5865,13 +5860,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>9.1</v>
+        <v>3.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5914,7 +5904,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 26029-2022</t>
+          <t>A 37045-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5928,10 +5918,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44734</v>
+        <v>46273</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5949,7 +5939,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>9.699999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5992,7 +5982,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 31883-2022</t>
+          <t>A 37054-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6006,10 +5996,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44777</v>
+        <v>46273</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6021,8 +6011,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1.5</v>
+        <v>6.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6065,7 +6060,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 52789-2024</t>
+          <t>A 37865-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6079,10 +6074,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45610</v>
+        <v>46279</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6094,8 +6089,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>2.4</v>
+        <v>9.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6155,7 +6155,7 @@
         <v>44628</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE72"/>
+  <dimension ref="A1:AE71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 53870-2022</t>
+          <t>A 25961-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44880</v>
+        <v>46181</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1430,13 +1430,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>2.3</v>
+        <v>7.3</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1448,7 +1443,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1460,10 +1455,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1472,46 +1467,50 @@
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 25961-2026</t>
+          <t>A 53870-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1525,10 +1524,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46181</v>
+        <v>44880</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1540,8 +1539,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>7.3</v>
+        <v>2.3</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1553,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1565,10 +1569,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1577,43 +1581,39 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
-        <v/>
-      </c>
-      <c r="Z10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 6319-2022</t>
+          <t>A 72700-2021</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1858,10 +1858,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44600</v>
+        <v>44545</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1917,7 +1917,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 72700-2021</t>
+          <t>A 6319-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1931,10 +1931,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44545</v>
+        <v>44600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1990,7 +1990,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 54188-2021</t>
+          <t>A 9813-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44470</v>
+        <v>44620</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>6.5</v>
+        <v>4.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2063,7 +2063,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 9813-2022</t>
+          <t>A 19082-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44620</v>
+        <v>45048</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2092,8 +2092,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>4.3</v>
+        <v>6.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2136,7 +2141,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 41446-2023</t>
+          <t>A 40815-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2150,10 +2155,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45175</v>
+        <v>44824</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2165,13 +2170,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>8.4</v>
+        <v>15.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2214,7 +2214,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 30621-2023</t>
+          <t>A 55072-2021</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45112</v>
+        <v>44474</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2287,7 +2287,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 30623-2023</t>
+          <t>A 52795-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2301,10 +2301,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45112</v>
+        <v>45226</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2360,7 +2360,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 1906-2022</t>
+          <t>A 24023-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44575</v>
+        <v>45796</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2433,7 +2433,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 39717-2023</t>
+          <t>A 19420-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45167</v>
+        <v>45429</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2506,7 +2506,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 38308-2023</t>
+          <t>A 60754-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45161</v>
+        <v>45644</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2579,7 +2579,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16735-2023</t>
+          <t>A 52802-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45030</v>
+        <v>44875</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2608,8 +2608,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>8.699999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2652,7 +2657,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 19082-2023</t>
+          <t>A 6734-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2666,10 +2671,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45048</v>
+        <v>44602</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2681,13 +2686,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>6.5</v>
+        <v>32.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2730,7 +2730,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 55003-2022</t>
+          <t>A 30621-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44886</v>
+        <v>45112</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>6.6</v>
+        <v>3.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2803,7 +2803,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 59853-2022</t>
+          <t>A 30623-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44908</v>
+        <v>45112</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2876,7 +2876,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 8193-2023</t>
+          <t>A 59853-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2890,10 +2890,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44974</v>
+        <v>44908</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2905,13 +2905,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>10.5</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2954,7 +2949,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 8228-2023</t>
+          <t>A 10298-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2968,10 +2963,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44974</v>
+        <v>46076</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2984,7 +2979,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>13.9</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3027,7 +3022,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 47123-2024</t>
+          <t>A 3683-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3041,10 +3036,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45586</v>
+        <v>44950</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3056,8 +3051,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>5.3</v>
+        <v>6.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3100,7 +3100,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 40815-2022</t>
+          <t>A 23574-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44824</v>
+        <v>45077</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>15.9</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3173,7 +3173,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 31883-2022</t>
+          <t>A 41446-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44777</v>
+        <v>45175</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3202,8 +3202,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>8.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3246,7 +3251,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 51096-2024</t>
+          <t>A 30634-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3260,10 +3265,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45603</v>
+        <v>45112</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3276,7 +3281,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.3</v>
+        <v>6.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3319,7 +3324,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 23574-2023</t>
+          <t>A 26382-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3333,10 +3338,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45077</v>
+        <v>45092</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3348,8 +3353,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>20.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3392,7 +3402,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 55072-2021</t>
+          <t>A 61260-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3406,10 +3416,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44474</v>
+        <v>46000</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3422,7 +3432,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3465,7 +3475,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 26029-2022</t>
+          <t>A 1040-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3479,10 +3489,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44734</v>
+        <v>45666</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3494,13 +3504,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>9.699999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3543,7 +3548,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 59612-2021</t>
+          <t>A 33022-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3557,10 +3562,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44491</v>
+        <v>45840</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3573,7 +3578,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3616,7 +3621,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 26382-2023</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3630,10 +3635,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45092</v>
+        <v>44491</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3645,13 +3650,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>20.3</v>
+        <v>6.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3694,7 +3694,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 52802-2022</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3708,10 +3708,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44875</v>
+        <v>44491</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3723,13 +3723,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3772,7 +3767,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 10516-2022</t>
+          <t>A 11771-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3786,10 +3781,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44623</v>
+        <v>45727</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3802,7 +3797,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3845,7 +3840,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 10517-2022</t>
+          <t>A 52809-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3859,10 +3854,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44623</v>
+        <v>44875</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3874,8 +3869,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3918,7 +3918,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 16735-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44491</v>
+        <v>45030</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>6.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3991,7 +3991,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 52789-2024</t>
+          <t>A 1906-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45610</v>
+        <v>44575</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4081,7 +4081,7 @@
         <v>45166</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 40607-2024</t>
+          <t>A 59612-2021</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45556</v>
+        <v>44491</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 19420-2024</t>
+          <t>A 26274-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4224,10 +4224,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45429</v>
+        <v>46182</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4283,7 +4283,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 60754-2024</t>
+          <t>A 26257-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45644</v>
+        <v>46182</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4356,7 +4356,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 11771-2025</t>
+          <t>A 27399-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4366,14 +4366,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45727</v>
+        <v>46189</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 24023-2025</t>
+          <t>A 19266-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45796</v>
+        <v>45428</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4502,7 +4502,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 6734-2022</t>
+          <t>A 27400-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4512,14 +4512,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44602</v>
+        <v>46189</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>32.3</v>
+        <v>3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4575,7 +4575,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 59609-2021</t>
+          <t>A 10516-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4589,10 +4589,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44491</v>
+        <v>44623</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>12.7</v>
+        <v>2.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4648,7 +4648,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 30634-2023</t>
+          <t>A 10517-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4662,10 +4662,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45112</v>
+        <v>44623</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>6.2</v>
+        <v>1.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4721,7 +4721,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 1040-2025</t>
+          <t>A 39717-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45666</v>
+        <v>45167</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 19266-2024</t>
+          <t>A 35521-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45428</v>
+        <v>46262</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4823,8 +4823,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>3.8</v>
+        <v>6.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4867,7 +4872,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 52809-2022</t>
+          <t>A 35459-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4881,10 +4886,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44875</v>
+        <v>46262</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4896,13 +4901,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4945,7 +4945,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 52795-2023</t>
+          <t>A 55003-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4959,10 +4959,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45226</v>
+        <v>44886</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.7</v>
+        <v>6.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5018,7 +5018,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 3683-2023</t>
+          <t>A 37054-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5032,10 +5032,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44950</v>
+        <v>46273</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 59805-2024</t>
+          <t>A 37045-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5110,10 +5110,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45639</v>
+        <v>46273</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5125,8 +5125,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>3</v>
+        <v>7.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5169,7 +5174,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 59609-2021</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5186,7 +5191,7 @@
         <v>44491</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5199,7 +5204,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>6.8</v>
+        <v>12.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5242,7 +5247,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 10298-2026</t>
+          <t>A 37865-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5256,10 +5261,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46076</v>
+        <v>46279</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5271,8 +5276,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>9.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5315,7 +5325,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 33022-2025</t>
+          <t>A 40607-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5329,10 +5339,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45840</v>
+        <v>45556</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5345,7 +5355,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5388,7 +5398,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 61260-2025</t>
+          <t>A 59805-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5402,10 +5412,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46000</v>
+        <v>45639</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5418,7 +5428,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5461,7 +5471,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 26274-2026</t>
+          <t>A 8193-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5475,10 +5485,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46182</v>
+        <v>44974</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5490,8 +5500,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>10.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5534,7 +5549,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 26257-2026</t>
+          <t>A 8228-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5548,10 +5563,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46182</v>
+        <v>44974</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5564,7 +5579,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.3</v>
+        <v>13.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5607,7 +5622,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 27399-2026</t>
+          <t>A 51096-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5617,14 +5632,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46189</v>
+        <v>45603</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5637,7 +5652,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5680,7 +5695,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 27400-2026</t>
+          <t>A 47123-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5690,14 +5705,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46189</v>
+        <v>45586</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5710,7 +5725,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3</v>
+        <v>5.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5753,7 +5768,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 35521-2026</t>
+          <t>A 38308-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5767,10 +5782,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46262</v>
+        <v>45161</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5782,13 +5797,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>6.2</v>
+        <v>2.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5831,7 +5841,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 35459-2026</t>
+          <t>A 26029-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5845,10 +5855,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46262</v>
+        <v>44734</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5860,8 +5870,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>3.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5904,7 +5919,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 37045-2026</t>
+          <t>A 31883-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5918,10 +5933,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46273</v>
+        <v>44777</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5933,13 +5948,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>7.6</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5982,7 +5992,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 37054-2026</t>
+          <t>A 52789-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5996,10 +6006,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46273</v>
+        <v>45610</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6011,13 +6021,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>6.3</v>
+        <v>2.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6057,27 +6062,27 @@
       </c>
       <c r="V70" s="2" t="inlineStr"/>
     </row>
-    <row r="71" ht="15" customHeight="1">
+    <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 37865-2026</t>
+          <t>S 1310-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46279</v>
+        <v>44628</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6089,13 +6094,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>9.1</v>
+        <v>36.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6134,79 +6134,6 @@
         <v>0</v>
       </c>
       <c r="V71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>S 1310-2022</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Skogsgödsling</t>
-        </is>
-      </c>
-      <c r="D72" s="1" t="n">
-        <v>44628</v>
-      </c>
-      <c r="E72" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>KUNGSÖR</t>
-        </is>
-      </c>
-      <c r="I72" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" t="n">
-        <v>0</v>
-      </c>
-      <c r="N72" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" t="n">
-        <v>0</v>
-      </c>
-      <c r="T72" t="n">
-        <v>0</v>
-      </c>
-      <c r="U72" t="n">
-        <v>0</v>
-      </c>
-      <c r="V72" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 8475-2025</t>
+          <t>A 37056-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45709</v>
+        <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         <v>15</v>
       </c>
       <c r="U3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
@@ -793,46 +793,46 @@
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 8475-2025 artfynd.xlsx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 37056-2026 artfynd.xlsx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 8475-2025 karta.png", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 37056-2026 karta.png", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 8475-2025 georefererad karta.tif", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 37056-2026 georefererad karta.tif", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="Z3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 8475-2025 karta knärot.png", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 37056-2026 karta knärot.png", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 8475-2025 FSC-klagomål.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 37056-2026 FSC-klagomål.docx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 8475-2025 FSC-klagomål mail.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 37056-2026 FSC-klagomål mail.docx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 8475-2025 tillsynsbegäran.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 37056-2026 tillsynsbegäran.docx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 8475-2025 tillsynsbegäran mail.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 37056-2026 tillsynsbegäran mail.docx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/fåglar/A 8475-2025 prioriterade fågelarter.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/fåglar/A 37056-2026 prioriterade fågelarter.docx", "A 37056-2026")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 37056-2026</t>
+          <t>A 8475-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46273</v>
+        <v>45709</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>15</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
@@ -913,39 +913,39 @@
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 37056-2026 artfynd.xlsx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 8475-2025 artfynd.xlsx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 37056-2026 karta.png", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 8475-2025 karta.png", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 37056-2026 georefererad karta.tif", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 8475-2025 georefererad karta.tif", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="Z4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 37056-2026 karta knärot.png", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 8475-2025 karta knärot.png", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 37056-2026 FSC-klagomål.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 8475-2025 FSC-klagomål.docx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 37056-2026 FSC-klagomål mail.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 8475-2025 FSC-klagomål mail.docx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 37056-2026 tillsynsbegäran.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 8475-2025 tillsynsbegäran.docx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 37056-2026 tillsynsbegäran mail.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 8475-2025 tillsynsbegäran mail.docx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/fåglar/A 37056-2026 prioriterade fågelarter.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/fåglar/A 8475-2025 prioriterade fågelarter.docx", "A 8475-2025")</f>
         <v/>
       </c>
     </row>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25961-2026</t>
+          <t>A 53870-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46181</v>
+        <v>44880</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1430,8 +1430,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>7.3</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1443,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1455,10 +1460,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1467,50 +1472,46 @@
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
-        <v/>
-      </c>
-      <c r="Z9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 53870-2022</t>
+          <t>A 25961-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1524,10 +1525,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44880</v>
+        <v>46181</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1539,13 +1540,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>2.3</v>
+        <v>7.3</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1557,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1569,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1581,39 +1577,43 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
+        <v/>
+      </c>
+      <c r="Z10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44545</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44620</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 19082-2023</t>
+          <t>A 41446-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45048</v>
+        <v>45175</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>6.5</v>
+        <v>8.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2141,7 +2141,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 40815-2022</t>
+          <t>A 30621-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44824</v>
+        <v>45112</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>15.9</v>
+        <v>3.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2214,7 +2214,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 55072-2021</t>
+          <t>A 30623-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44474</v>
+        <v>45112</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2287,7 +2287,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 52795-2023</t>
+          <t>A 51096-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2301,10 +2301,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45226</v>
+        <v>45603</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2360,7 +2360,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 24023-2025</t>
+          <t>A 52789-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45796</v>
+        <v>45610</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2433,7 +2433,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 19420-2024</t>
+          <t>A 40607-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45429</v>
+        <v>45556</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2506,7 +2506,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 60754-2024</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45644</v>
+        <v>44491</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.4</v>
+        <v>6.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2579,7 +2579,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 52802-2022</t>
+          <t>A 11771-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44875</v>
+        <v>45727</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2608,13 +2608,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>5.8</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2657,7 +2652,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 6734-2022</t>
+          <t>A 19420-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2671,10 +2666,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44602</v>
+        <v>45429</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2687,7 +2682,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>32.3</v>
+        <v>3.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2730,7 +2725,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 30621-2023</t>
+          <t>A 60754-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2744,10 +2739,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45112</v>
+        <v>45644</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2760,7 +2755,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2803,7 +2798,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 30623-2023</t>
+          <t>A 24023-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2817,10 +2812,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45112</v>
+        <v>45796</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2833,7 +2828,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2876,7 +2871,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 59853-2022</t>
+          <t>A 59805-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2890,10 +2885,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44908</v>
+        <v>45639</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2906,7 +2901,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2966,7 +2961,7 @@
         <v>46076</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3022,7 +3017,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 3683-2023</t>
+          <t>A 39717-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3036,10 +3031,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44950</v>
+        <v>45167</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3051,13 +3046,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>6.3</v>
+        <v>2.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3100,7 +3090,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 23574-2023</t>
+          <t>A 38308-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3114,10 +3104,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45077</v>
+        <v>45161</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3130,7 +3120,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3173,7 +3163,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 41446-2023</t>
+          <t>A 55003-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3187,10 +3177,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45175</v>
+        <v>44886</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3202,13 +3192,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3251,7 +3236,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 30634-2023</t>
+          <t>A 47123-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3265,10 +3250,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45112</v>
+        <v>45586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3281,7 +3266,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3324,7 +3309,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 26382-2023</t>
+          <t>A 40815-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3338,10 +3323,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45092</v>
+        <v>44824</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3353,13 +3338,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>20.3</v>
+        <v>15.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3402,7 +3382,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 61260-2025</t>
+          <t>A 1040-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3416,10 +3396,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46000</v>
+        <v>45666</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3432,7 +3412,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.4</v>
+        <v>1.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3475,7 +3455,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 1040-2025</t>
+          <t>A 55072-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3489,10 +3469,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45666</v>
+        <v>44474</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3505,7 +3485,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3548,7 +3528,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33022-2025</t>
+          <t>A 10516-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3562,10 +3542,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45840</v>
+        <v>44623</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3578,7 +3558,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3621,7 +3601,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 10517-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3635,10 +3615,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44491</v>
+        <v>44623</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3651,7 +3631,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6.8</v>
+        <v>1.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3694,7 +3674,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 33022-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3708,10 +3688,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44491</v>
+        <v>45840</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3724,7 +3704,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6.8</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3767,7 +3747,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 11771-2025</t>
+          <t>A 61260-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3781,10 +3761,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45727</v>
+        <v>46000</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3797,7 +3777,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3840,7 +3820,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 52809-2022</t>
+          <t>A 6734-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3854,10 +3834,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44875</v>
+        <v>44602</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3869,13 +3849,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>2.5</v>
+        <v>32.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3918,7 +3893,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 16735-2023</t>
+          <t>A 30634-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3932,10 +3907,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45030</v>
+        <v>45112</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3948,7 +3923,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>8.699999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3991,7 +3966,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 1906-2022</t>
+          <t>A 52795-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4005,10 +3980,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44575</v>
+        <v>45226</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4021,7 +3996,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4064,7 +4039,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 39269-2023</t>
+          <t>A 26274-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4078,10 +4053,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45166</v>
+        <v>46182</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4094,7 +4069,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4137,7 +4112,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 59612-2021</t>
+          <t>A 26257-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4151,10 +4126,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44491</v>
+        <v>46182</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4167,7 +4142,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4210,7 +4185,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 26274-2026</t>
+          <t>A 27399-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4220,14 +4195,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46182</v>
+        <v>46189</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4240,7 +4215,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4283,7 +4258,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 26257-2026</t>
+          <t>A 27400-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4293,14 +4268,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46182</v>
+        <v>46189</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4313,7 +4288,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4356,7 +4331,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 27399-2026</t>
+          <t>A 16735-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4366,14 +4341,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46189</v>
+        <v>45030</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4386,7 +4361,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4429,7 +4404,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 19266-2024</t>
+          <t>A 19082-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4443,10 +4418,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45428</v>
+        <v>45048</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4458,8 +4433,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>3.8</v>
+        <v>6.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4502,7 +4482,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 27400-2026</t>
+          <t>A 26029-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4512,14 +4492,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46189</v>
+        <v>44734</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4531,8 +4511,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4575,7 +4560,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 10516-2022</t>
+          <t>A 59612-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4589,10 +4574,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44623</v>
+        <v>44491</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4605,7 +4590,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4648,7 +4633,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 10517-2022</t>
+          <t>A 35521-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4662,10 +4647,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44623</v>
+        <v>46262</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4677,8 +4662,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>1.2</v>
+        <v>6.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4721,7 +4711,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 39717-2023</t>
+          <t>A 35459-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4735,10 +4725,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45167</v>
+        <v>46262</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4751,7 +4741,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4794,7 +4784,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 35521-2026</t>
+          <t>A 52802-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4808,10 +4798,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46262</v>
+        <v>44875</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4829,7 +4819,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4872,7 +4862,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 35459-2026</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4886,10 +4876,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46262</v>
+        <v>44491</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4902,7 +4892,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.5</v>
+        <v>6.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4945,7 +4935,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 55003-2022</t>
+          <t>A 37045-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4959,10 +4949,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44886</v>
+        <v>46273</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4974,8 +4964,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5035,7 +5030,7 @@
         <v>46273</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5096,7 +5091,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 37045-2026</t>
+          <t>A 37865-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5110,10 +5105,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46273</v>
+        <v>46279</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5131,7 +5126,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>7.6</v>
+        <v>9.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5174,7 +5169,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 59609-2021</t>
+          <t>A 39269-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5188,10 +5183,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44491</v>
+        <v>45166</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5204,7 +5199,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>12.7</v>
+        <v>3.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5247,7 +5242,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 37865-2026</t>
+          <t>A 59609-2021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5261,10 +5256,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46279</v>
+        <v>44491</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5276,13 +5271,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>9.1</v>
+        <v>12.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5325,7 +5315,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 40607-2024</t>
+          <t>A 19266-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5339,10 +5329,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45556</v>
+        <v>45428</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5355,7 +5345,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5398,7 +5388,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 59805-2024</t>
+          <t>A 52809-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5412,10 +5402,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45639</v>
+        <v>44875</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5427,8 +5417,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5471,7 +5466,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 8193-2023</t>
+          <t>A 3683-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5485,10 +5480,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44974</v>
+        <v>44950</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5506,7 +5501,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>10.5</v>
+        <v>6.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5549,7 +5544,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 8228-2023</t>
+          <t>A 1906-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5563,10 +5558,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44974</v>
+        <v>44575</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5579,7 +5574,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>13.9</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5622,7 +5617,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 51096-2024</t>
+          <t>A 59853-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5636,10 +5631,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45603</v>
+        <v>44908</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5652,7 +5647,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5695,7 +5690,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 47123-2024</t>
+          <t>A 8193-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5709,10 +5704,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45586</v>
+        <v>44974</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5724,8 +5719,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>5.3</v>
+        <v>10.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5768,7 +5768,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 38308-2023</t>
+          <t>A 8228-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5782,10 +5782,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45161</v>
+        <v>44974</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.9</v>
+        <v>13.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5841,7 +5841,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 26029-2022</t>
+          <t>A 31883-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5855,10 +5855,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44734</v>
+        <v>44777</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5870,13 +5870,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>9.699999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5919,7 +5914,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 31883-2022</t>
+          <t>A 23574-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5933,10 +5928,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44777</v>
+        <v>45077</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5949,7 +5944,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5992,7 +5987,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 52789-2024</t>
+          <t>A 26382-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6006,10 +6001,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45610</v>
+        <v>45092</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6021,8 +6016,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>2.4</v>
+        <v>20.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>44628</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>45709</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44880</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>46181</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44545</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44620</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>45175</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>45112</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>45112</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>45603</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>45610</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>45556</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>44491</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>45727</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         <v>45429</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>45644</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>45796</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>45639</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>46076</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>45167</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         <v>45161</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>44886</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>45586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>44824</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>45666</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>44474</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>44623</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>44623</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>45840</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>46000</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>44602</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>45112</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>45226</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>46182</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>46182</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>46189</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>46189</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>45030</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>45048</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>44734</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>44491</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>46262</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>46262</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         <v>44875</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>44491</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>46273</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>46273</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>46279</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>45166</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>44491</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>45428</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>44875</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
         <v>44950</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>44575</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>44908</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>44974</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v>44974</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>44777</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>45077</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6004,7 +6004,7 @@
         <v>45092</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>44628</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>45709</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44880</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>46181</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44545</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44620</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>45175</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>45112</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>45112</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>45603</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>45610</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>45556</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>44491</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>45727</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         <v>45429</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>45644</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>45796</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>45639</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>46076</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>45167</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         <v>45161</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>44886</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>45586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>44824</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>45666</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>44474</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>44623</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>44623</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>45840</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>46000</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>44602</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>45112</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>45226</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>46182</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>46182</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>46189</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>46189</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>45030</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>45048</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>44734</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>44491</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>46262</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>46262</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         <v>44875</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>44491</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>46273</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>46273</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>46279</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>45166</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>44491</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>45428</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>44875</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
         <v>44950</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>44575</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>44908</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>44974</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v>44974</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>44777</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>45077</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6004,7 +6004,7 @@
         <v>45092</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>44628</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE71"/>
+  <dimension ref="A1:AE70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 37056-2026</t>
+          <t>A 8475-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46273</v>
+        <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         <v>15</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
@@ -793,46 +793,46 @@
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 37056-2026 artfynd.xlsx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 8475-2025 artfynd.xlsx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 37056-2026 karta.png", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 8475-2025 karta.png", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 37056-2026 georefererad karta.tif", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 8475-2025 georefererad karta.tif", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="Z3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 37056-2026 karta knärot.png", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 8475-2025 karta knärot.png", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 37056-2026 FSC-klagomål.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 8475-2025 FSC-klagomål.docx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 37056-2026 FSC-klagomål mail.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 8475-2025 FSC-klagomål mail.docx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 37056-2026 tillsynsbegäran.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 8475-2025 tillsynsbegäran.docx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 37056-2026 tillsynsbegäran mail.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 8475-2025 tillsynsbegäran mail.docx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/fåglar/A 37056-2026 prioriterade fågelarter.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/fåglar/A 8475-2025 prioriterade fågelarter.docx", "A 8475-2025")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 8475-2025</t>
+          <t>A 37056-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45709</v>
+        <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>15</v>
       </c>
       <c r="U4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
@@ -913,39 +913,39 @@
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 8475-2025 artfynd.xlsx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 37056-2026 artfynd.xlsx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 8475-2025 karta.png", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 37056-2026 karta.png", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 8475-2025 georefererad karta.tif", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 37056-2026 georefererad karta.tif", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="Z4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 8475-2025 karta knärot.png", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 37056-2026 karta knärot.png", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 8475-2025 FSC-klagomål.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 37056-2026 FSC-klagomål.docx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 8475-2025 FSC-klagomål mail.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 37056-2026 FSC-klagomål mail.docx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 8475-2025 tillsynsbegäran.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 37056-2026 tillsynsbegäran.docx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 8475-2025 tillsynsbegäran mail.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 37056-2026 tillsynsbegäran mail.docx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/fåglar/A 8475-2025 prioriterade fågelarter.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/fåglar/A 37056-2026 prioriterade fågelarter.docx", "A 37056-2026")</f>
         <v/>
       </c>
     </row>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 53870-2022</t>
+          <t>A 25961-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44880</v>
+        <v>46181</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1430,13 +1430,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>2.3</v>
+        <v>7.3</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1448,7 +1443,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1460,10 +1455,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1472,46 +1467,50 @@
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 25961-2026</t>
+          <t>A 53870-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1525,10 +1524,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46181</v>
+        <v>44880</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1540,8 +1539,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>7.3</v>
+        <v>2.3</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1553,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1565,10 +1569,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1577,43 +1581,39 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
-        <v/>
-      </c>
-      <c r="Z10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44545</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44620</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 41446-2023</t>
+          <t>A 19082-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45175</v>
+        <v>45048</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>8.4</v>
+        <v>6.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2141,7 +2141,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 30621-2023</t>
+          <t>A 40815-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45112</v>
+        <v>44824</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.2</v>
+        <v>15.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2214,7 +2214,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 30623-2023</t>
+          <t>A 52795-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45112</v>
+        <v>45226</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2287,7 +2287,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 51096-2024</t>
+          <t>A 52802-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2301,10 +2301,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45603</v>
+        <v>44875</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2316,8 +2316,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>5.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2360,7 +2365,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 52789-2024</t>
+          <t>A 6734-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2374,10 +2379,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45610</v>
+        <v>44602</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2390,7 +2395,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.4</v>
+        <v>32.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2433,7 +2438,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 40607-2024</t>
+          <t>A 30621-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2447,10 +2452,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45556</v>
+        <v>45112</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2506,7 +2511,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 30623-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2520,10 +2525,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44491</v>
+        <v>45112</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2536,7 +2541,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>6.8</v>
+        <v>2.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2579,7 +2584,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 11771-2025</t>
+          <t>A 59853-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2593,10 +2598,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45727</v>
+        <v>44908</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2609,7 +2614,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2652,7 +2657,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 19420-2024</t>
+          <t>A 1040-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2666,10 +2671,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45429</v>
+        <v>45666</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2682,7 +2687,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2725,7 +2730,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 60754-2024</t>
+          <t>A 3683-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2739,10 +2744,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45644</v>
+        <v>44950</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2754,8 +2759,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>6.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2798,7 +2808,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 24023-2025</t>
+          <t>A 23574-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2812,10 +2822,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45796</v>
+        <v>45077</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2828,7 +2838,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2871,7 +2881,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 59805-2024</t>
+          <t>A 41446-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2885,10 +2895,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45639</v>
+        <v>45175</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2900,8 +2910,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>8.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2944,7 +2959,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 10298-2026</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2958,10 +2973,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46076</v>
+        <v>44491</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2974,7 +2989,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>6.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3017,7 +3032,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 39717-2023</t>
+          <t>A 30634-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3031,10 +3046,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45167</v>
+        <v>45112</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3047,7 +3062,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.3</v>
+        <v>6.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3090,7 +3105,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 38308-2023</t>
+          <t>A 26382-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3104,10 +3119,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45161</v>
+        <v>45092</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3119,8 +3134,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>2.9</v>
+        <v>20.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3163,7 +3183,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 55003-2022</t>
+          <t>A 10298-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3177,10 +3197,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44886</v>
+        <v>46076</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3193,7 +3213,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>6.6</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3236,7 +3256,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 47123-2024</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3250,10 +3270,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45586</v>
+        <v>44491</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3266,7 +3286,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3309,7 +3329,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 40815-2022</t>
+          <t>A 11771-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3323,10 +3343,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44824</v>
+        <v>45727</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3339,7 +3359,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>15.9</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3382,7 +3402,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 1040-2025</t>
+          <t>A 61260-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3396,10 +3416,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45666</v>
+        <v>46000</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3412,7 +3432,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3455,7 +3475,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 55072-2021</t>
+          <t>A 52809-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3469,10 +3489,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44474</v>
+        <v>44875</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3484,8 +3504,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3528,7 +3553,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 10516-2022</t>
+          <t>A 16735-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3542,10 +3567,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44623</v>
+        <v>45030</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3558,7 +3583,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3601,7 +3626,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 10517-2022</t>
+          <t>A 33022-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3615,10 +3640,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44623</v>
+        <v>45840</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3631,7 +3656,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3674,7 +3699,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 33022-2025</t>
+          <t>A 1906-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3688,10 +3713,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45840</v>
+        <v>44575</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3704,7 +3729,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3747,7 +3772,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 61260-2025</t>
+          <t>A 39269-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3761,10 +3786,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46000</v>
+        <v>45166</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3777,7 +3802,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3820,7 +3845,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 6734-2022</t>
+          <t>A 59612-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3834,10 +3859,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44602</v>
+        <v>44491</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3850,7 +3875,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>32.3</v>
+        <v>3.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3893,7 +3918,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 30634-2023</t>
+          <t>A 19266-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3907,10 +3932,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45112</v>
+        <v>45428</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3923,7 +3948,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>6.2</v>
+        <v>3.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3966,7 +3991,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 52795-2023</t>
+          <t>A 10516-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3980,10 +4005,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45226</v>
+        <v>44623</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3996,7 +4021,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4039,7 +4064,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 26274-2026</t>
+          <t>A 10517-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4053,10 +4078,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46182</v>
+        <v>44623</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4069,7 +4094,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4112,7 +4137,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 26257-2026</t>
+          <t>A 39717-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4126,10 +4151,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46182</v>
+        <v>45167</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4142,7 +4167,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4185,7 +4210,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 27399-2026</t>
+          <t>A 26274-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4195,14 +4220,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46189</v>
+        <v>46182</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4215,7 +4240,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4258,7 +4283,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 27400-2026</t>
+          <t>A 26257-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4268,14 +4293,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46189</v>
+        <v>46182</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4288,7 +4313,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4331,7 +4356,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 16735-2023</t>
+          <t>A 27399-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4341,14 +4366,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45030</v>
+        <v>46189</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4361,7 +4386,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>8.699999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4404,7 +4429,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 19082-2023</t>
+          <t>A 27400-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4414,14 +4439,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45048</v>
+        <v>46189</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4433,13 +4458,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>6.5</v>
+        <v>3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4482,7 +4502,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26029-2022</t>
+          <t>A 55003-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4496,10 +4516,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44734</v>
+        <v>44886</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4511,13 +4531,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>9.699999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4560,7 +4575,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 59612-2021</t>
+          <t>A 59609-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4577,7 +4592,7 @@
         <v>44491</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4590,7 +4605,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.2</v>
+        <v>12.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4650,7 +4665,7 @@
         <v>46262</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4728,7 +4743,7 @@
         <v>46262</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4784,7 +4799,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 52802-2022</t>
+          <t>A 37054-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4798,10 +4813,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44875</v>
+        <v>46273</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4819,7 +4834,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4862,7 +4877,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 37045-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4876,10 +4891,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44491</v>
+        <v>46273</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4891,8 +4906,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4935,7 +4955,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 37045-2026</t>
+          <t>A 40607-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4949,10 +4969,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46273</v>
+        <v>45556</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4964,13 +4984,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>7.6</v>
+        <v>3.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5013,7 +5028,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 37054-2026</t>
+          <t>A 59805-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5027,10 +5042,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46273</v>
+        <v>45639</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5042,13 +5057,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>6.3</v>
+        <v>3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5108,7 +5118,7 @@
         <v>46279</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5169,7 +5179,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 39269-2023</t>
+          <t>A 8193-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5183,10 +5193,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45166</v>
+        <v>44974</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5198,8 +5208,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>3.3</v>
+        <v>10.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5242,7 +5257,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 59609-2021</t>
+          <t>A 8228-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5256,10 +5271,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44491</v>
+        <v>44974</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5272,7 +5287,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>12.7</v>
+        <v>13.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5315,7 +5330,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 19266-2024</t>
+          <t>A 51096-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5329,10 +5344,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45428</v>
+        <v>45603</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5345,7 +5360,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5388,7 +5403,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 52809-2022</t>
+          <t>A 47123-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5402,10 +5417,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44875</v>
+        <v>45586</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5417,13 +5432,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>2.5</v>
+        <v>5.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5466,7 +5476,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 3683-2023</t>
+          <t>A 38308-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5480,10 +5490,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44950</v>
+        <v>45161</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5495,13 +5505,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>6.3</v>
+        <v>2.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5544,7 +5549,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 1906-2022</t>
+          <t>A 26029-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5558,10 +5563,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44575</v>
+        <v>44734</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5573,8 +5578,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5617,7 +5627,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 59853-2022</t>
+          <t>A 31883-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5631,10 +5641,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44908</v>
+        <v>44777</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5647,7 +5657,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5690,7 +5700,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 8193-2023</t>
+          <t>A 52789-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5704,10 +5714,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44974</v>
+        <v>45610</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5719,13 +5729,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>10.5</v>
+        <v>2.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5768,7 +5773,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 8228-2023</t>
+          <t>A 24023-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5782,10 +5787,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44974</v>
+        <v>45796</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5798,7 +5803,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>13.9</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5841,7 +5846,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 31883-2022</t>
+          <t>A 19420-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5855,10 +5860,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44777</v>
+        <v>45429</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5871,7 +5876,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5914,7 +5919,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 23574-2023</t>
+          <t>A 60754-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5928,10 +5933,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45077</v>
+        <v>45644</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5944,7 +5949,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5984,27 +5989,27 @@
       </c>
       <c r="V69" s="2" t="inlineStr"/>
     </row>
-    <row r="70" ht="15" customHeight="1">
+    <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 26382-2023</t>
+          <t>S 1310-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45092</v>
+        <v>44628</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6016,13 +6021,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>20.3</v>
+        <v>36.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6061,79 +6061,6 @@
         <v>0</v>
       </c>
       <c r="V70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>S 1310-2022</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Skogsgödsling</t>
-        </is>
-      </c>
-      <c r="D71" s="1" t="n">
-        <v>44628</v>
-      </c>
-      <c r="E71" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>KUNGSÖR</t>
-        </is>
-      </c>
-      <c r="I71" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="J71" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
-      <c r="R71" t="n">
-        <v>0</v>
-      </c>
-      <c r="S71" t="n">
-        <v>0</v>
-      </c>
-      <c r="T71" t="n">
-        <v>0</v>
-      </c>
-      <c r="U71" t="n">
-        <v>0</v>
-      </c>
-      <c r="V71" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 8475-2025</t>
+          <t>A 37056-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45709</v>
+        <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         <v>15</v>
       </c>
       <c r="U3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
@@ -793,46 +793,46 @@
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 8475-2025 artfynd.xlsx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 37056-2026 artfynd.xlsx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 8475-2025 karta.png", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 37056-2026 karta.png", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 8475-2025 georefererad karta.tif", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 37056-2026 georefererad karta.tif", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="Z3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 8475-2025 karta knärot.png", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 37056-2026 karta knärot.png", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 8475-2025 FSC-klagomål.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 37056-2026 FSC-klagomål.docx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 8475-2025 FSC-klagomål mail.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 37056-2026 FSC-klagomål mail.docx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 8475-2025 tillsynsbegäran.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 37056-2026 tillsynsbegäran.docx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 8475-2025 tillsynsbegäran mail.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 37056-2026 tillsynsbegäran mail.docx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/fåglar/A 8475-2025 prioriterade fågelarter.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/fåglar/A 37056-2026 prioriterade fågelarter.docx", "A 37056-2026")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 37056-2026</t>
+          <t>A 8475-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46273</v>
+        <v>45709</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>15</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
@@ -913,39 +913,39 @@
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 37056-2026 artfynd.xlsx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 8475-2025 artfynd.xlsx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 37056-2026 karta.png", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 8475-2025 karta.png", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 37056-2026 georefererad karta.tif", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 8475-2025 georefererad karta.tif", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="Z4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 37056-2026 karta knärot.png", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 8475-2025 karta knärot.png", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 37056-2026 FSC-klagomål.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 8475-2025 FSC-klagomål.docx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 37056-2026 FSC-klagomål mail.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 8475-2025 FSC-klagomål mail.docx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 37056-2026 tillsynsbegäran.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 8475-2025 tillsynsbegäran.docx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 37056-2026 tillsynsbegäran mail.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 8475-2025 tillsynsbegäran mail.docx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/fåglar/A 37056-2026 prioriterade fågelarter.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/fåglar/A 8475-2025 prioriterade fågelarter.docx", "A 8475-2025")</f>
         <v/>
       </c>
     </row>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25961-2026</t>
+          <t>A 53870-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46181</v>
+        <v>44880</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1430,8 +1430,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>7.3</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1443,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1455,10 +1460,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1467,50 +1472,46 @@
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
-        <v/>
-      </c>
-      <c r="Z9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 53870-2022</t>
+          <t>A 25961-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1524,10 +1525,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44880</v>
+        <v>46181</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1539,13 +1540,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>2.3</v>
+        <v>7.3</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1557,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1569,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1581,39 +1577,43 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
+        <v/>
+      </c>
+      <c r="Z10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44545</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44620</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 19082-2023</t>
+          <t>A 41446-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45048</v>
+        <v>45175</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>6.5</v>
+        <v>8.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2141,7 +2141,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 40815-2022</t>
+          <t>A 30621-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44824</v>
+        <v>45112</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>15.9</v>
+        <v>3.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2214,7 +2214,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 52795-2023</t>
+          <t>A 30623-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45226</v>
+        <v>45112</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2287,7 +2287,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 52802-2022</t>
+          <t>A 51096-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2301,10 +2301,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44875</v>
+        <v>45603</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2316,13 +2316,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>5.8</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2365,7 +2360,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 6734-2022</t>
+          <t>A 40607-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2379,10 +2374,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44602</v>
+        <v>45556</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2395,7 +2390,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>32.3</v>
+        <v>3.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2438,7 +2433,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 30621-2023</t>
+          <t>A 11771-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2452,10 +2447,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45112</v>
+        <v>45727</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2468,7 +2463,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2511,7 +2506,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 30623-2023</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2525,10 +2520,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45112</v>
+        <v>44491</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2541,7 +2536,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.6</v>
+        <v>6.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2584,7 +2579,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 59853-2022</t>
+          <t>A 59805-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2598,10 +2593,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44908</v>
+        <v>45639</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2614,7 +2609,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2674,7 +2669,7 @@
         <v>45666</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2730,7 +2725,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 3683-2023</t>
+          <t>A 10298-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2744,10 +2739,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44950</v>
+        <v>46076</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2759,13 +2754,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>6.3</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2808,7 +2798,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 23574-2023</t>
+          <t>A 39717-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2822,10 +2812,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45077</v>
+        <v>45167</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2838,7 +2828,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2881,7 +2871,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 41446-2023</t>
+          <t>A 38308-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2895,10 +2885,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45175</v>
+        <v>45161</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2910,13 +2900,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>8.4</v>
+        <v>2.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2959,7 +2944,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 55003-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2973,10 +2958,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44491</v>
+        <v>44886</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2989,7 +2974,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3032,7 +3017,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 30634-2023</t>
+          <t>A 47123-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3046,10 +3031,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45112</v>
+        <v>45586</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3062,7 +3047,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3105,7 +3090,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 26382-2023</t>
+          <t>A 40815-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3119,10 +3104,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45092</v>
+        <v>44824</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3134,13 +3119,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>20.3</v>
+        <v>15.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3183,7 +3163,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 10298-2026</t>
+          <t>A 33022-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3197,10 +3177,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46076</v>
+        <v>45840</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3256,7 +3236,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 61260-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3270,10 +3250,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44491</v>
+        <v>46000</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3286,7 +3266,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3329,7 +3309,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 11771-2025</t>
+          <t>A 10516-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3343,10 +3323,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45727</v>
+        <v>44623</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3359,7 +3339,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3402,7 +3382,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 61260-2025</t>
+          <t>A 10517-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3416,10 +3396,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46000</v>
+        <v>44623</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3432,7 +3412,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.4</v>
+        <v>1.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3475,7 +3455,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 52809-2022</t>
+          <t>A 26274-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3489,10 +3469,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44875</v>
+        <v>46182</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3504,13 +3484,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3553,7 +3528,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 16735-2023</t>
+          <t>A 26257-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3567,10 +3542,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45030</v>
+        <v>46182</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3583,7 +3558,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>8.699999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3626,7 +3601,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 33022-2025</t>
+          <t>A 27399-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3636,14 +3611,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45840</v>
+        <v>46189</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3656,7 +3631,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3699,7 +3674,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 1906-2022</t>
+          <t>A 27400-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3709,14 +3684,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44575</v>
+        <v>46189</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3729,7 +3704,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3772,7 +3747,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 39269-2023</t>
+          <t>A 6734-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3786,10 +3761,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45166</v>
+        <v>44602</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3802,7 +3777,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.3</v>
+        <v>32.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3845,7 +3820,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 59612-2021</t>
+          <t>A 30634-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3859,10 +3834,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44491</v>
+        <v>45112</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3875,7 +3850,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3918,7 +3893,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 19266-2024</t>
+          <t>A 52795-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3932,10 +3907,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45428</v>
+        <v>45226</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3948,7 +3923,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3991,7 +3966,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 10516-2022</t>
+          <t>A 35521-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4005,10 +3980,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44623</v>
+        <v>46262</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4020,8 +3995,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>2.1</v>
+        <v>6.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4064,7 +4044,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 10517-2022</t>
+          <t>A 35459-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4078,10 +4058,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44623</v>
+        <v>46262</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4094,7 +4074,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4137,7 +4117,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 39717-2023</t>
+          <t>A 16735-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4151,10 +4131,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45167</v>
+        <v>45030</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4167,7 +4147,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4210,7 +4190,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 26274-2026</t>
+          <t>A 19082-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4224,10 +4204,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46182</v>
+        <v>45048</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4239,8 +4219,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>6.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4283,7 +4268,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 26257-2026</t>
+          <t>A 37045-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4297,10 +4282,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46182</v>
+        <v>46273</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4312,8 +4297,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>1.3</v>
+        <v>7.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4356,7 +4346,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 27399-2026</t>
+          <t>A 37054-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4366,14 +4356,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46189</v>
+        <v>46273</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4385,8 +4375,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>6.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4429,7 +4424,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 27400-2026</t>
+          <t>A 37865-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4439,14 +4434,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46189</v>
+        <v>46279</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4458,8 +4453,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>3</v>
+        <v>9.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4502,7 +4502,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 55003-2022</t>
+          <t>A 26029-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4516,10 +4516,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44886</v>
+        <v>44734</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4531,8 +4531,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>6.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4575,7 +4580,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 59609-2021</t>
+          <t>A 59612-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4592,7 +4597,7 @@
         <v>44491</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4605,7 +4610,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>12.7</v>
+        <v>3.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4648,7 +4653,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 35521-2026</t>
+          <t>A 52802-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4662,10 +4667,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46262</v>
+        <v>44875</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4683,7 +4688,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4726,7 +4731,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 35459-2026</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4740,10 +4745,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46262</v>
+        <v>44491</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4756,7 +4761,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.5</v>
+        <v>6.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4799,7 +4804,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 37054-2026</t>
+          <t>A 39269-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4813,10 +4818,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46273</v>
+        <v>45166</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4828,13 +4833,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>6.3</v>
+        <v>3.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4877,7 +4877,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 37045-2026</t>
+          <t>A 59609-2021</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4891,10 +4891,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46273</v>
+        <v>44491</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4906,13 +4906,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>7.6</v>
+        <v>12.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4955,7 +4950,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 40607-2024</t>
+          <t>A 19266-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4969,10 +4964,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45556</v>
+        <v>45428</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4985,7 +4980,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5028,7 +5023,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 59805-2024</t>
+          <t>A 52809-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5042,10 +5037,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45639</v>
+        <v>44875</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5057,8 +5052,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5101,7 +5101,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 37865-2026</t>
+          <t>A 3683-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5115,10 +5115,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46279</v>
+        <v>44950</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>9.1</v>
+        <v>6.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5179,7 +5179,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 8193-2023</t>
+          <t>A 1906-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44974</v>
+        <v>44575</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5208,13 +5208,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>10.5</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5257,7 +5252,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 8228-2023</t>
+          <t>A 59853-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5271,10 +5266,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44974</v>
+        <v>44908</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5287,7 +5282,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>13.9</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5330,7 +5325,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 51096-2024</t>
+          <t>A 8193-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5344,10 +5339,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45603</v>
+        <v>44974</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5359,8 +5354,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>1.3</v>
+        <v>10.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5403,7 +5403,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 47123-2024</t>
+          <t>A 8228-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5417,10 +5417,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45586</v>
+        <v>44974</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.3</v>
+        <v>13.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5476,7 +5476,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 38308-2023</t>
+          <t>A 31883-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5490,10 +5490,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45161</v>
+        <v>44777</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5549,7 +5549,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 26029-2022</t>
+          <t>A 23574-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5563,10 +5563,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44734</v>
+        <v>45077</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5578,13 +5578,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>9.699999999999999</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5627,7 +5622,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 31883-2022</t>
+          <t>A 26382-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5641,10 +5636,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44777</v>
+        <v>45092</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5656,8 +5651,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>1.5</v>
+        <v>20.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5717,7 +5717,7 @@
         <v>45610</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 24023-2025</t>
+          <t>A 19420-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45796</v>
+        <v>45429</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5846,7 +5846,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 19420-2024</t>
+          <t>A 60754-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5860,10 +5860,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45429</v>
+        <v>45644</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5919,7 +5919,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 60754-2024</t>
+          <t>A 24023-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5933,10 +5933,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45644</v>
+        <v>45796</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6009,7 +6009,7 @@
         <v>44628</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 37056-2026</t>
+          <t>A 8475-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46273</v>
+        <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         <v>15</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
@@ -793,46 +793,46 @@
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 37056-2026 artfynd.xlsx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 8475-2025 artfynd.xlsx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 37056-2026 karta.png", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 8475-2025 karta.png", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 37056-2026 georefererad karta.tif", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 8475-2025 georefererad karta.tif", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="Z3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 37056-2026 karta knärot.png", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 8475-2025 karta knärot.png", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 37056-2026 FSC-klagomål.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 8475-2025 FSC-klagomål.docx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 37056-2026 FSC-klagomål mail.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 8475-2025 FSC-klagomål mail.docx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 37056-2026 tillsynsbegäran.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 8475-2025 tillsynsbegäran.docx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 37056-2026 tillsynsbegäran mail.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 8475-2025 tillsynsbegäran mail.docx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/fåglar/A 37056-2026 prioriterade fågelarter.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/fåglar/A 8475-2025 prioriterade fågelarter.docx", "A 8475-2025")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 8475-2025</t>
+          <t>A 37056-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45709</v>
+        <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>15</v>
       </c>
       <c r="U4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
@@ -913,39 +913,39 @@
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 8475-2025 artfynd.xlsx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 37056-2026 artfynd.xlsx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 8475-2025 karta.png", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 37056-2026 karta.png", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 8475-2025 georefererad karta.tif", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 37056-2026 georefererad karta.tif", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="Z4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 8475-2025 karta knärot.png", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 37056-2026 karta knärot.png", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 8475-2025 FSC-klagomål.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 37056-2026 FSC-klagomål.docx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 8475-2025 FSC-klagomål mail.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 37056-2026 FSC-klagomål mail.docx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 8475-2025 tillsynsbegäran.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 37056-2026 tillsynsbegäran.docx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 8475-2025 tillsynsbegäran mail.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 37056-2026 tillsynsbegäran mail.docx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/fåglar/A 8475-2025 prioriterade fågelarter.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/fåglar/A 37056-2026 prioriterade fågelarter.docx", "A 37056-2026")</f>
         <v/>
       </c>
     </row>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 53870-2022</t>
+          <t>A 25961-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44880</v>
+        <v>46181</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1430,13 +1430,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>2.3</v>
+        <v>7.3</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1448,7 +1443,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1460,10 +1455,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1472,46 +1467,50 @@
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 25961-2026</t>
+          <t>A 53870-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1525,10 +1524,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46181</v>
+        <v>44880</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1540,8 +1539,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>7.3</v>
+        <v>2.3</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1553,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1565,10 +1569,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1577,43 +1581,39 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
-        <v/>
-      </c>
-      <c r="Z10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44545</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44620</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 41446-2023</t>
+          <t>A 19082-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45175</v>
+        <v>45048</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>8.4</v>
+        <v>6.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2141,7 +2141,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 30621-2023</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45112</v>
+        <v>44491</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.2</v>
+        <v>6.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2214,7 +2214,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 30623-2023</t>
+          <t>A 52789-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45112</v>
+        <v>45610</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2287,7 +2287,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 51096-2024</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2301,10 +2301,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45603</v>
+        <v>44491</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>6.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2360,7 +2360,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 40607-2024</t>
+          <t>A 40815-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45556</v>
+        <v>44824</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.2</v>
+        <v>15.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2433,7 +2433,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 11771-2025</t>
+          <t>A 24023-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45727</v>
+        <v>45796</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2506,7 +2506,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 19420-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44491</v>
+        <v>45429</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>6.8</v>
+        <v>3.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2579,7 +2579,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 59805-2024</t>
+          <t>A 60754-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45639</v>
+        <v>45644</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2652,7 +2652,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 1040-2025</t>
+          <t>A 11771-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45666</v>
+        <v>45727</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2725,7 +2725,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 10298-2026</t>
+          <t>A 52795-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46076</v>
+        <v>45226</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2798,7 +2798,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 39717-2023</t>
+          <t>A 52809-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2812,10 +2812,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45167</v>
+        <v>44875</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2827,8 +2827,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2871,7 +2876,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 38308-2023</t>
+          <t>A 16735-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2885,10 +2890,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45161</v>
+        <v>45030</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2901,7 +2906,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2944,7 +2949,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 55003-2022</t>
+          <t>A 1040-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2958,10 +2963,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44886</v>
+        <v>45666</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2974,7 +2979,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>6.6</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3017,7 +3022,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 47123-2024</t>
+          <t>A 1906-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3031,10 +3036,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45586</v>
+        <v>44575</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3047,7 +3052,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>5.3</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3090,7 +3095,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 40815-2022</t>
+          <t>A 52802-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3104,10 +3109,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44824</v>
+        <v>44875</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3119,8 +3124,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>15.9</v>
+        <v>5.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3163,7 +3173,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33022-2025</t>
+          <t>A 6734-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3177,10 +3187,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45840</v>
+        <v>44602</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3193,7 +3203,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>32.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3236,7 +3246,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 61260-2025</t>
+          <t>A 30621-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3250,10 +3260,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46000</v>
+        <v>45112</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3266,7 +3276,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3309,7 +3319,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 10516-2022</t>
+          <t>A 30623-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3323,10 +3333,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44623</v>
+        <v>45112</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3339,7 +3349,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3382,7 +3392,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10517-2022</t>
+          <t>A 39269-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3396,10 +3406,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44623</v>
+        <v>45166</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3412,7 +3422,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3455,7 +3465,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 26274-2026</t>
+          <t>A 59853-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3469,10 +3479,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46182</v>
+        <v>44908</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3528,7 +3538,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 26257-2026</t>
+          <t>A 59612-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3542,10 +3552,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46182</v>
+        <v>44491</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3558,7 +3568,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3601,7 +3611,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 27399-2026</t>
+          <t>A 19266-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3611,14 +3621,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46189</v>
+        <v>45428</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3631,7 +3641,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3674,7 +3684,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 27400-2026</t>
+          <t>A 3683-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3684,14 +3694,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46189</v>
+        <v>44950</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3703,8 +3713,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>3</v>
+        <v>6.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3747,7 +3762,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 6734-2022</t>
+          <t>A 33022-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3761,10 +3776,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44602</v>
+        <v>45840</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3777,7 +3792,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>32.3</v>
+        <v>1.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3820,7 +3835,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 30634-2023</t>
+          <t>A 23574-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3834,10 +3849,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45112</v>
+        <v>45077</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3850,7 +3865,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>6.2</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3893,7 +3908,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 52795-2023</t>
+          <t>A 10516-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3907,10 +3922,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45226</v>
+        <v>44623</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3923,7 +3938,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3966,7 +3981,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 35521-2026</t>
+          <t>A 10517-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3980,10 +3995,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46262</v>
+        <v>44623</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3995,13 +4010,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>6.2</v>
+        <v>1.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4044,7 +4054,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 35459-2026</t>
+          <t>A 39717-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4058,10 +4068,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46262</v>
+        <v>45167</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4074,7 +4084,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4117,7 +4127,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 16735-2023</t>
+          <t>A 41446-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4131,10 +4141,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45030</v>
+        <v>45175</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4146,8 +4156,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4190,7 +4205,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 19082-2023</t>
+          <t>A 30634-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4204,10 +4219,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45048</v>
+        <v>45112</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4219,13 +4234,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4268,7 +4278,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 37045-2026</t>
+          <t>A 26382-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4282,10 +4292,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46273</v>
+        <v>45092</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4303,7 +4313,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>7.6</v>
+        <v>20.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4346,7 +4356,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 37054-2026</t>
+          <t>A 55003-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4360,10 +4370,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46273</v>
+        <v>44886</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4375,13 +4385,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4424,7 +4429,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 37865-2026</t>
+          <t>A 26274-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4438,10 +4443,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46279</v>
+        <v>46182</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4453,13 +4458,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>9.1</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4502,7 +4502,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26029-2022</t>
+          <t>A 26257-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4516,10 +4516,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44734</v>
+        <v>46182</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4531,13 +4531,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>9.699999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4580,7 +4575,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 59612-2021</t>
+          <t>A 27399-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4590,14 +4585,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44491</v>
+        <v>46189</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4610,7 +4605,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4653,7 +4648,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 52802-2022</t>
+          <t>A 27400-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4663,14 +4658,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44875</v>
+        <v>46189</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4682,13 +4677,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>5.8</v>
+        <v>3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4731,7 +4721,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 59609-2021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4748,7 +4738,7 @@
         <v>44491</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4761,7 +4751,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>6.8</v>
+        <v>12.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4804,7 +4794,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 39269-2023</t>
+          <t>A 10298-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4818,10 +4808,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45166</v>
+        <v>46076</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4834,7 +4824,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4877,7 +4867,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 59609-2021</t>
+          <t>A 40607-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4891,10 +4881,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44491</v>
+        <v>45556</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4907,7 +4897,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>12.7</v>
+        <v>3.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4950,7 +4940,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 19266-2024</t>
+          <t>A 59805-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4964,10 +4954,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45428</v>
+        <v>45639</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4980,7 +4970,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5023,7 +5013,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 52809-2022</t>
+          <t>A 8193-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5037,10 +5027,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44875</v>
+        <v>44974</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5058,7 +5048,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.5</v>
+        <v>10.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5101,7 +5091,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 3683-2023</t>
+          <t>A 8228-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5115,10 +5105,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44950</v>
+        <v>44974</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5130,13 +5120,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>6.3</v>
+        <v>13.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5179,7 +5164,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 1906-2022</t>
+          <t>A 51096-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5193,10 +5178,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44575</v>
+        <v>45603</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5209,7 +5194,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5252,7 +5237,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 59853-2022</t>
+          <t>A 47123-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5266,10 +5251,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44908</v>
+        <v>45586</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5282,7 +5267,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5325,7 +5310,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 8193-2023</t>
+          <t>A 38308-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5339,10 +5324,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44974</v>
+        <v>45161</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5354,13 +5339,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>10.5</v>
+        <v>2.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5403,7 +5383,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 8228-2023</t>
+          <t>A 35521-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5417,10 +5397,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44974</v>
+        <v>46262</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5432,8 +5412,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>13.9</v>
+        <v>6.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5476,7 +5461,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 31883-2022</t>
+          <t>A 35459-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5490,10 +5475,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44777</v>
+        <v>46262</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5506,7 +5491,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5549,7 +5534,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 23574-2023</t>
+          <t>A 61260-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5563,10 +5548,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45077</v>
+        <v>46000</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5579,7 +5564,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5622,7 +5607,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 26382-2023</t>
+          <t>A 26029-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5636,10 +5621,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45092</v>
+        <v>44734</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5657,7 +5642,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>20.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5700,7 +5685,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 52789-2024</t>
+          <t>A 31883-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5714,10 +5699,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45610</v>
+        <v>44777</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5730,7 +5715,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5773,7 +5758,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 19420-2024</t>
+          <t>A 37054-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5787,10 +5772,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45429</v>
+        <v>46273</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5802,8 +5787,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>3.8</v>
+        <v>6.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5846,7 +5836,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 60754-2024</t>
+          <t>A 37045-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5860,10 +5850,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45644</v>
+        <v>46273</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5875,8 +5865,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5919,7 +5914,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 24023-2025</t>
+          <t>A 37865-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5933,10 +5928,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45796</v>
+        <v>46279</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5948,8 +5943,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>9.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6009,7 +6009,7 @@
         <v>44628</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25961-2026</t>
+          <t>A 53870-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46181</v>
+        <v>44880</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1430,8 +1430,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>7.3</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1443,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1455,10 +1460,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1467,50 +1472,46 @@
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
-        <v/>
-      </c>
-      <c r="Z9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 53870-2022</t>
+          <t>A 25961-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1524,10 +1525,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44880</v>
+        <v>46181</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1539,13 +1540,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>2.3</v>
+        <v>7.3</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1557,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1569,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1581,39 +1577,43 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
+        <v/>
+      </c>
+      <c r="Z10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44545</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44620</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 19082-2023</t>
+          <t>A 41446-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45048</v>
+        <v>45175</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>6.5</v>
+        <v>8.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2141,7 +2141,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 30621-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44491</v>
+        <v>45112</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>6.8</v>
+        <v>3.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2214,7 +2214,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 52789-2024</t>
+          <t>A 30623-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45610</v>
+        <v>45112</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2287,7 +2287,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 51096-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2301,10 +2301,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44491</v>
+        <v>45603</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>6.8</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2360,7 +2360,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 40815-2022</t>
+          <t>A 40607-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44824</v>
+        <v>45556</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>15.9</v>
+        <v>3.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2433,7 +2433,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 24023-2025</t>
+          <t>A 11771-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45796</v>
+        <v>45727</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2506,7 +2506,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 19420-2024</t>
+          <t>A 59805-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45429</v>
+        <v>45639</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2579,7 +2579,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 60754-2024</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45644</v>
+        <v>44491</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>6.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2652,7 +2652,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 11771-2025</t>
+          <t>A 39717-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45727</v>
+        <v>45167</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2725,7 +2725,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 52795-2023</t>
+          <t>A 38308-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45226</v>
+        <v>45161</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2798,7 +2798,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 52809-2022</t>
+          <t>A 55003-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2812,10 +2812,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44875</v>
+        <v>44886</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2827,13 +2827,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>2.5</v>
+        <v>6.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2876,7 +2871,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 16735-2023</t>
+          <t>A 47123-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2890,10 +2885,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45030</v>
+        <v>45586</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2906,7 +2901,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>8.699999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2949,7 +2944,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 1040-2025</t>
+          <t>A 40815-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2963,10 +2958,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45666</v>
+        <v>44824</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2979,7 +2974,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>15.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3022,7 +3017,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 1906-2022</t>
+          <t>A 10516-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3036,10 +3031,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44575</v>
+        <v>44623</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3052,7 +3047,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3095,7 +3090,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 52802-2022</t>
+          <t>A 10517-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3109,10 +3104,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44875</v>
+        <v>44623</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3124,13 +3119,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>5.8</v>
+        <v>1.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3190,7 +3180,7 @@
         <v>44602</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3246,7 +3236,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 30621-2023</t>
+          <t>A 30634-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3263,7 +3253,7 @@
         <v>45112</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3276,7 +3266,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3319,7 +3309,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 30623-2023</t>
+          <t>A 33022-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3333,10 +3323,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45112</v>
+        <v>45840</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3349,7 +3339,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3392,7 +3382,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 39269-2023</t>
+          <t>A 61260-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3406,10 +3396,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45166</v>
+        <v>46000</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3422,7 +3412,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3465,7 +3455,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 59853-2022</t>
+          <t>A 52795-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3479,10 +3469,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44908</v>
+        <v>45226</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3495,7 +3485,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3538,7 +3528,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 59612-2021</t>
+          <t>A 16735-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3552,10 +3542,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44491</v>
+        <v>45030</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3568,7 +3558,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3611,7 +3601,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 19266-2024</t>
+          <t>A 19082-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3625,10 +3615,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45428</v>
+        <v>45048</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3640,8 +3630,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>3.8</v>
+        <v>6.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3684,7 +3679,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 3683-2023</t>
+          <t>A 10298-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3698,10 +3693,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44950</v>
+        <v>46076</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3713,13 +3708,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>6.3</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3762,7 +3752,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 33022-2025</t>
+          <t>A 26029-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3776,10 +3766,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45840</v>
+        <v>44734</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3791,8 +3781,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>1.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3835,7 +3830,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 23574-2023</t>
+          <t>A 59612-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3849,10 +3844,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45077</v>
+        <v>44491</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3865,7 +3860,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3908,7 +3903,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 10516-2022</t>
+          <t>A 52802-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3922,10 +3917,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44623</v>
+        <v>44875</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3937,8 +3932,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3981,7 +3981,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 10517-2022</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44623</v>
+        <v>44491</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>6.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 39717-2023</t>
+          <t>A 39269-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4068,10 +4068,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45167</v>
+        <v>45166</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4127,7 +4127,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 41446-2023</t>
+          <t>A 26274-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4141,10 +4141,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45175</v>
+        <v>46182</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4156,13 +4156,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>8.4</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4205,7 +4200,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 30634-2023</t>
+          <t>A 26257-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4219,10 +4214,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45112</v>
+        <v>46182</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4235,7 +4230,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>6.2</v>
+        <v>1.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4278,7 +4273,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 26382-2023</t>
+          <t>A 27399-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4288,14 +4283,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45092</v>
+        <v>46189</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4307,13 +4302,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>20.3</v>
+        <v>1.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4356,7 +4346,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 55003-2022</t>
+          <t>A 27400-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4366,14 +4356,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44886</v>
+        <v>46189</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4386,7 +4376,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>6.6</v>
+        <v>3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4429,7 +4419,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 26274-2026</t>
+          <t>A 59609-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4443,10 +4433,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46182</v>
+        <v>44491</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4459,7 +4449,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>12.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4502,7 +4492,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26257-2026</t>
+          <t>A 19266-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4516,10 +4506,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46182</v>
+        <v>45428</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4532,7 +4522,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4575,7 +4565,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 27399-2026</t>
+          <t>A 52809-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4585,14 +4575,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46189</v>
+        <v>44875</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4604,8 +4594,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4648,7 +4643,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 27400-2026</t>
+          <t>A 3683-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4658,14 +4653,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46189</v>
+        <v>44950</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4677,8 +4672,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>3</v>
+        <v>6.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4721,7 +4721,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 59609-2021</t>
+          <t>A 1906-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44491</v>
+        <v>44575</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>12.7</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4794,7 +4794,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 10298-2026</t>
+          <t>A 35521-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46076</v>
+        <v>46262</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4823,8 +4823,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>6.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4867,7 +4872,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 40607-2024</t>
+          <t>A 35459-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4881,10 +4886,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45556</v>
+        <v>46262</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4897,7 +4902,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4940,7 +4945,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 59805-2024</t>
+          <t>A 59853-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4954,10 +4959,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45639</v>
+        <v>44908</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4970,7 +4975,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5030,7 +5035,7 @@
         <v>44974</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5108,7 +5113,7 @@
         <v>44974</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5164,7 +5169,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 51096-2024</t>
+          <t>A 37045-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5178,10 +5183,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45603</v>
+        <v>46273</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5193,8 +5198,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>1.3</v>
+        <v>7.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5237,7 +5247,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 47123-2024</t>
+          <t>A 31883-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5251,10 +5261,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45586</v>
+        <v>44777</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5267,7 +5277,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>5.3</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5310,7 +5320,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 38308-2023</t>
+          <t>A 37054-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5324,10 +5334,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45161</v>
+        <v>46273</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5339,8 +5349,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>2.9</v>
+        <v>6.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5383,7 +5398,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 35521-2026</t>
+          <t>A 23574-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5397,10 +5412,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46262</v>
+        <v>45077</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5412,13 +5427,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>6.2</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5461,7 +5471,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 35459-2026</t>
+          <t>A 26382-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5475,10 +5485,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46262</v>
+        <v>45092</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5490,8 +5500,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>3.5</v>
+        <v>20.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5534,7 +5549,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 61260-2025</t>
+          <t>A 37865-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5548,10 +5563,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46000</v>
+        <v>46279</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5563,8 +5578,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>4.4</v>
+        <v>9.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5607,7 +5627,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 26029-2022</t>
+          <t>A 52789-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5621,10 +5641,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44734</v>
+        <v>45610</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5636,13 +5656,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>9.699999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5685,7 +5700,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 31883-2022</t>
+          <t>A 19420-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5699,10 +5714,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44777</v>
+        <v>45429</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5715,7 +5730,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5758,7 +5773,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 37054-2026</t>
+          <t>A 60754-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5772,10 +5787,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46273</v>
+        <v>45644</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5787,13 +5802,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>6.3</v>
+        <v>2.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5836,7 +5846,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 37045-2026</t>
+          <t>A 24023-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5850,10 +5860,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46273</v>
+        <v>45796</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5865,13 +5875,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>7.6</v>
+        <v>1.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5914,7 +5919,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 37865-2026</t>
+          <t>A 1040-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5928,10 +5933,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46279</v>
+        <v>45666</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5943,13 +5948,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>9.1</v>
+        <v>1.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6009,7 +6009,7 @@
         <v>44628</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44880</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>46181</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44545</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 6319-2022</t>
+          <t>A 9813-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1931,10 +1931,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44600</v>
+        <v>44620</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1990,7 +1990,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 9813-2022</t>
+          <t>A 6319-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44620</v>
+        <v>44600</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2063,7 +2063,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 41446-2023</t>
+          <t>A 51096-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45175</v>
+        <v>45603</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2092,13 +2092,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>8.4</v>
+        <v>1.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2141,7 +2136,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 30621-2023</t>
+          <t>A 19082-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2155,10 +2150,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45112</v>
+        <v>45048</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2170,8 +2165,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2214,7 +2214,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 30623-2023</t>
+          <t>A 47123-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45112</v>
+        <v>45586</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.6</v>
+        <v>5.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2287,7 +2287,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 51096-2024</t>
+          <t>A 40815-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2301,10 +2301,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45603</v>
+        <v>44824</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>15.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2360,7 +2360,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 40607-2024</t>
+          <t>A 38308-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45556</v>
+        <v>45161</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2450,7 +2450,7 @@
         <v>45727</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 59805-2024</t>
+          <t>A 52809-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45639</v>
+        <v>44875</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2535,8 +2535,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2579,7 +2584,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 26029-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2593,10 +2598,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44491</v>
+        <v>44734</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2608,8 +2613,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>6.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2652,7 +2662,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 39717-2023</t>
+          <t>A 52795-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2666,10 +2676,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45167</v>
+        <v>45226</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2682,7 +2692,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2725,7 +2735,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 38308-2023</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2739,10 +2749,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45161</v>
+        <v>44491</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2755,7 +2765,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.9</v>
+        <v>6.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2798,7 +2808,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 55003-2022</t>
+          <t>A 31883-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2812,10 +2822,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44886</v>
+        <v>44777</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2828,7 +2838,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>6.6</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2871,7 +2881,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 47123-2024</t>
+          <t>A 16735-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2885,10 +2895,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45586</v>
+        <v>45030</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2901,7 +2911,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>5.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2944,7 +2954,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 40815-2022</t>
+          <t>A 52802-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2958,10 +2968,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44824</v>
+        <v>44875</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2973,8 +2983,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>15.9</v>
+        <v>5.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3017,7 +3032,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 10516-2022</t>
+          <t>A 6734-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3031,10 +3046,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44623</v>
+        <v>44602</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3047,7 +3062,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.1</v>
+        <v>32.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3090,7 +3105,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 10517-2022</t>
+          <t>A 1906-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3104,10 +3119,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44623</v>
+        <v>44575</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3120,7 +3135,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3163,7 +3178,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 6734-2022</t>
+          <t>A 30621-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3177,10 +3192,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44602</v>
+        <v>45112</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3193,7 +3208,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>32.3</v>
+        <v>3.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3236,7 +3251,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 30634-2023</t>
+          <t>A 30623-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3253,7 +3268,7 @@
         <v>45112</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3266,7 +3281,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>6.2</v>
+        <v>2.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3309,7 +3324,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 33022-2025</t>
+          <t>A 52789-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3323,10 +3338,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45840</v>
+        <v>45610</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3339,7 +3354,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3382,7 +3397,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 61260-2025</t>
+          <t>A 59853-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3396,10 +3411,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46000</v>
+        <v>44908</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3412,7 +3427,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3455,7 +3470,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 52795-2023</t>
+          <t>A 39269-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3469,10 +3484,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45226</v>
+        <v>45166</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3485,7 +3500,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3528,7 +3543,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 16735-2023</t>
+          <t>A 59612-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3542,10 +3557,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45030</v>
+        <v>44491</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3558,7 +3573,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>8.699999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3601,7 +3616,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 19082-2023</t>
+          <t>A 24023-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3615,10 +3630,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45048</v>
+        <v>45796</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3630,13 +3645,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>6.5</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3679,7 +3689,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 10298-2026</t>
+          <t>A 19420-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3693,10 +3703,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46076</v>
+        <v>45429</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3709,7 +3719,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3752,7 +3762,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 26029-2022</t>
+          <t>A 60754-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3766,10 +3776,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44734</v>
+        <v>45644</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3781,13 +3791,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>9.699999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3830,7 +3835,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 59612-2021</t>
+          <t>A 19266-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3844,10 +3849,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44491</v>
+        <v>45428</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3860,7 +3865,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3903,7 +3908,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 52802-2022</t>
+          <t>A 3683-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3917,10 +3922,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44875</v>
+        <v>44950</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3938,7 +3943,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3981,7 +3986,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 23574-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3995,10 +4000,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44491</v>
+        <v>45077</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4011,7 +4016,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>6.8</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4054,7 +4059,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 39269-2023</t>
+          <t>A 10516-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4068,10 +4073,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45166</v>
+        <v>44623</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4084,7 +4089,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4127,7 +4132,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 26274-2026</t>
+          <t>A 10517-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4141,10 +4146,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46182</v>
+        <v>44623</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4157,7 +4162,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4200,7 +4205,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 26257-2026</t>
+          <t>A 39717-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4214,10 +4219,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46182</v>
+        <v>45167</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4230,7 +4235,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4273,7 +4278,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 27399-2026</t>
+          <t>A 41446-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4283,14 +4288,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46189</v>
+        <v>45175</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4302,8 +4307,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>1.4</v>
+        <v>8.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4346,7 +4356,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 27400-2026</t>
+          <t>A 1040-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4356,14 +4366,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46189</v>
+        <v>45666</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4376,7 +4386,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4419,7 +4429,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 59609-2021</t>
+          <t>A 30634-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4433,10 +4443,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44491</v>
+        <v>45112</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4449,7 +4459,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>12.7</v>
+        <v>6.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4492,7 +4502,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 19266-2024</t>
+          <t>A 26382-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4506,10 +4516,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45428</v>
+        <v>45092</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4521,8 +4531,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>3.8</v>
+        <v>20.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4565,7 +4580,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 52809-2022</t>
+          <t>A 55003-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4579,10 +4594,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44875</v>
+        <v>44886</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4594,13 +4609,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>2.5</v>
+        <v>6.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4643,7 +4653,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 3683-2023</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4657,10 +4667,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44950</v>
+        <v>44491</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4672,13 +4682,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>6.3</v>
+        <v>6.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4721,7 +4726,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 1906-2022</t>
+          <t>A 59609-2021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4735,10 +4740,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44575</v>
+        <v>44491</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4751,7 +4756,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>12.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4794,7 +4799,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 35521-2026</t>
+          <t>A 61260-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4808,10 +4813,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46262</v>
+        <v>46000</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4823,13 +4828,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4872,7 +4872,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 35459-2026</t>
+          <t>A 33022-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4886,10 +4886,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46262</v>
+        <v>45840</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4945,7 +4945,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 59853-2022</t>
+          <t>A 40607-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4959,10 +4959,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44908</v>
+        <v>45556</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5018,7 +5018,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 8193-2023</t>
+          <t>A 59805-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5032,10 +5032,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44974</v>
+        <v>45639</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5047,13 +5047,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>10.5</v>
+        <v>3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5096,7 +5091,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 8228-2023</t>
+          <t>A 8193-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5113,7 +5108,7 @@
         <v>44974</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5125,8 +5120,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>13.9</v>
+        <v>10.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5169,7 +5169,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 37045-2026</t>
+          <t>A 8228-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5183,10 +5183,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46273</v>
+        <v>44974</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5198,13 +5198,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>7.6</v>
+        <v>13.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5247,7 +5242,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 31883-2022</t>
+          <t>A 10298-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5261,10 +5256,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44777</v>
+        <v>46076</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5320,7 +5315,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 37054-2026</t>
+          <t>A 26274-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5334,10 +5329,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46273</v>
+        <v>46182</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5349,13 +5344,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>6.3</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5398,7 +5388,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 23574-2023</t>
+          <t>A 26257-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5412,10 +5402,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45077</v>
+        <v>46182</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5428,7 +5418,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5471,7 +5461,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 26382-2023</t>
+          <t>A 27399-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5481,14 +5471,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45092</v>
+        <v>46189</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5500,13 +5490,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>20.3</v>
+        <v>1.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5549,7 +5534,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 37865-2026</t>
+          <t>A 27400-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5559,14 +5544,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46279</v>
+        <v>46189</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5578,13 +5563,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>9.1</v>
+        <v>3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5627,7 +5607,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 52789-2024</t>
+          <t>A 37054-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5641,10 +5621,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45610</v>
+        <v>46273</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5656,8 +5636,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>2.4</v>
+        <v>6.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5700,7 +5685,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 19420-2024</t>
+          <t>A 37045-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5714,10 +5699,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45429</v>
+        <v>46273</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5729,8 +5714,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>3.8</v>
+        <v>7.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5773,7 +5763,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 60754-2024</t>
+          <t>A 37865-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5787,10 +5777,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45644</v>
+        <v>46279</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5802,8 +5792,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>2.4</v>
+        <v>9.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5846,7 +5841,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 24023-2025</t>
+          <t>A 35459-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5860,10 +5855,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45796</v>
+        <v>46262</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5876,7 +5871,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5919,7 +5914,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 1040-2025</t>
+          <t>A 35521-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5933,10 +5928,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45666</v>
+        <v>46262</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5948,8 +5943,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>1.6</v>
+        <v>6.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6009,7 +6009,7 @@
         <v>44628</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44880</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>46181</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44545</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44620</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44600</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>45603</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>45048</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>45586</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>44824</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>45161</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>45727</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>44875</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>44734</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>45226</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>44491</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>44777</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>45030</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>44875</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>44602</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>44575</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>45112</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>45112</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>45610</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>44908</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>45166</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>44491</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45796</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>45429</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>45644</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>45428</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>44950</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>45077</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>44623</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>44623</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>45167</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>45175</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>45666</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>45112</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>45092</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>44886</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>44491</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>44491</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46000</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>45840</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>45556</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>45639</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>44974</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>44974</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>46076</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>46182</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>46182</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         <v>46189</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>46189</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>46273</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>46273</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>46279</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>46262</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>46262</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>44628</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44880</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>46181</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44545</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44620</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44600</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>45603</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>45048</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>45586</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>44824</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>45161</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>45727</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>44875</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>44734</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>45226</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>44491</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>44777</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>45030</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>44875</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>44602</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>44575</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>45112</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>45112</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>45610</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>44908</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>45166</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>44491</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45796</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>45429</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>45644</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>45428</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>44950</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>45077</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>44623</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>44623</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>45167</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>45175</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>45666</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>45112</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>45092</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>44886</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>44491</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>44491</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46000</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>45840</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>45556</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>45639</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>44974</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>44974</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>46076</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>46182</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>46182</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         <v>46189</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>46189</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>46273</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>46273</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>46279</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>46262</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         <v>46262</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>44628</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 8475-2025</t>
+          <t>A 37056-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45709</v>
+        <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         <v>15</v>
       </c>
       <c r="U3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
@@ -793,46 +793,46 @@
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 8475-2025 artfynd.xlsx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 37056-2026 artfynd.xlsx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 8475-2025 karta.png", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 37056-2026 karta.png", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 8475-2025 georefererad karta.tif", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 37056-2026 georefererad karta.tif", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="Z3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 8475-2025 karta knärot.png", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 37056-2026 karta knärot.png", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 8475-2025 FSC-klagomål.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 37056-2026 FSC-klagomål.docx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 8475-2025 FSC-klagomål mail.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 37056-2026 FSC-klagomål mail.docx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 8475-2025 tillsynsbegäran.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 37056-2026 tillsynsbegäran.docx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 8475-2025 tillsynsbegäran mail.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 37056-2026 tillsynsbegäran mail.docx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/fåglar/A 8475-2025 prioriterade fågelarter.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/fåglar/A 37056-2026 prioriterade fågelarter.docx", "A 37056-2026")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 37056-2026</t>
+          <t>A 8475-2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46273</v>
+        <v>45709</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>15</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
@@ -913,39 +913,39 @@
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 37056-2026 artfynd.xlsx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 8475-2025 artfynd.xlsx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 37056-2026 karta.png", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 8475-2025 karta.png", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 37056-2026 georefererad karta.tif", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 8475-2025 georefererad karta.tif", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="Z4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 37056-2026 karta knärot.png", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 8475-2025 karta knärot.png", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 37056-2026 FSC-klagomål.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 8475-2025 FSC-klagomål.docx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 37056-2026 FSC-klagomål mail.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 8475-2025 FSC-klagomål mail.docx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 37056-2026 tillsynsbegäran.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 8475-2025 tillsynsbegäran.docx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 37056-2026 tillsynsbegäran mail.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 8475-2025 tillsynsbegäran mail.docx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/fåglar/A 37056-2026 prioriterade fågelarter.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/fåglar/A 8475-2025 prioriterade fågelarter.docx", "A 8475-2025")</f>
         <v/>
       </c>
     </row>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 53870-2022</t>
+          <t>A 25961-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44880</v>
+        <v>46181</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1430,13 +1430,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>2.3</v>
+        <v>7.3</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1448,7 +1443,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1460,10 +1455,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1472,46 +1467,50 @@
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 25961-2026</t>
+          <t>A 53870-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1525,10 +1524,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46181</v>
+        <v>44880</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1540,8 +1539,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>7.3</v>
+        <v>2.3</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1553,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1565,10 +1569,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1577,43 +1581,39 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
-        <v/>
-      </c>
-      <c r="Z10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44545</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 9813-2022</t>
+          <t>A 6319-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1931,10 +1931,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44620</v>
+        <v>44600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1990,7 +1990,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 6319-2022</t>
+          <t>A 9813-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44600</v>
+        <v>44620</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2063,7 +2063,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 51096-2024</t>
+          <t>A 1906-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45603</v>
+        <v>44575</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2136,7 +2136,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 19082-2023</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2150,10 +2150,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45048</v>
+        <v>44491</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2165,13 +2165,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2214,7 +2209,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 47123-2024</t>
+          <t>A 41446-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2228,10 +2223,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45586</v>
+        <v>45175</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2243,8 +2238,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>5.3</v>
+        <v>8.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2287,7 +2287,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 40815-2022</t>
+          <t>A 30621-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2301,10 +2301,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44824</v>
+        <v>45112</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>15.9</v>
+        <v>3.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2360,7 +2360,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 38308-2023</t>
+          <t>A 30623-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45161</v>
+        <v>45112</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2433,7 +2433,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 11771-2025</t>
+          <t>A 59853-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45727</v>
+        <v>44908</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2506,7 +2506,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 52809-2022</t>
+          <t>A 8193-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44875</v>
+        <v>44974</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.5</v>
+        <v>10.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2584,7 +2584,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 26029-2022</t>
+          <t>A 8228-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44734</v>
+        <v>44974</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2613,13 +2613,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>9.699999999999999</v>
+        <v>13.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2662,7 +2657,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 52795-2023</t>
+          <t>A 26274-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2676,10 +2671,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45226</v>
+        <v>46182</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2692,7 +2687,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2735,7 +2730,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 26257-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2749,10 +2744,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44491</v>
+        <v>46182</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2765,7 +2760,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>6.8</v>
+        <v>1.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2825,7 +2820,7 @@
         <v>44777</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2881,7 +2876,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 16735-2023</t>
+          <t>A 27399-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2891,14 +2886,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45030</v>
+        <v>46189</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2911,7 +2906,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>8.699999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2954,7 +2949,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 52802-2022</t>
+          <t>A 27400-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2964,14 +2959,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44875</v>
+        <v>46189</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2983,13 +2978,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>5.8</v>
+        <v>3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3032,7 +3022,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 6734-2022</t>
+          <t>A 23574-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3046,10 +3036,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44602</v>
+        <v>45077</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3062,7 +3052,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>32.3</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3105,7 +3095,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 1906-2022</t>
+          <t>A 26382-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3119,10 +3109,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44575</v>
+        <v>45092</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3134,8 +3124,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>20.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3178,7 +3173,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 30621-2023</t>
+          <t>A 52789-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3192,10 +3187,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45112</v>
+        <v>45610</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3208,7 +3203,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3251,7 +3246,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 30623-2023</t>
+          <t>A 19420-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3265,10 +3260,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45112</v>
+        <v>45429</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3281,7 +3276,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3324,7 +3319,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 52789-2024</t>
+          <t>A 60754-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3338,10 +3333,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45610</v>
+        <v>45644</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3397,7 +3392,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 59853-2022</t>
+          <t>A 24023-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3411,10 +3406,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44908</v>
+        <v>45796</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3427,7 +3422,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3470,7 +3465,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 39269-2023</t>
+          <t>A 51096-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3484,10 +3479,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45166</v>
+        <v>45603</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3500,7 +3495,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3543,7 +3538,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 59612-2021</t>
+          <t>A 37045-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3557,10 +3552,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44491</v>
+        <v>46273</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3572,8 +3567,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>3.2</v>
+        <v>7.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3616,7 +3616,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 24023-2025</t>
+          <t>A 37054-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3630,10 +3630,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45796</v>
+        <v>46273</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3645,8 +3645,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>6.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3689,7 +3694,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 19420-2024</t>
+          <t>A 1040-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3703,10 +3708,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45429</v>
+        <v>45666</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3719,7 +3724,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3762,7 +3767,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 60754-2024</t>
+          <t>A 37865-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3776,10 +3781,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45644</v>
+        <v>46279</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3791,8 +3796,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>2.4</v>
+        <v>9.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3835,7 +3845,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 19266-2024</t>
+          <t>A 40607-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3849,10 +3859,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45428</v>
+        <v>45556</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3865,7 +3875,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3908,7 +3918,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 3683-2023</t>
+          <t>A 10298-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3922,10 +3932,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44950</v>
+        <v>46076</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3937,13 +3947,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>6.3</v>
+        <v>1.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3986,7 +3991,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 23574-2023</t>
+          <t>A 11771-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4000,10 +4005,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45077</v>
+        <v>45727</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4016,7 +4021,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4059,7 +4064,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 10516-2022</t>
+          <t>A 35521-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4073,10 +4078,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44623</v>
+        <v>46262</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4088,8 +4093,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>2.1</v>
+        <v>6.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4132,7 +4142,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 10517-2022</t>
+          <t>A 35459-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4146,10 +4156,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44623</v>
+        <v>46262</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4162,7 +4172,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4205,7 +4215,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 39717-2023</t>
+          <t>A 33022-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4219,10 +4229,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45167</v>
+        <v>45840</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4235,7 +4245,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4278,7 +4288,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 41446-2023</t>
+          <t>A 61260-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4292,10 +4302,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45175</v>
+        <v>46000</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4307,13 +4317,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>8.4</v>
+        <v>4.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4356,7 +4361,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 1040-2025</t>
+          <t>A 59805-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4370,10 +4375,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45666</v>
+        <v>45639</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4386,7 +4391,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4429,7 +4434,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 30634-2023</t>
+          <t>A 39717-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4443,10 +4448,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45112</v>
+        <v>45167</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4459,7 +4464,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>6.2</v>
+        <v>2.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4502,7 +4507,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26382-2023</t>
+          <t>A 38308-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4516,10 +4521,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45092</v>
+        <v>45161</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4531,13 +4536,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>20.3</v>
+        <v>2.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4597,7 +4597,7 @@
         <v>44886</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 47123-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4667,10 +4667,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44491</v>
+        <v>45586</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4726,7 +4726,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 59609-2021</t>
+          <t>A 40815-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4740,10 +4740,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44491</v>
+        <v>44824</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>12.7</v>
+        <v>15.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4799,7 +4799,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 61260-2025</t>
+          <t>A 10516-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46000</v>
+        <v>44623</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.4</v>
+        <v>2.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4872,7 +4872,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 33022-2025</t>
+          <t>A 10517-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4886,10 +4886,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45840</v>
+        <v>44623</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4945,7 +4945,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 40607-2024</t>
+          <t>A 6734-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4959,10 +4959,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45556</v>
+        <v>44602</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.2</v>
+        <v>32.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5018,7 +5018,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 59805-2024</t>
+          <t>A 30634-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5032,10 +5032,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45639</v>
+        <v>45112</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3</v>
+        <v>6.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5091,7 +5091,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 8193-2023</t>
+          <t>A 52795-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5105,10 +5105,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44974</v>
+        <v>45226</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5120,13 +5120,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>10.5</v>
+        <v>3.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5169,7 +5164,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 8228-2023</t>
+          <t>A 16735-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5183,10 +5178,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44974</v>
+        <v>45030</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5199,7 +5194,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>13.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5242,7 +5237,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 10298-2026</t>
+          <t>A 19082-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5256,10 +5251,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46076</v>
+        <v>45048</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5271,8 +5266,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>6.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5315,7 +5315,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 26274-2026</t>
+          <t>A 26029-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5329,10 +5329,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46182</v>
+        <v>44734</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5344,8 +5344,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5388,7 +5393,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 26257-2026</t>
+          <t>A 59612-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5402,10 +5407,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46182</v>
+        <v>44491</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5418,7 +5423,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5461,7 +5466,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 27399-2026</t>
+          <t>A 52802-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5471,14 +5476,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46189</v>
+        <v>44875</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5490,8 +5495,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>1.4</v>
+        <v>5.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5534,7 +5544,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 27400-2026</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5544,14 +5554,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46189</v>
+        <v>44491</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5564,7 +5574,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3</v>
+        <v>6.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5607,7 +5617,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 37054-2026</t>
+          <t>A 39269-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5621,10 +5631,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46273</v>
+        <v>45166</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5636,13 +5646,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>6.3</v>
+        <v>3.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5685,7 +5690,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 37045-2026</t>
+          <t>A 59609-2021</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5699,10 +5704,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46273</v>
+        <v>44491</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5714,13 +5719,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>7.6</v>
+        <v>12.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 37865-2026</t>
+          <t>A 19266-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46279</v>
+        <v>45428</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5792,13 +5792,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>9.1</v>
+        <v>3.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5841,7 +5836,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 35459-2026</t>
+          <t>A 52809-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5855,10 +5850,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46262</v>
+        <v>44875</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5870,8 +5865,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5914,7 +5914,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 35521-2026</t>
+          <t>A 3683-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46262</v>
+        <v>44950</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6009,7 +6009,7 @@
         <v>44628</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 37056-2026</t>
+          <t>A 8475-2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46273</v>
+        <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         <v>15</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
@@ -793,46 +793,46 @@
         </is>
       </c>
       <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 37056-2026 artfynd.xlsx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 8475-2025 artfynd.xlsx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 37056-2026 karta.png", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 8475-2025 karta.png", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 37056-2026 georefererad karta.tif", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 8475-2025 georefererad karta.tif", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="Z3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 37056-2026 karta knärot.png", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 8475-2025 karta knärot.png", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 37056-2026 FSC-klagomål.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 8475-2025 FSC-klagomål.docx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 37056-2026 FSC-klagomål mail.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 8475-2025 FSC-klagomål mail.docx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 37056-2026 tillsynsbegäran.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 8475-2025 tillsynsbegäran.docx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 37056-2026 tillsynsbegäran mail.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 8475-2025 tillsynsbegäran mail.docx", "A 8475-2025")</f>
         <v/>
       </c>
       <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/fåglar/A 37056-2026 prioriterade fågelarter.docx", "A 37056-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/fåglar/A 8475-2025 prioriterade fågelarter.docx", "A 8475-2025")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 8475-2025</t>
+          <t>A 37056-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45709</v>
+        <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>15</v>
       </c>
       <c r="U4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
@@ -913,39 +913,39 @@
         </is>
       </c>
       <c r="W4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 8475-2025 artfynd.xlsx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 37056-2026 artfynd.xlsx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="X4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 8475-2025 karta.png", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 37056-2026 karta.png", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="Y4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 8475-2025 georefererad karta.tif", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 37056-2026 georefererad karta.tif", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="Z4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 8475-2025 karta knärot.png", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 37056-2026 karta knärot.png", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AA4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 8475-2025 FSC-klagomål.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 37056-2026 FSC-klagomål.docx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AB4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 8475-2025 FSC-klagomål mail.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 37056-2026 FSC-klagomål mail.docx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AC4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 8475-2025 tillsynsbegäran.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 37056-2026 tillsynsbegäran.docx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AD4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 8475-2025 tillsynsbegäran mail.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 37056-2026 tillsynsbegäran mail.docx", "A 37056-2026")</f>
         <v/>
       </c>
       <c r="AE4">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/fåglar/A 8475-2025 prioriterade fågelarter.docx", "A 8475-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/fåglar/A 37056-2026 prioriterade fågelarter.docx", "A 37056-2026")</f>
         <v/>
       </c>
     </row>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>46181</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>44880</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44545</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44620</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 1906-2022</t>
+          <t>A 19082-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44575</v>
+        <v>45048</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2092,8 +2092,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2136,7 +2141,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 40815-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2150,10 +2155,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44491</v>
+        <v>44824</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2166,7 +2171,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>6.8</v>
+        <v>15.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2209,7 +2214,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 41446-2023</t>
+          <t>A 52795-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2223,10 +2228,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45175</v>
+        <v>45226</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2238,13 +2243,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>8.4</v>
+        <v>3.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2287,7 +2287,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 30621-2023</t>
+          <t>A 24023-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2301,10 +2301,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45112</v>
+        <v>45796</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2360,7 +2360,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 30623-2023</t>
+          <t>A 19420-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45112</v>
+        <v>45429</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2433,7 +2433,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 59853-2022</t>
+          <t>A 60754-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44908</v>
+        <v>45644</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2506,7 +2506,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 8193-2023</t>
+          <t>A 52802-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44974</v>
+        <v>44875</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>10.5</v>
+        <v>5.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2584,7 +2584,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 8228-2023</t>
+          <t>A 6734-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44974</v>
+        <v>44602</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>13.9</v>
+        <v>32.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2657,7 +2657,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 26274-2026</t>
+          <t>A 30621-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46182</v>
+        <v>45112</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2730,7 +2730,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 26257-2026</t>
+          <t>A 30623-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46182</v>
+        <v>45112</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2803,7 +2803,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 31883-2022</t>
+          <t>A 1040-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44777</v>
+        <v>45666</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2876,7 +2876,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 27399-2026</t>
+          <t>A 59853-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2886,14 +2886,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46189</v>
+        <v>44908</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2949,7 +2949,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 27400-2026</t>
+          <t>A 3683-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2959,14 +2959,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46189</v>
+        <v>44950</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2978,8 +2978,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>6.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3022,7 +3027,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 23574-2023</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3036,10 +3041,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45077</v>
+        <v>44491</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3052,7 +3057,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>6.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3095,7 +3100,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 26382-2023</t>
+          <t>A 23574-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3109,10 +3114,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45092</v>
+        <v>45077</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3124,13 +3129,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>20.3</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3173,7 +3173,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 52789-2024</t>
+          <t>A 41446-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45610</v>
+        <v>45175</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3202,8 +3202,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>2.4</v>
+        <v>8.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3246,7 +3251,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 19420-2024</t>
+          <t>A 30634-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3260,10 +3265,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45429</v>
+        <v>45112</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3276,7 +3281,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.8</v>
+        <v>6.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3319,7 +3324,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 60754-2024</t>
+          <t>A 26382-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3333,10 +3338,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45644</v>
+        <v>45092</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3348,8 +3353,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>20.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3392,7 +3402,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 24023-2025</t>
+          <t>A 10298-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3406,10 +3416,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45796</v>
+        <v>46076</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3465,7 +3475,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 51096-2024</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3479,10 +3489,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45603</v>
+        <v>44491</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3495,7 +3505,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.3</v>
+        <v>6.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3538,7 +3548,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 37045-2026</t>
+          <t>A 11771-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3552,10 +3562,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46273</v>
+        <v>45727</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3567,13 +3577,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>7.6</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3616,7 +3621,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 37054-2026</t>
+          <t>A 61260-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3630,10 +3635,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46273</v>
+        <v>46000</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3645,13 +3650,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>6.3</v>
+        <v>4.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3694,7 +3694,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 1040-2025</t>
+          <t>A 52809-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3708,10 +3708,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45666</v>
+        <v>44875</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3723,8 +3723,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3767,7 +3772,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 37865-2026</t>
+          <t>A 16735-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3781,10 +3786,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46279</v>
+        <v>45030</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3796,13 +3801,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3845,7 +3845,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 40607-2024</t>
+          <t>A 33022-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45556</v>
+        <v>45840</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3918,7 +3918,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 10298-2026</t>
+          <t>A 1906-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46076</v>
+        <v>44575</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3991,7 +3991,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 11771-2025</t>
+          <t>A 39269-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45727</v>
+        <v>45166</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4064,7 +4064,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 35521-2026</t>
+          <t>A 59612-2021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4078,10 +4078,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46262</v>
+        <v>44491</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4093,13 +4093,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>6.2</v>
+        <v>3.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4142,7 +4137,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 35459-2026</t>
+          <t>A 19266-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4156,10 +4151,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46262</v>
+        <v>45428</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4172,7 +4167,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4215,7 +4210,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 33022-2025</t>
+          <t>A 10516-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4229,10 +4224,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45840</v>
+        <v>44623</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4245,7 +4240,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4288,7 +4283,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 61260-2025</t>
+          <t>A 10517-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4302,10 +4297,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46000</v>
+        <v>44623</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4318,7 +4313,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.4</v>
+        <v>1.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4361,7 +4356,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 59805-2024</t>
+          <t>A 39717-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4375,10 +4370,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45639</v>
+        <v>45167</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4391,7 +4386,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4434,7 +4429,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 39717-2023</t>
+          <t>A 26274-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4448,10 +4443,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45167</v>
+        <v>46182</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4464,7 +4459,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4507,7 +4502,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 38308-2023</t>
+          <t>A 26257-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4521,10 +4516,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45161</v>
+        <v>46182</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4537,7 +4532,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4580,7 +4575,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 55003-2022</t>
+          <t>A 27399-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4590,14 +4585,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44886</v>
+        <v>46189</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4610,7 +4605,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>6.6</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4653,7 +4648,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 47123-2024</t>
+          <t>A 27400-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4663,14 +4658,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45586</v>
+        <v>46189</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4683,7 +4678,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>5.3</v>
+        <v>3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4726,7 +4721,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 40815-2022</t>
+          <t>A 55003-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4740,10 +4735,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44824</v>
+        <v>44886</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4756,7 +4751,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>15.9</v>
+        <v>6.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4799,7 +4794,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 10516-2022</t>
+          <t>A 59609-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4813,10 +4808,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44623</v>
+        <v>44491</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4829,7 +4824,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.1</v>
+        <v>12.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4872,7 +4867,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 10517-2022</t>
+          <t>A 37054-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4886,10 +4881,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44623</v>
+        <v>46273</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4901,8 +4896,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>1.2</v>
+        <v>6.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4945,7 +4945,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 6734-2022</t>
+          <t>A 37045-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4959,10 +4959,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44602</v>
+        <v>46273</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4974,8 +4974,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>32.3</v>
+        <v>7.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5018,7 +5023,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 30634-2023</t>
+          <t>A 40607-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5032,10 +5037,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45112</v>
+        <v>45556</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5048,7 +5053,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>6.2</v>
+        <v>3.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5091,7 +5096,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 52795-2023</t>
+          <t>A 59805-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5105,10 +5110,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45226</v>
+        <v>45639</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5121,7 +5126,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5164,7 +5169,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 16735-2023</t>
+          <t>A 8193-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5178,10 +5183,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45030</v>
+        <v>44974</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5193,8 +5198,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>8.699999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5237,7 +5247,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 19082-2023</t>
+          <t>A 8228-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5251,10 +5261,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45048</v>
+        <v>44974</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5266,13 +5276,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>6.5</v>
+        <v>13.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5315,7 +5320,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 26029-2022</t>
+          <t>A 37865-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5329,10 +5334,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44734</v>
+        <v>46279</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5350,7 +5355,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>9.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5393,7 +5398,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 59612-2021</t>
+          <t>A 51096-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5407,10 +5412,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44491</v>
+        <v>45603</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5423,7 +5428,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5466,7 +5471,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 52802-2022</t>
+          <t>A 47123-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5480,10 +5485,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44875</v>
+        <v>45586</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5495,13 +5500,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5544,7 +5544,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 38308-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5558,10 +5558,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44491</v>
+        <v>45161</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>6.8</v>
+        <v>2.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5617,7 +5617,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 39269-2023</t>
+          <t>A 26029-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5631,10 +5631,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45166</v>
+        <v>44734</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5646,8 +5646,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>3.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5690,7 +5695,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 59609-2021</t>
+          <t>A 31883-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5704,10 +5709,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44491</v>
+        <v>44777</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5720,7 +5725,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>12.7</v>
+        <v>1.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5763,7 +5768,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 19266-2024</t>
+          <t>A 52789-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5777,10 +5782,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45428</v>
+        <v>45610</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5793,7 +5798,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5836,7 +5841,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 52809-2022</t>
+          <t>A 35521-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5850,10 +5855,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44875</v>
+        <v>46262</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5871,7 +5876,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.5</v>
+        <v>6.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5914,7 +5919,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 3683-2023</t>
+          <t>A 35459-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5928,10 +5933,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44950</v>
+        <v>46262</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5943,13 +5948,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>6.3</v>
+        <v>3.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6009,7 +6009,7 @@
         <v>44628</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25961-2026</t>
+          <t>A 53870-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46181</v>
+        <v>44880</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1430,8 +1430,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>7.3</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1443,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1455,10 +1460,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1467,50 +1472,46 @@
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
-        <v/>
-      </c>
-      <c r="Z9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 53870-2022</t>
+          <t>A 25961-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1524,10 +1525,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44880</v>
+        <v>46181</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1539,13 +1540,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>2.3</v>
+        <v>7.3</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1557,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1569,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1581,39 +1577,43 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
+        <v/>
+      </c>
+      <c r="Z10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44545</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 9813-2022</t>
+          <t>A 19420-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44620</v>
+        <v>45429</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2063,7 +2063,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 19082-2023</t>
+          <t>A 60754-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45048</v>
+        <v>45644</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2092,13 +2092,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>6.5</v>
+        <v>2.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2141,7 +2136,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 40815-2022</t>
+          <t>A 24023-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2155,10 +2150,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44824</v>
+        <v>45796</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2171,7 +2166,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>15.9</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2214,7 +2209,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 52795-2023</t>
+          <t>A 9813-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2228,10 +2223,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45226</v>
+        <v>44620</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2244,7 +2239,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2287,7 +2282,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 24023-2025</t>
+          <t>A 41446-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2301,10 +2296,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45796</v>
+        <v>45175</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2316,8 +2311,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>8.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2360,7 +2360,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 19420-2024</t>
+          <t>A 30621-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45429</v>
+        <v>45112</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2433,7 +2433,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 60754-2024</t>
+          <t>A 30623-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45644</v>
+        <v>45112</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2506,7 +2506,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 52802-2022</t>
+          <t>A 1040-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44875</v>
+        <v>45666</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2535,13 +2535,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>5.8</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2584,7 +2579,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 6734-2022</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2598,10 +2593,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44602</v>
+        <v>44491</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2614,7 +2609,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>32.3</v>
+        <v>6.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2657,7 +2652,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 30621-2023</t>
+          <t>A 51096-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2671,10 +2666,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45112</v>
+        <v>45603</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2687,7 +2682,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2730,7 +2725,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 30623-2023</t>
+          <t>A 40607-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2744,10 +2739,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45112</v>
+        <v>45556</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2760,7 +2755,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2803,7 +2798,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 1040-2025</t>
+          <t>A 11771-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2817,10 +2812,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45666</v>
+        <v>45727</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2833,7 +2828,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2876,7 +2871,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 59853-2022</t>
+          <t>A 6734-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2890,10 +2885,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44908</v>
+        <v>44602</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2906,7 +2901,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>32.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2949,7 +2944,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 3683-2023</t>
+          <t>A 10298-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2963,10 +2958,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44950</v>
+        <v>46076</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2978,13 +2973,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>6.3</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3027,7 +3017,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 30634-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3041,10 +3031,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44491</v>
+        <v>45112</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3057,7 +3047,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3100,7 +3090,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 23574-2023</t>
+          <t>A 59805-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3114,10 +3104,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45077</v>
+        <v>45639</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3130,7 +3120,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3173,7 +3163,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 41446-2023</t>
+          <t>A 39717-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3187,10 +3177,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45175</v>
+        <v>45167</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3202,13 +3192,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>8.4</v>
+        <v>2.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3251,7 +3236,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 30634-2023</t>
+          <t>A 38308-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3265,10 +3250,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45112</v>
+        <v>45161</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3281,7 +3266,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>6.2</v>
+        <v>2.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3324,7 +3309,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 26382-2023</t>
+          <t>A 55003-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3338,10 +3323,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45092</v>
+        <v>44886</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3353,13 +3338,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>20.3</v>
+        <v>6.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3402,7 +3382,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10298-2026</t>
+          <t>A 47123-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3416,10 +3396,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46076</v>
+        <v>45586</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3432,7 +3412,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3475,7 +3455,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 40815-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3489,10 +3469,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44491</v>
+        <v>44824</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3505,7 +3485,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>6.8</v>
+        <v>15.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3548,7 +3528,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 11771-2025</t>
+          <t>A 33022-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3562,10 +3542,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45727</v>
+        <v>45840</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3578,7 +3558,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3638,7 +3618,7 @@
         <v>46000</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3694,7 +3674,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 52809-2022</t>
+          <t>A 10516-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3708,10 +3688,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44875</v>
+        <v>44623</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3723,13 +3703,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3772,7 +3747,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 16735-2023</t>
+          <t>A 10517-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3786,10 +3761,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45030</v>
+        <v>44623</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3802,7 +3777,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>8.699999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3845,7 +3820,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 33022-2025</t>
+          <t>A 52795-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3859,10 +3834,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45840</v>
+        <v>45226</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3875,7 +3850,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3918,7 +3893,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 1906-2022</t>
+          <t>A 16735-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3932,10 +3907,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44575</v>
+        <v>45030</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3948,7 +3923,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3991,7 +3966,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 39269-2023</t>
+          <t>A 19082-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4005,10 +3980,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45166</v>
+        <v>45048</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4020,8 +3995,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>3.3</v>
+        <v>6.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4064,7 +4044,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 59612-2021</t>
+          <t>A 26274-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4078,10 +4058,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44491</v>
+        <v>46182</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4094,7 +4074,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4137,7 +4117,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 19266-2024</t>
+          <t>A 26257-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4151,10 +4131,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45428</v>
+        <v>46182</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4167,7 +4147,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4210,7 +4190,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 10516-2022</t>
+          <t>A 27399-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4220,14 +4200,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44623</v>
+        <v>46189</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4240,7 +4220,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4283,7 +4263,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 10517-2022</t>
+          <t>A 27400-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4293,14 +4273,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44623</v>
+        <v>46189</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4313,7 +4293,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4356,7 +4336,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 39717-2023</t>
+          <t>A 26029-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4370,10 +4350,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45167</v>
+        <v>44734</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4385,8 +4365,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>2.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4429,7 +4414,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 26274-2026</t>
+          <t>A 59612-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4443,10 +4428,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46182</v>
+        <v>44491</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4459,7 +4444,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4502,7 +4487,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26257-2026</t>
+          <t>A 52802-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4516,10 +4501,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46182</v>
+        <v>44875</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4531,8 +4516,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>5.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4575,7 +4565,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 27399-2026</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4585,14 +4575,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46189</v>
+        <v>44491</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4605,7 +4595,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>6.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4648,7 +4638,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 27400-2026</t>
+          <t>A 39269-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4658,14 +4648,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46189</v>
+        <v>45166</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4678,7 +4668,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4721,7 +4711,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 55003-2022</t>
+          <t>A 37045-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4735,10 +4725,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44886</v>
+        <v>46273</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4750,8 +4740,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4794,7 +4789,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 59609-2021</t>
+          <t>A 37054-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4808,10 +4803,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44491</v>
+        <v>46273</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4823,8 +4818,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>12.7</v>
+        <v>6.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4867,7 +4867,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 37054-2026</t>
+          <t>A 37865-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4881,10 +4881,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46273</v>
+        <v>46279</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>6.3</v>
+        <v>9.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4945,7 +4945,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 37045-2026</t>
+          <t>A 59609-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4959,10 +4959,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46273</v>
+        <v>44491</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4974,13 +4974,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>7.6</v>
+        <v>12.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5023,7 +5018,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 40607-2024</t>
+          <t>A 19266-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5037,10 +5032,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45556</v>
+        <v>45428</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5053,7 +5048,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5096,7 +5091,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 59805-2024</t>
+          <t>A 52809-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5110,10 +5105,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45639</v>
+        <v>44875</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5125,8 +5120,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5169,7 +5169,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 8193-2023</t>
+          <t>A 3683-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5183,10 +5183,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44974</v>
+        <v>44950</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>10.5</v>
+        <v>6.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5247,7 +5247,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 8228-2023</t>
+          <t>A 1906-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44974</v>
+        <v>44575</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>13.9</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5320,7 +5320,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 37865-2026</t>
+          <t>A 59853-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5334,10 +5334,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46279</v>
+        <v>44908</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5349,13 +5349,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>9.1</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5398,7 +5393,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 51096-2024</t>
+          <t>A 8193-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5412,10 +5407,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45603</v>
+        <v>44974</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5427,8 +5422,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1.3</v>
+        <v>10.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5471,7 +5471,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 47123-2024</t>
+          <t>A 8228-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45586</v>
+        <v>44974</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>5.3</v>
+        <v>13.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5544,7 +5544,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 38308-2023</t>
+          <t>A 31883-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5558,10 +5558,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45161</v>
+        <v>44777</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5617,7 +5617,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 26029-2022</t>
+          <t>A 23574-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5631,10 +5631,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44734</v>
+        <v>45077</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5646,13 +5646,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>9.699999999999999</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5695,7 +5690,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 31883-2022</t>
+          <t>A 26382-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5709,10 +5704,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44777</v>
+        <v>45092</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5724,8 +5719,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>1.5</v>
+        <v>20.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5768,7 +5768,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 52789-2024</t>
+          <t>A 35521-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5782,10 +5782,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45610</v>
+        <v>46262</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5797,8 +5797,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>2.4</v>
+        <v>6.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5841,7 +5846,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 35521-2026</t>
+          <t>A 35459-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5858,7 +5863,7 @@
         <v>46262</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5870,13 +5875,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>6.2</v>
+        <v>3.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5919,7 +5919,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 35459-2026</t>
+          <t>A 52789-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5933,10 +5933,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46262</v>
+        <v>45610</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6009,7 +6009,7 @@
         <v>44628</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44880</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>46181</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44545</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 19420-2024</t>
+          <t>A 9813-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45429</v>
+        <v>44620</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2063,7 +2063,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 60754-2024</t>
+          <t>A 19082-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45644</v>
+        <v>45048</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2092,8 +2092,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>2.4</v>
+        <v>6.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2136,7 +2141,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 24023-2025</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2150,10 +2155,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45796</v>
+        <v>44491</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2166,7 +2171,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>6.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2209,7 +2214,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 9813-2022</t>
+          <t>A 1040-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2223,10 +2228,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44620</v>
+        <v>45666</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2239,7 +2244,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.3</v>
+        <v>1.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2282,7 +2287,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 41446-2023</t>
+          <t>A 40815-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2296,10 +2301,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45175</v>
+        <v>44824</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2311,13 +2316,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>8.4</v>
+        <v>15.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2360,7 +2360,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 30621-2023</t>
+          <t>A 11771-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45112</v>
+        <v>45727</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2433,7 +2433,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 30623-2023</t>
+          <t>A 52795-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45112</v>
+        <v>45226</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2506,7 +2506,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 1040-2025</t>
+          <t>A 52809-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45666</v>
+        <v>44875</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2535,8 +2535,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2579,7 +2584,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 52802-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2593,10 +2598,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44491</v>
+        <v>44875</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2608,8 +2613,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2652,7 +2662,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 51096-2024</t>
+          <t>A 6734-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2666,10 +2676,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45603</v>
+        <v>44602</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2682,7 +2692,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.3</v>
+        <v>32.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2725,7 +2735,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 40607-2024</t>
+          <t>A 16735-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2739,10 +2749,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45556</v>
+        <v>45030</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2755,7 +2765,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2798,7 +2808,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 11771-2025</t>
+          <t>A 1906-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2812,10 +2822,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45727</v>
+        <v>44575</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2828,7 +2838,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2871,7 +2881,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 6734-2022</t>
+          <t>A 30621-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2885,10 +2895,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44602</v>
+        <v>45112</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2901,7 +2911,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>32.3</v>
+        <v>3.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2944,7 +2954,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 10298-2026</t>
+          <t>A 30623-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2958,10 +2968,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46076</v>
+        <v>45112</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2974,7 +2984,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3017,7 +3027,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 30634-2023</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3031,10 +3041,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45112</v>
+        <v>44491</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3047,7 +3057,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3090,7 +3100,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 59805-2024</t>
+          <t>A 59853-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3104,10 +3114,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45639</v>
+        <v>44908</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3120,7 +3130,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3163,7 +3173,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 39717-2023</t>
+          <t>A 39269-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3177,10 +3187,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45167</v>
+        <v>45166</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3193,7 +3203,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3236,7 +3246,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 38308-2023</t>
+          <t>A 59612-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3250,10 +3260,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45161</v>
+        <v>44491</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3266,7 +3276,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3309,7 +3319,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 55003-2022</t>
+          <t>A 3683-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3323,10 +3333,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44886</v>
+        <v>44950</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3338,8 +3348,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3382,7 +3397,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 47123-2024</t>
+          <t>A 19266-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3396,10 +3411,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45586</v>
+        <v>45428</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3412,7 +3427,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3455,7 +3470,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 40815-2022</t>
+          <t>A 61260-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3469,10 +3484,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44824</v>
+        <v>46000</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3485,7 +3500,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>15.9</v>
+        <v>4.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3528,7 +3543,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33022-2025</t>
+          <t>A 23574-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3542,10 +3557,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45840</v>
+        <v>45077</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3558,7 +3573,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3601,7 +3616,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 61260-2025</t>
+          <t>A 41446-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3615,10 +3630,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46000</v>
+        <v>45175</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3630,8 +3645,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>4.4</v>
+        <v>8.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3691,7 +3711,7 @@
         <v>44623</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3764,7 +3784,7 @@
         <v>44623</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3820,7 +3840,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 52795-2023</t>
+          <t>A 39717-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3834,10 +3854,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45226</v>
+        <v>45167</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3850,7 +3870,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3893,7 +3913,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 16735-2023</t>
+          <t>A 33022-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3907,10 +3927,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45030</v>
+        <v>45840</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3923,7 +3943,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>8.699999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3966,7 +3986,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 19082-2023</t>
+          <t>A 30634-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3980,10 +4000,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45048</v>
+        <v>45112</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3995,13 +4015,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4044,7 +4059,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 26274-2026</t>
+          <t>A 26382-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4058,10 +4073,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46182</v>
+        <v>45092</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4073,8 +4088,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>20.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4117,7 +4137,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 26257-2026</t>
+          <t>A 55003-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4131,10 +4151,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46182</v>
+        <v>44886</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4147,7 +4167,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.3</v>
+        <v>6.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4190,7 +4210,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 27399-2026</t>
+          <t>A 59609-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4200,14 +4220,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46189</v>
+        <v>44491</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4220,7 +4240,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>12.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4263,7 +4283,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 27400-2026</t>
+          <t>A 26274-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4273,14 +4293,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46189</v>
+        <v>46182</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4293,7 +4313,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4336,7 +4356,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 26029-2022</t>
+          <t>A 26257-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4350,10 +4370,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44734</v>
+        <v>46182</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4365,13 +4385,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>9.699999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4414,7 +4429,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 59612-2021</t>
+          <t>A 27399-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4424,14 +4439,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44491</v>
+        <v>46189</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4444,7 +4459,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4487,7 +4502,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 52802-2022</t>
+          <t>A 27400-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4497,14 +4512,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44875</v>
+        <v>46189</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4516,13 +4531,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>5.8</v>
+        <v>3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4565,7 +4575,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 40607-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4579,10 +4589,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44491</v>
+        <v>45556</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4595,7 +4605,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>6.8</v>
+        <v>3.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4638,7 +4648,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 39269-2023</t>
+          <t>A 59805-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4652,10 +4662,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45166</v>
+        <v>45639</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4668,7 +4678,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4711,7 +4721,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 37045-2026</t>
+          <t>A 8193-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4725,10 +4735,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46273</v>
+        <v>44974</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4746,7 +4756,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4789,7 +4799,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 37054-2026</t>
+          <t>A 8228-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4803,10 +4813,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46273</v>
+        <v>44974</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4818,13 +4828,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>6.3</v>
+        <v>13.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4867,7 +4872,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 37865-2026</t>
+          <t>A 51096-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4881,10 +4886,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46279</v>
+        <v>45603</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4896,13 +4901,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>9.1</v>
+        <v>1.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4945,7 +4945,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 59609-2021</t>
+          <t>A 47123-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4959,10 +4959,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44491</v>
+        <v>45586</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>12.7</v>
+        <v>5.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5018,7 +5018,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 19266-2024</t>
+          <t>A 38308-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5032,10 +5032,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45428</v>
+        <v>45161</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5091,7 +5091,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 52809-2022</t>
+          <t>A 37054-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5105,10 +5105,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44875</v>
+        <v>46273</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.5</v>
+        <v>6.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5169,7 +5169,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 3683-2023</t>
+          <t>A 37045-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5183,10 +5183,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44950</v>
+        <v>46273</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>6.3</v>
+        <v>7.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5247,7 +5247,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 1906-2022</t>
+          <t>A 26029-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44575</v>
+        <v>44734</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5276,8 +5276,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5320,7 +5325,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 59853-2022</t>
+          <t>A 37865-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5334,10 +5339,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44908</v>
+        <v>46279</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5349,8 +5354,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>9.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5393,7 +5403,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 8193-2023</t>
+          <t>A 31883-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5407,10 +5417,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44974</v>
+        <v>44777</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5422,13 +5432,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>10.5</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5471,7 +5476,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 8228-2023</t>
+          <t>A 52789-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5485,10 +5490,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44974</v>
+        <v>45610</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5501,7 +5506,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>13.9</v>
+        <v>2.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5544,7 +5549,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 31883-2022</t>
+          <t>A 24023-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5558,10 +5563,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44777</v>
+        <v>45796</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5617,7 +5622,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 23574-2023</t>
+          <t>A 19420-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5631,10 +5636,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45077</v>
+        <v>45429</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5647,7 +5652,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5690,7 +5695,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 26382-2023</t>
+          <t>A 60754-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5704,10 +5709,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45092</v>
+        <v>45644</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5719,13 +5724,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>20.3</v>
+        <v>2.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5785,7 +5785,7 @@
         <v>46262</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>46262</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 52789-2024</t>
+          <t>A 10298-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5933,10 +5933,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45610</v>
+        <v>46076</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6009,7 +6009,7 @@
         <v>44628</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44880</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>46181</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44545</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44620</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 19082-2023</t>
+          <t>A 41446-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45048</v>
+        <v>45175</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>6.5</v>
+        <v>8.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2141,7 +2141,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 30621-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44491</v>
+        <v>45112</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>6.8</v>
+        <v>3.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2214,7 +2214,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 1040-2025</t>
+          <t>A 30623-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45666</v>
+        <v>45112</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2287,7 +2287,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 40815-2022</t>
+          <t>A 51096-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2301,10 +2301,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44824</v>
+        <v>45603</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>15.9</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2360,7 +2360,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 11771-2025</t>
+          <t>A 40607-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45727</v>
+        <v>45556</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2433,7 +2433,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 52795-2023</t>
+          <t>A 11771-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45226</v>
+        <v>45727</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2506,7 +2506,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 52809-2022</t>
+          <t>A 59805-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44875</v>
+        <v>45639</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2535,13 +2535,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2584,7 +2579,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 52802-2022</t>
+          <t>A 39717-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2598,10 +2593,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44875</v>
+        <v>45167</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2613,13 +2608,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>5.8</v>
+        <v>2.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2662,7 +2652,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 6734-2022</t>
+          <t>A 38308-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2676,10 +2666,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44602</v>
+        <v>45161</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2692,7 +2682,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>32.3</v>
+        <v>2.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2735,7 +2725,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 16735-2023</t>
+          <t>A 55003-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2749,10 +2739,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45030</v>
+        <v>44886</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2765,7 +2755,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>8.699999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2808,7 +2798,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 1906-2022</t>
+          <t>A 47123-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2822,10 +2812,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44575</v>
+        <v>45586</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2838,7 +2828,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>5.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2881,7 +2871,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 30621-2023</t>
+          <t>A 33022-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2895,10 +2885,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45112</v>
+        <v>45840</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2911,7 +2901,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2954,7 +2944,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 30623-2023</t>
+          <t>A 40815-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2968,10 +2958,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45112</v>
+        <v>44824</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2984,7 +2974,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.6</v>
+        <v>15.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3044,7 +3034,7 @@
         <v>44491</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3100,7 +3090,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 59853-2022</t>
+          <t>A 61260-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3114,10 +3104,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44908</v>
+        <v>46000</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3130,7 +3120,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>4.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3173,7 +3163,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 39269-2023</t>
+          <t>A 10516-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3187,10 +3177,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45166</v>
+        <v>44623</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3203,7 +3193,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3246,7 +3236,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 59612-2021</t>
+          <t>A 10517-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3260,10 +3250,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44491</v>
+        <v>44623</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3276,7 +3266,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3319,7 +3309,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 3683-2023</t>
+          <t>A 6734-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3333,10 +3323,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44950</v>
+        <v>44602</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3348,13 +3338,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>6.3</v>
+        <v>32.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3397,7 +3382,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 19266-2024</t>
+          <t>A 30634-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3411,10 +3396,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45428</v>
+        <v>45112</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3427,7 +3412,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.8</v>
+        <v>6.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3470,7 +3455,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 61260-2025</t>
+          <t>A 52795-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3484,10 +3469,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46000</v>
+        <v>45226</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3500,7 +3485,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3543,7 +3528,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 23574-2023</t>
+          <t>A 26274-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3557,10 +3542,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45077</v>
+        <v>46182</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3573,7 +3558,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3616,7 +3601,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 41446-2023</t>
+          <t>A 26257-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3630,10 +3615,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45175</v>
+        <v>46182</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3645,13 +3630,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>8.4</v>
+        <v>1.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3694,7 +3674,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 10516-2022</t>
+          <t>A 16735-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3708,10 +3688,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44623</v>
+        <v>45030</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3724,7 +3704,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3767,7 +3747,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 10517-2022</t>
+          <t>A 19082-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3781,10 +3761,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44623</v>
+        <v>45048</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3796,8 +3776,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>1.2</v>
+        <v>6.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3840,7 +3825,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 39717-2023</t>
+          <t>A 27399-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3850,14 +3835,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45167</v>
+        <v>46189</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3870,7 +3855,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3913,7 +3898,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 33022-2025</t>
+          <t>A 27400-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3923,14 +3908,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45840</v>
+        <v>46189</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3943,7 +3928,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3986,7 +3971,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 30634-2023</t>
+          <t>A 10298-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4000,10 +3985,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45112</v>
+        <v>46076</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4016,7 +4001,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>6.2</v>
+        <v>1.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4059,7 +4044,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 26382-2023</t>
+          <t>A 26029-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4073,10 +4058,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45092</v>
+        <v>44734</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4094,7 +4079,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>20.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4137,7 +4122,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 55003-2022</t>
+          <t>A 59612-2021</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4151,10 +4136,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44886</v>
+        <v>44491</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4167,7 +4152,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>6.6</v>
+        <v>3.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4210,7 +4195,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 59609-2021</t>
+          <t>A 52802-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4224,10 +4209,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44491</v>
+        <v>44875</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4239,8 +4224,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>12.7</v>
+        <v>5.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4283,7 +4273,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 26274-2026</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4297,10 +4287,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46182</v>
+        <v>44491</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4313,7 +4303,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>6.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4356,7 +4346,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 26257-2026</t>
+          <t>A 39269-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4370,10 +4360,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46182</v>
+        <v>45166</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4386,7 +4376,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4429,7 +4419,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 27399-2026</t>
+          <t>A 37045-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4439,14 +4429,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46189</v>
+        <v>46273</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4458,8 +4448,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>7.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4502,7 +4497,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 27400-2026</t>
+          <t>A 59609-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4512,14 +4507,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46189</v>
+        <v>44491</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4532,7 +4527,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3</v>
+        <v>12.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4575,7 +4570,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 40607-2024</t>
+          <t>A 37054-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4589,10 +4584,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45556</v>
+        <v>46273</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4604,8 +4599,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>3.2</v>
+        <v>6.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4648,7 +4648,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 59805-2024</t>
+          <t>A 19266-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4662,10 +4662,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45639</v>
+        <v>45428</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4721,7 +4721,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 8193-2023</t>
+          <t>A 37865-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44974</v>
+        <v>46279</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>10.5</v>
+        <v>9.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4799,7 +4799,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 8228-2023</t>
+          <t>A 52809-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44974</v>
+        <v>44875</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4828,8 +4828,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>13.9</v>
+        <v>2.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4872,7 +4877,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 51096-2024</t>
+          <t>A 3683-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4886,10 +4891,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45603</v>
+        <v>44950</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4901,8 +4906,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>1.3</v>
+        <v>6.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4945,7 +4955,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 47123-2024</t>
+          <t>A 1906-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4959,10 +4969,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45586</v>
+        <v>44575</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4975,7 +4985,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5.3</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5018,7 +5028,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 38308-2023</t>
+          <t>A 59853-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5032,10 +5042,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45161</v>
+        <v>44908</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5048,7 +5058,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5091,7 +5101,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 37054-2026</t>
+          <t>A 8193-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5105,10 +5115,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46273</v>
+        <v>44974</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5126,7 +5136,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>6.3</v>
+        <v>10.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5169,7 +5179,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 37045-2026</t>
+          <t>A 8228-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5183,10 +5193,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46273</v>
+        <v>44974</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5198,13 +5208,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>7.6</v>
+        <v>13.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5247,7 +5252,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 26029-2022</t>
+          <t>A 31883-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5261,10 +5266,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44734</v>
+        <v>44777</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5276,13 +5281,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>9.699999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5325,7 +5325,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 37865-2026</t>
+          <t>A 23574-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5339,10 +5339,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46279</v>
+        <v>45077</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5354,13 +5354,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>9.1</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5403,7 +5398,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 31883-2022</t>
+          <t>A 26382-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5417,10 +5412,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44777</v>
+        <v>45092</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5432,8 +5427,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>20.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5493,7 +5493,7 @@
         <v>45610</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 24023-2025</t>
+          <t>A 19420-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5563,10 +5563,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45796</v>
+        <v>45429</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5622,7 +5622,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 19420-2024</t>
+          <t>A 60754-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5636,10 +5636,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45429</v>
+        <v>45644</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5695,7 +5695,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 60754-2024</t>
+          <t>A 24023-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5709,10 +5709,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45644</v>
+        <v>45796</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5785,7 +5785,7 @@
         <v>46262</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>46262</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 10298-2026</t>
+          <t>A 1040-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5933,10 +5933,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46076</v>
+        <v>45666</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6009,7 +6009,7 @@
         <v>44628</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44880</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>46181</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44545</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44620</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>45175</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>45112</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>45112</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>45603</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>45556</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>45727</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>45639</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>45167</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         <v>45161</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>44886</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>45586</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>45840</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>44824</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>44491</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         <v>46000</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>44623</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>44623</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>44602</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>45112</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>45226</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>46182</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>46182</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>45030</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>45048</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>46189</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>46189</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>46076</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>44734</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>44491</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>44875</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>44491</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>45166</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>46273</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>44491</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>46273</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>45428</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>46279</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>44875</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>44950</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>44575</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>44908</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>44974</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>44974</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>44777</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>45077</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>45092</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>45610</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>45429</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5639,7 +5639,7 @@
         <v>45644</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>45796</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v>46262</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>46262</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>45666</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>44628</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44880</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>46181</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44545</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44620</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>45175</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>45112</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>45112</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>45603</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>45556</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>45727</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         <v>45639</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>45167</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         <v>45161</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>44886</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>45586</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>45840</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>44824</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>44491</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         <v>46000</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>44623</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>44623</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>44602</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>45112</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>45226</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>46182</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>46182</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>45030</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>45048</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>46189</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>46189</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>46076</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>44734</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>44491</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>44875</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>44491</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>45166</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>46273</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>44491</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>46273</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>45428</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>46279</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>44875</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>44950</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>44575</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>44908</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>44974</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>44974</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>44777</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>45077</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>45092</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>45610</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>45429</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5639,7 +5639,7 @@
         <v>45644</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>45796</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v>46262</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>46262</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>45666</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>44628</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 53870-2022</t>
+          <t>A 25961-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44880</v>
+        <v>46181</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1430,13 +1430,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>2.3</v>
+        <v>7.3</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1448,7 +1443,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1460,10 +1455,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1472,46 +1467,50 @@
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 25961-2026</t>
+          <t>A 53870-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1525,10 +1524,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46181</v>
+        <v>44880</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1540,8 +1539,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>7.3</v>
+        <v>2.3</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1553,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1565,10 +1569,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1577,43 +1581,39 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
-        <v/>
-      </c>
-      <c r="Z10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44545</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44620</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 41446-2023</t>
+          <t>A 19082-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45175</v>
+        <v>45048</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>8.4</v>
+        <v>6.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2141,7 +2141,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 30621-2023</t>
+          <t>A 40815-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45112</v>
+        <v>44824</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.2</v>
+        <v>15.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2214,7 +2214,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 30623-2023</t>
+          <t>A 52795-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45112</v>
+        <v>45226</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2287,7 +2287,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 51096-2024</t>
+          <t>A 52802-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2301,10 +2301,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45603</v>
+        <v>44875</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2316,8 +2316,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>5.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2360,7 +2365,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 40607-2024</t>
+          <t>A 6734-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2374,10 +2379,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45556</v>
+        <v>44602</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2390,7 +2395,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.2</v>
+        <v>32.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2433,7 +2438,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 11771-2025</t>
+          <t>A 30621-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2447,10 +2452,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45727</v>
+        <v>45112</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2463,7 +2468,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2506,7 +2511,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 59805-2024</t>
+          <t>A 30623-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2520,10 +2525,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45639</v>
+        <v>45112</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2536,7 +2541,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2579,7 +2584,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 39717-2023</t>
+          <t>A 59853-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2593,10 +2598,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45167</v>
+        <v>44908</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2609,7 +2614,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2652,7 +2657,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 38308-2023</t>
+          <t>A 3683-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2666,10 +2671,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45161</v>
+        <v>44950</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2681,8 +2686,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>2.9</v>
+        <v>6.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2725,7 +2735,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 55003-2022</t>
+          <t>A 23574-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2739,10 +2749,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44886</v>
+        <v>45077</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2755,7 +2765,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>6.6</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2798,7 +2808,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 47123-2024</t>
+          <t>A 41446-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2812,10 +2822,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45586</v>
+        <v>45175</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2827,8 +2837,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>5.3</v>
+        <v>8.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2871,7 +2886,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 33022-2025</t>
+          <t>A 30634-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2885,10 +2900,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45840</v>
+        <v>45112</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2901,7 +2916,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.5</v>
+        <v>6.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2944,7 +2959,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 40815-2022</t>
+          <t>A 26382-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2958,10 +2973,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44824</v>
+        <v>45092</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2973,8 +2988,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>15.9</v>
+        <v>20.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3034,7 +3054,7 @@
         <v>44491</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3090,7 +3110,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 61260-2025</t>
+          <t>A 33022-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3104,10 +3124,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46000</v>
+        <v>45840</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3120,7 +3140,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4.4</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3163,7 +3183,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 10516-2022</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3177,10 +3197,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44623</v>
+        <v>44491</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3193,7 +3213,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.1</v>
+        <v>6.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3236,7 +3256,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 10517-2022</t>
+          <t>A 11771-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3250,10 +3270,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44623</v>
+        <v>45727</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3266,7 +3286,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3309,7 +3329,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 6734-2022</t>
+          <t>A 52809-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3323,10 +3343,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44602</v>
+        <v>44875</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3338,8 +3358,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>32.3</v>
+        <v>2.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3382,7 +3407,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 30634-2023</t>
+          <t>A 16735-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3396,10 +3421,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45112</v>
+        <v>45030</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3412,7 +3437,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>6.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3455,7 +3480,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 52795-2023</t>
+          <t>A 1906-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3469,10 +3494,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45226</v>
+        <v>44575</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3485,7 +3510,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3528,7 +3553,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 26274-2026</t>
+          <t>A 39269-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3542,10 +3567,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46182</v>
+        <v>45166</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3558,7 +3583,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3601,7 +3626,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 26257-2026</t>
+          <t>A 59612-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3615,10 +3640,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46182</v>
+        <v>44491</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3631,7 +3656,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3674,7 +3699,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 16735-2023</t>
+          <t>A 19266-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3688,10 +3713,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45030</v>
+        <v>45428</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3704,7 +3729,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>8.699999999999999</v>
+        <v>3.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3747,7 +3772,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 19082-2023</t>
+          <t>A 10516-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3761,10 +3786,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45048</v>
+        <v>44623</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3776,13 +3801,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>6.5</v>
+        <v>2.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3825,7 +3845,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 27399-2026</t>
+          <t>A 10517-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3835,14 +3855,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46189</v>
+        <v>44623</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3855,7 +3875,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3898,7 +3918,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 27400-2026</t>
+          <t>A 39717-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3908,14 +3928,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46189</v>
+        <v>45167</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3928,7 +3948,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3971,7 +3991,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 10298-2026</t>
+          <t>A 26274-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3985,10 +4005,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46076</v>
+        <v>46182</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4001,7 +4021,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4044,7 +4064,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 26029-2022</t>
+          <t>A 26257-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4058,10 +4078,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44734</v>
+        <v>46182</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4073,13 +4093,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>9.699999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4122,7 +4137,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 59612-2021</t>
+          <t>A 10298-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4136,10 +4151,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44491</v>
+        <v>46076</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4152,7 +4167,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4195,7 +4210,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 52802-2022</t>
+          <t>A 27399-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4205,14 +4220,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44875</v>
+        <v>46189</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4224,13 +4239,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>5.8</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4273,7 +4283,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 27400-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4283,14 +4293,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44491</v>
+        <v>46189</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4303,7 +4313,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>6.8</v>
+        <v>3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4346,7 +4356,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 39269-2023</t>
+          <t>A 55003-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4360,10 +4370,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45166</v>
+        <v>44886</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4376,7 +4386,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.3</v>
+        <v>6.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4419,7 +4429,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 37045-2026</t>
+          <t>A 61260-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4433,10 +4443,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46273</v>
+        <v>46000</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4448,13 +4458,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>7.6</v>
+        <v>4.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4514,7 +4519,7 @@
         <v>44491</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4587,7 +4592,7 @@
         <v>46273</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4648,7 +4653,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 19266-2024</t>
+          <t>A 37045-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4662,10 +4667,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45428</v>
+        <v>46273</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4677,8 +4682,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>3.8</v>
+        <v>7.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4721,7 +4731,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 37865-2026</t>
+          <t>A 40607-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4735,10 +4745,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46279</v>
+        <v>45556</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4750,13 +4760,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>9.1</v>
+        <v>3.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4799,7 +4804,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 52809-2022</t>
+          <t>A 59805-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4813,10 +4818,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44875</v>
+        <v>45639</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4828,13 +4833,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4877,7 +4877,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 3683-2023</t>
+          <t>A 37865-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4891,10 +4891,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44950</v>
+        <v>46279</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>6.3</v>
+        <v>9.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 1906-2022</t>
+          <t>A 8193-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44575</v>
+        <v>44974</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4984,8 +4984,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>10.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5028,7 +5033,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 59853-2022</t>
+          <t>A 8228-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5042,10 +5047,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44908</v>
+        <v>44974</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5058,7 +5063,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.7</v>
+        <v>13.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5101,7 +5106,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 8193-2023</t>
+          <t>A 51096-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5115,10 +5120,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44974</v>
+        <v>45603</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5130,13 +5135,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>10.5</v>
+        <v>1.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5179,7 +5179,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 8228-2023</t>
+          <t>A 47123-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44974</v>
+        <v>45586</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>13.9</v>
+        <v>5.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5252,7 +5252,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 31883-2022</t>
+          <t>A 38308-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5266,10 +5266,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44777</v>
+        <v>45161</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5282,7 +5282,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5325,7 +5325,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 23574-2023</t>
+          <t>A 26029-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5339,10 +5339,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45077</v>
+        <v>44734</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5354,8 +5354,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5398,7 +5403,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 26382-2023</t>
+          <t>A 31883-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5412,10 +5417,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45092</v>
+        <v>44777</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5427,13 +5432,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>20.3</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5493,7 +5493,7 @@
         <v>45610</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 19420-2024</t>
+          <t>A 24023-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5563,10 +5563,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45429</v>
+        <v>45796</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5622,7 +5622,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 60754-2024</t>
+          <t>A 19420-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5636,10 +5636,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45644</v>
+        <v>45429</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5695,7 +5695,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 24023-2025</t>
+          <t>A 60754-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5709,10 +5709,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45796</v>
+        <v>45644</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5785,7 +5785,7 @@
         <v>46262</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>46262</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>45666</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>44628</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25961-2026</t>
+          <t>A 53870-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46181</v>
+        <v>44880</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1430,8 +1430,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>7.3</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1443,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1455,10 +1460,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1467,50 +1472,46 @@
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
-        <v/>
-      </c>
-      <c r="Z9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 53870-2022</t>
+          <t>A 25961-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1524,10 +1525,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44880</v>
+        <v>46181</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1539,13 +1540,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>2.3</v>
+        <v>7.3</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1557,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1569,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1581,39 +1577,43 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
+        <v/>
+      </c>
+      <c r="Z10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44545</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44620</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 19082-2023</t>
+          <t>A 41446-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45048</v>
+        <v>45175</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>6.5</v>
+        <v>8.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2141,7 +2141,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 40815-2022</t>
+          <t>A 30621-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44824</v>
+        <v>45112</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>15.9</v>
+        <v>3.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2214,7 +2214,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 52795-2023</t>
+          <t>A 30623-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45226</v>
+        <v>45112</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2287,7 +2287,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 52802-2022</t>
+          <t>A 51096-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2301,10 +2301,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44875</v>
+        <v>45603</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2316,13 +2316,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>5.8</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2365,7 +2360,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 6734-2022</t>
+          <t>A 40607-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2379,10 +2374,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44602</v>
+        <v>45556</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2395,7 +2390,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>32.3</v>
+        <v>3.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2438,7 +2433,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 30621-2023</t>
+          <t>A 19420-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2452,10 +2447,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45112</v>
+        <v>45429</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2468,7 +2463,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2511,7 +2506,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 30623-2023</t>
+          <t>A 60754-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2525,10 +2520,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45112</v>
+        <v>45644</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2541,7 +2536,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2584,7 +2579,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 59853-2022</t>
+          <t>A 24023-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2598,10 +2593,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44908</v>
+        <v>45796</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2614,7 +2609,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2657,7 +2652,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 3683-2023</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2671,10 +2666,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44950</v>
+        <v>44491</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2686,13 +2681,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>6.3</v>
+        <v>6.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2735,7 +2725,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 23574-2023</t>
+          <t>A 11771-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2749,10 +2739,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45077</v>
+        <v>45727</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2765,7 +2755,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2808,7 +2798,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 41446-2023</t>
+          <t>A 1040-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2822,10 +2812,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45175</v>
+        <v>45666</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2837,13 +2827,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>8.4</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2886,7 +2871,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 30634-2023</t>
+          <t>A 59805-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2900,10 +2885,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45112</v>
+        <v>45639</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2916,7 +2901,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>6.2</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2959,7 +2944,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 26382-2023</t>
+          <t>A 10298-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2973,10 +2958,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45092</v>
+        <v>46076</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2988,13 +2973,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>20.3</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3037,7 +3017,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 39717-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3051,10 +3031,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44491</v>
+        <v>45167</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3067,7 +3047,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>6.8</v>
+        <v>2.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3110,7 +3090,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33022-2025</t>
+          <t>A 38308-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3124,10 +3104,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45840</v>
+        <v>45161</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3140,7 +3120,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3183,7 +3163,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 55003-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3197,10 +3177,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44491</v>
+        <v>44886</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3213,7 +3193,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3256,7 +3236,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 11771-2025</t>
+          <t>A 47123-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3270,10 +3250,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45727</v>
+        <v>45586</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3286,7 +3266,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>5.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3329,7 +3309,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 52809-2022</t>
+          <t>A 40815-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3343,10 +3323,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44875</v>
+        <v>44824</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3358,13 +3338,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>2.5</v>
+        <v>15.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3407,7 +3382,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 16735-2023</t>
+          <t>A 33022-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3421,10 +3396,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45030</v>
+        <v>45840</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3437,7 +3412,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>8.699999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3480,7 +3455,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 1906-2022</t>
+          <t>A 61260-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3494,10 +3469,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44575</v>
+        <v>46000</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3510,7 +3485,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3553,7 +3528,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 39269-2023</t>
+          <t>A 10516-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3567,10 +3542,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45166</v>
+        <v>44623</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3583,7 +3558,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3626,7 +3601,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 59612-2021</t>
+          <t>A 10517-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3640,10 +3615,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44491</v>
+        <v>44623</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3656,7 +3631,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3699,7 +3674,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 19266-2024</t>
+          <t>A 6734-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3713,10 +3688,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45428</v>
+        <v>44602</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3729,7 +3704,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.8</v>
+        <v>32.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3772,7 +3747,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 10516-2022</t>
+          <t>A 30634-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3786,10 +3761,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44623</v>
+        <v>45112</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3802,7 +3777,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.1</v>
+        <v>6.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3845,7 +3820,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 10517-2022</t>
+          <t>A 52795-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3859,10 +3834,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44623</v>
+        <v>45226</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3875,7 +3850,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3918,7 +3893,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 39717-2023</t>
+          <t>A 26274-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3932,10 +3907,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45167</v>
+        <v>46182</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3948,7 +3923,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3991,7 +3966,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 26274-2026</t>
+          <t>A 26257-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4008,7 +3983,7 @@
         <v>46182</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4021,7 +3996,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4064,7 +4039,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 26257-2026</t>
+          <t>A 27399-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4074,14 +4049,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46182</v>
+        <v>46189</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4094,7 +4069,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4137,7 +4112,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 10298-2026</t>
+          <t>A 27400-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4147,14 +4122,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46076</v>
+        <v>46189</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4167,7 +4142,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4210,7 +4185,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 27399-2026</t>
+          <t>A 16735-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4220,14 +4195,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46189</v>
+        <v>45030</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4240,7 +4215,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4283,7 +4258,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 27400-2026</t>
+          <t>A 19082-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4293,14 +4268,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46189</v>
+        <v>45048</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4312,8 +4287,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>3</v>
+        <v>6.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4356,7 +4336,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 55003-2022</t>
+          <t>A 37865-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4370,10 +4350,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44886</v>
+        <v>46279</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4385,8 +4365,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>6.6</v>
+        <v>9.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4429,7 +4414,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 61260-2025</t>
+          <t>A 26029-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4443,10 +4428,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46000</v>
+        <v>44734</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4458,8 +4443,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>4.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4502,7 +4492,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 59609-2021</t>
+          <t>A 59612-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4519,7 +4509,7 @@
         <v>44491</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4532,7 +4522,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>12.7</v>
+        <v>3.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4575,7 +4565,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 37054-2026</t>
+          <t>A 52802-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4589,10 +4579,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46273</v>
+        <v>44875</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4610,7 +4600,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4653,7 +4643,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 37045-2026</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4667,10 +4657,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46273</v>
+        <v>44491</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4682,13 +4672,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4731,7 +4716,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 40607-2024</t>
+          <t>A 39269-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4745,10 +4730,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45556</v>
+        <v>45166</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4761,7 +4746,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4804,7 +4789,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 59805-2024</t>
+          <t>A 59609-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4818,10 +4803,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45639</v>
+        <v>44491</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4834,7 +4819,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3</v>
+        <v>12.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4877,7 +4862,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 37865-2026</t>
+          <t>A 19266-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4891,10 +4876,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46279</v>
+        <v>45428</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4906,13 +4891,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>9.1</v>
+        <v>3.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4955,7 +4935,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 8193-2023</t>
+          <t>A 52809-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4969,10 +4949,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44974</v>
+        <v>44875</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4990,7 +4970,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>10.5</v>
+        <v>2.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5033,7 +5013,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 8228-2023</t>
+          <t>A 35521-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5047,10 +5027,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44974</v>
+        <v>46262</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5062,8 +5042,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>13.9</v>
+        <v>6.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5106,7 +5091,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 51096-2024</t>
+          <t>A 35459-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5120,10 +5105,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45603</v>
+        <v>46262</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5136,7 +5121,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5179,7 +5164,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 47123-2024</t>
+          <t>A 3683-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5193,10 +5178,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45586</v>
+        <v>44950</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5208,8 +5193,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>5.3</v>
+        <v>6.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5252,7 +5242,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 38308-2023</t>
+          <t>A 1906-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5266,10 +5256,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45161</v>
+        <v>44575</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5282,7 +5272,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5325,7 +5315,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 26029-2022</t>
+          <t>A 37045-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5339,10 +5329,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44734</v>
+        <v>46273</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5360,7 +5350,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>9.699999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5403,7 +5393,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 31883-2022</t>
+          <t>A 59853-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5417,10 +5407,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44777</v>
+        <v>44908</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5433,7 +5423,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5476,7 +5466,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 52789-2024</t>
+          <t>A 37054-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5490,10 +5480,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45610</v>
+        <v>46273</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5505,8 +5495,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>2.4</v>
+        <v>6.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5549,7 +5544,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 24023-2025</t>
+          <t>A 8193-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5563,10 +5558,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45796</v>
+        <v>44974</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5578,8 +5573,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>1.5</v>
+        <v>10.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5622,7 +5622,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 19420-2024</t>
+          <t>A 8228-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5636,10 +5636,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45429</v>
+        <v>44974</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.8</v>
+        <v>13.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5695,7 +5695,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 60754-2024</t>
+          <t>A 31883-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5709,10 +5709,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45644</v>
+        <v>44777</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5768,7 +5768,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 35521-2026</t>
+          <t>A 23574-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5782,10 +5782,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46262</v>
+        <v>45077</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5797,13 +5797,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>6.2</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5846,7 +5841,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 35459-2026</t>
+          <t>A 26382-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5860,10 +5855,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46262</v>
+        <v>45092</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5875,8 +5870,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>3.5</v>
+        <v>20.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5919,7 +5919,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 1040-2025</t>
+          <t>A 52789-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5933,10 +5933,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45666</v>
+        <v>45610</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6009,7 +6009,7 @@
         <v>44628</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 53870-2022</t>
+          <t>A 25961-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44880</v>
+        <v>46181</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1430,13 +1430,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>2.3</v>
+        <v>7.3</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1448,7 +1443,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1460,10 +1455,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1472,46 +1467,50 @@
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 25961-2026</t>
+          <t>A 53870-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1525,10 +1524,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46181</v>
+        <v>44880</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1540,8 +1539,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>7.3</v>
+        <v>2.3</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1553,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1565,10 +1569,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1577,43 +1581,39 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
-        <v/>
-      </c>
-      <c r="Z10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44545</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44620</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 41446-2023</t>
+          <t>A 19082-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45175</v>
+        <v>45048</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>8.4</v>
+        <v>6.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2141,7 +2141,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 30621-2023</t>
+          <t>A 40815-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45112</v>
+        <v>44824</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.2</v>
+        <v>15.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2214,7 +2214,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 30623-2023</t>
+          <t>A 52795-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45112</v>
+        <v>45226</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2287,7 +2287,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 51096-2024</t>
+          <t>A 24023-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2301,10 +2301,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45603</v>
+        <v>45796</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2360,7 +2360,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 40607-2024</t>
+          <t>A 19420-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45556</v>
+        <v>45429</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2433,7 +2433,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 19420-2024</t>
+          <t>A 60754-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45429</v>
+        <v>45644</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2506,7 +2506,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 60754-2024</t>
+          <t>A 52802-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45644</v>
+        <v>44875</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2535,8 +2535,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>2.4</v>
+        <v>5.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2579,7 +2584,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 24023-2025</t>
+          <t>A 6734-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2593,10 +2598,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45796</v>
+        <v>44602</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2609,7 +2614,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.5</v>
+        <v>32.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2652,7 +2657,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 30621-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2666,10 +2671,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44491</v>
+        <v>45112</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2682,7 +2687,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>6.8</v>
+        <v>3.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2725,7 +2730,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 11771-2025</t>
+          <t>A 30623-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2739,10 +2744,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45727</v>
+        <v>45112</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2755,7 +2760,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2815,7 +2820,7 @@
         <v>45666</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2871,7 +2876,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 59805-2024</t>
+          <t>A 59853-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2885,10 +2890,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45639</v>
+        <v>44908</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2901,7 +2906,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2944,7 +2949,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 10298-2026</t>
+          <t>A 3683-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2958,10 +2963,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46076</v>
+        <v>44950</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2973,8 +2978,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>6.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3017,7 +3027,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 39717-2023</t>
+          <t>A 23574-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3031,10 +3041,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45167</v>
+        <v>45077</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3047,7 +3057,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3090,7 +3100,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 38308-2023</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3104,10 +3114,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45161</v>
+        <v>44491</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3120,7 +3130,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.9</v>
+        <v>6.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3163,7 +3173,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 55003-2022</t>
+          <t>A 41446-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3177,10 +3187,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44886</v>
+        <v>45175</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3192,8 +3202,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3236,7 +3251,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 47123-2024</t>
+          <t>A 30634-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3250,10 +3265,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45586</v>
+        <v>45112</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3266,7 +3281,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3309,7 +3324,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 40815-2022</t>
+          <t>A 26382-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3323,10 +3338,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44824</v>
+        <v>45092</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3338,8 +3353,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>15.9</v>
+        <v>20.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3382,7 +3402,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 33022-2025</t>
+          <t>A 10298-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3396,10 +3416,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45840</v>
+        <v>46076</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3455,7 +3475,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 61260-2025</t>
+          <t>A 59615-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3469,10 +3489,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46000</v>
+        <v>44491</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3485,7 +3505,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3528,7 +3548,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 10516-2022</t>
+          <t>A 11771-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3542,10 +3562,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44623</v>
+        <v>45727</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3558,7 +3578,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3601,7 +3621,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 10517-2022</t>
+          <t>A 52809-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3615,10 +3635,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44623</v>
+        <v>44875</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3630,8 +3650,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3674,7 +3699,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 6734-2022</t>
+          <t>A 61260-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3688,10 +3713,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44602</v>
+        <v>46000</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3704,7 +3729,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>32.3</v>
+        <v>4.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3747,7 +3772,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 30634-2023</t>
+          <t>A 16735-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3761,10 +3786,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45112</v>
+        <v>45030</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3777,7 +3802,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>6.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3820,7 +3845,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 52795-2023</t>
+          <t>A 1906-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3834,10 +3859,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45226</v>
+        <v>44575</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3850,7 +3875,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3893,7 +3918,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 26274-2026</t>
+          <t>A 33022-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3907,10 +3932,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46182</v>
+        <v>45840</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3923,7 +3948,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3966,7 +3991,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 26257-2026</t>
+          <t>A 39269-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3980,10 +4005,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46182</v>
+        <v>45166</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3996,7 +4021,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4039,7 +4064,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 27399-2026</t>
+          <t>A 59612-2021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4049,14 +4074,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46189</v>
+        <v>44491</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4069,7 +4094,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4112,7 +4137,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 27400-2026</t>
+          <t>A 19266-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4122,14 +4147,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46189</v>
+        <v>45428</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4142,7 +4167,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4185,7 +4210,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 16735-2023</t>
+          <t>A 10516-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4199,10 +4224,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45030</v>
+        <v>44623</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4215,7 +4240,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>8.699999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4258,7 +4283,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 19082-2023</t>
+          <t>A 10517-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4272,10 +4297,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45048</v>
+        <v>44623</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4287,13 +4312,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>6.5</v>
+        <v>1.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4336,7 +4356,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 37865-2026</t>
+          <t>A 39717-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4350,10 +4370,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46279</v>
+        <v>45167</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4365,13 +4385,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>9.1</v>
+        <v>2.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4414,7 +4429,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 26029-2022</t>
+          <t>A 26274-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4428,10 +4443,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44734</v>
+        <v>46182</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4443,13 +4458,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>9.699999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4492,7 +4502,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 59612-2021</t>
+          <t>A 26257-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4506,10 +4516,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44491</v>
+        <v>46182</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4522,7 +4532,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4565,7 +4575,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 52802-2022</t>
+          <t>A 55003-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4579,10 +4589,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44875</v>
+        <v>44886</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4594,13 +4604,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4643,7 +4648,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 27399-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4653,14 +4658,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44491</v>
+        <v>46189</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4673,7 +4678,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>6.8</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4716,7 +4721,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 39269-2023</t>
+          <t>A 27400-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4726,14 +4731,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45166</v>
+        <v>46189</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4746,7 +4751,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4806,7 +4811,7 @@
         <v>44491</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4862,7 +4867,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 19266-2024</t>
+          <t>A 40607-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4876,10 +4881,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45428</v>
+        <v>45556</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4892,7 +4897,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4935,7 +4940,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 52809-2022</t>
+          <t>A 59805-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4949,10 +4954,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44875</v>
+        <v>45639</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4964,13 +4969,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5013,7 +5013,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 35521-2026</t>
+          <t>A 37865-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5027,10 +5027,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46262</v>
+        <v>46279</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>6.2</v>
+        <v>9.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5091,7 +5091,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 35459-2026</t>
+          <t>A 8193-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5105,10 +5105,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46262</v>
+        <v>44974</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5120,8 +5120,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>3.5</v>
+        <v>10.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5164,7 +5169,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 3683-2023</t>
+          <t>A 8228-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5178,10 +5183,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44950</v>
+        <v>44974</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5193,13 +5198,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>6.3</v>
+        <v>13.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5242,7 +5242,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 1906-2022</t>
+          <t>A 51096-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5256,10 +5256,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44575</v>
+        <v>45603</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5315,7 +5315,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 37045-2026</t>
+          <t>A 47123-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5329,10 +5329,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46273</v>
+        <v>45586</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5344,13 +5344,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5393,7 +5388,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 59853-2022</t>
+          <t>A 38308-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5407,10 +5402,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44908</v>
+        <v>45161</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5423,7 +5418,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5466,7 +5461,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 37054-2026</t>
+          <t>A 26029-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5480,10 +5475,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46273</v>
+        <v>44734</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5501,7 +5496,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>6.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5544,7 +5539,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 8193-2023</t>
+          <t>A 31883-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5558,10 +5553,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44974</v>
+        <v>44777</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5573,13 +5568,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>10.5</v>
+        <v>1.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5622,7 +5612,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 8228-2023</t>
+          <t>A 52789-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5636,10 +5626,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44974</v>
+        <v>45610</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5652,7 +5642,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>13.9</v>
+        <v>2.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5695,7 +5685,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 31883-2022</t>
+          <t>A 35521-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5709,10 +5699,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44777</v>
+        <v>46262</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5724,8 +5714,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>1.5</v>
+        <v>6.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5768,7 +5763,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 23574-2023</t>
+          <t>A 35459-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5782,10 +5777,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45077</v>
+        <v>46262</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5798,7 +5793,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5841,7 +5836,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 26382-2023</t>
+          <t>A 37045-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5855,10 +5850,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45092</v>
+        <v>46273</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5876,7 +5871,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>20.3</v>
+        <v>7.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5919,7 +5914,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 52789-2024</t>
+          <t>A 37054-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5933,10 +5928,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45610</v>
+        <v>46273</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5948,8 +5943,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>2.4</v>
+        <v>6.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6009,7 +6009,7 @@
         <v>44628</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE70"/>
+  <dimension ref="A1:AE66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25961-2026</t>
+          <t>A 53870-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46181</v>
+        <v>44880</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1430,8 +1430,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>7.3</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1443,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1455,10 +1460,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1467,50 +1472,46 @@
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
-        <v/>
-      </c>
-      <c r="Z9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 53870-2022</t>
+          <t>A 25961-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1524,10 +1525,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44880</v>
+        <v>46181</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1539,13 +1540,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>2.3</v>
+        <v>7.3</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1557,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1569,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1581,39 +1577,43 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
+        <v/>
+      </c>
+      <c r="Z10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44545</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44620</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 19082-2023</t>
+          <t>A 16735-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45048</v>
+        <v>45030</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2092,13 +2092,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>6.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2141,7 +2136,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 40815-2022</t>
+          <t>A 19082-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2155,10 +2150,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44824</v>
+        <v>45048</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2170,8 +2165,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>15.9</v>
+        <v>6.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2214,7 +2214,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 52795-2023</t>
+          <t>A 41446-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45226</v>
+        <v>45175</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2243,8 +2243,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>3.7</v>
+        <v>8.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2287,7 +2292,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 24023-2025</t>
+          <t>A 30621-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2301,10 +2306,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45796</v>
+        <v>45112</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2317,7 +2322,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2360,7 +2365,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 19420-2024</t>
+          <t>A 30623-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2374,10 +2379,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45429</v>
+        <v>45112</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2390,7 +2395,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2433,7 +2438,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 60754-2024</t>
+          <t>A 51096-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2447,10 +2452,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45644</v>
+        <v>45603</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2463,7 +2468,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2506,7 +2511,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 52802-2022</t>
+          <t>A 1040-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2520,10 +2525,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44875</v>
+        <v>45666</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2535,13 +2540,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>5.8</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2584,7 +2584,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 6734-2022</t>
+          <t>A 26029-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44602</v>
+        <v>44734</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2613,8 +2613,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>32.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2657,7 +2662,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 30621-2023</t>
+          <t>A 52802-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2671,10 +2676,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45112</v>
+        <v>44875</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2686,8 +2691,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>3.2</v>
+        <v>5.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2730,7 +2740,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 30623-2023</t>
+          <t>A 40607-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2744,10 +2754,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45112</v>
+        <v>45556</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2760,7 +2770,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2803,7 +2813,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 1040-2025</t>
+          <t>A 39269-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2817,10 +2827,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45666</v>
+        <v>45166</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2833,7 +2843,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2876,7 +2886,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 59853-2022</t>
+          <t>A 11771-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2890,10 +2900,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44908</v>
+        <v>45727</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2906,7 +2916,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2949,7 +2959,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 3683-2023</t>
+          <t>A 33022-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2963,10 +2973,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44950</v>
+        <v>45840</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2978,13 +2988,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>6.3</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3027,7 +3032,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 23574-2023</t>
+          <t>A 61260-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3041,10 +3046,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45077</v>
+        <v>46000</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3057,7 +3062,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3100,7 +3105,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 19266-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3114,10 +3119,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44491</v>
+        <v>45428</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3130,7 +3135,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>6.8</v>
+        <v>3.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3173,7 +3178,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 41446-2023</t>
+          <t>A 52809-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3187,10 +3192,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45175</v>
+        <v>44875</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3208,7 +3213,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>8.4</v>
+        <v>2.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3251,7 +3256,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 30634-2023</t>
+          <t>A 3683-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3265,10 +3270,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45112</v>
+        <v>44950</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3280,8 +3285,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3324,7 +3334,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 26382-2023</t>
+          <t>A 1906-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3338,10 +3348,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45092</v>
+        <v>44575</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3353,13 +3363,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>20.3</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3402,7 +3407,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10298-2026</t>
+          <t>A 59853-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3416,10 +3421,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46076</v>
+        <v>44908</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3432,7 +3437,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3475,7 +3480,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 59615-2021</t>
+          <t>A 8193-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3489,10 +3494,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44491</v>
+        <v>44974</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3504,8 +3509,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3548,7 +3558,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 11771-2025</t>
+          <t>A 8228-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3562,10 +3572,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45727</v>
+        <v>44974</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3578,7 +3588,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.9</v>
+        <v>13.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3621,7 +3631,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 52809-2022</t>
+          <t>A 31883-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3635,10 +3645,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44875</v>
+        <v>44777</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3650,13 +3660,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3699,7 +3704,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 61260-2025</t>
+          <t>A 23574-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3713,10 +3718,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46000</v>
+        <v>45077</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3729,7 +3734,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3772,7 +3777,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 16735-2023</t>
+          <t>A 26382-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3786,10 +3791,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45030</v>
+        <v>45092</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3801,8 +3806,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>8.699999999999999</v>
+        <v>20.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3845,7 +3855,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 1906-2022</t>
+          <t>A 26274-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3859,10 +3869,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44575</v>
+        <v>46182</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3875,7 +3885,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3918,7 +3928,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 33022-2025</t>
+          <t>A 26257-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3932,10 +3942,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45840</v>
+        <v>46182</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3948,7 +3958,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3991,7 +4001,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 39269-2023</t>
+          <t>A 52789-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4005,10 +4015,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45166</v>
+        <v>45610</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4021,7 +4031,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4064,7 +4074,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 59612-2021</t>
+          <t>A 27399-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4074,14 +4084,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44491</v>
+        <v>46189</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4094,7 +4104,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4137,7 +4147,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 19266-2024</t>
+          <t>A 27400-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4147,14 +4157,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45428</v>
+        <v>46189</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4167,7 +4177,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4210,7 +4220,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 10516-2022</t>
+          <t>A 19420-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4224,10 +4234,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44623</v>
+        <v>45429</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4240,7 +4250,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4283,7 +4293,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 10517-2022</t>
+          <t>A 60754-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4297,10 +4307,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44623</v>
+        <v>45644</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4313,7 +4323,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4356,7 +4366,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 39717-2023</t>
+          <t>A 10298-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4370,10 +4380,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45167</v>
+        <v>46076</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4386,7 +4396,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4429,7 +4439,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 26274-2026</t>
+          <t>A 24023-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4443,10 +4453,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46182</v>
+        <v>45796</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4459,7 +4469,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4502,7 +4512,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26257-2026</t>
+          <t>A 59805-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4516,10 +4526,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46182</v>
+        <v>45639</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4532,7 +4542,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4575,7 +4585,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 55003-2022</t>
+          <t>A 37045-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4589,10 +4599,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44886</v>
+        <v>46273</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4604,8 +4614,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4648,7 +4663,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 27399-2026</t>
+          <t>A 37054-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4658,14 +4673,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46189</v>
+        <v>46273</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4677,8 +4692,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>6.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4721,7 +4741,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 27400-2026</t>
+          <t>A 37865-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4731,14 +4751,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46189</v>
+        <v>46279</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4750,8 +4770,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>9.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4794,7 +4819,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 59609-2021</t>
+          <t>A 39717-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4808,10 +4833,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44491</v>
+        <v>45167</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4824,7 +4849,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>12.7</v>
+        <v>2.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4867,7 +4892,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 40607-2024</t>
+          <t>A 38308-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4881,10 +4906,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45556</v>
+        <v>45161</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4897,7 +4922,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4940,7 +4965,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 59805-2024</t>
+          <t>A 55003-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4954,10 +4979,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45639</v>
+        <v>44886</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4970,7 +4995,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>6.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5013,7 +5038,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 37865-2026</t>
+          <t>A 47123-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5027,10 +5052,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46279</v>
+        <v>45586</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5042,13 +5067,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>9.1</v>
+        <v>5.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5091,7 +5111,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 8193-2023</t>
+          <t>A 40815-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5105,10 +5125,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44974</v>
+        <v>44824</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5120,13 +5140,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>10.5</v>
+        <v>15.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5169,7 +5184,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 8228-2023</t>
+          <t>A 10516-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5183,10 +5198,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44974</v>
+        <v>44623</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5199,7 +5214,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>13.9</v>
+        <v>2.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5242,7 +5257,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 51096-2024</t>
+          <t>A 10517-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5256,10 +5271,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45603</v>
+        <v>44623</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5272,7 +5287,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5315,7 +5330,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 47123-2024</t>
+          <t>A 6734-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5329,10 +5344,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45586</v>
+        <v>44602</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5345,7 +5360,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>5.3</v>
+        <v>32.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5388,7 +5403,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 38308-2023</t>
+          <t>A 35521-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5402,10 +5417,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45161</v>
+        <v>46262</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5417,8 +5432,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>2.9</v>
+        <v>6.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5461,7 +5481,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 26029-2022</t>
+          <t>A 30634-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5475,10 +5495,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44734</v>
+        <v>45112</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5490,13 +5510,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>9.699999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5539,7 +5554,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 31883-2022</t>
+          <t>A 35459-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5553,10 +5568,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44777</v>
+        <v>46262</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5569,7 +5584,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5612,7 +5627,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 52789-2024</t>
+          <t>A 52795-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5626,10 +5641,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45610</v>
+        <v>45226</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5642,7 +5657,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5682,27 +5697,27 @@
       </c>
       <c r="V65" s="2" t="inlineStr"/>
     </row>
-    <row r="66" ht="15" customHeight="1">
+    <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 35521-2026</t>
+          <t>S 1310-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46262</v>
+        <v>44628</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5714,13 +5729,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>6.2</v>
+        <v>36.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5759,308 +5769,6 @@
         <v>0</v>
       </c>
       <c r="V66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67" ht="15" customHeight="1">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>A 35459-2026</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D67" s="1" t="n">
-        <v>46262</v>
-      </c>
-      <c r="E67" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>KUNGSÖR</t>
-        </is>
-      </c>
-      <c r="I67" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J67" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" t="n">
-        <v>0</v>
-      </c>
-      <c r="O67" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
-      <c r="R67" t="n">
-        <v>0</v>
-      </c>
-      <c r="S67" t="n">
-        <v>0</v>
-      </c>
-      <c r="T67" t="n">
-        <v>0</v>
-      </c>
-      <c r="U67" t="n">
-        <v>0</v>
-      </c>
-      <c r="V67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68" ht="15" customHeight="1">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>A 37045-2026</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D68" s="1" t="n">
-        <v>46273</v>
-      </c>
-      <c r="E68" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>KUNGSÖR</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I68" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="J68" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
-      <c r="R68" t="n">
-        <v>0</v>
-      </c>
-      <c r="S68" t="n">
-        <v>0</v>
-      </c>
-      <c r="T68" t="n">
-        <v>0</v>
-      </c>
-      <c r="U68" t="n">
-        <v>0</v>
-      </c>
-      <c r="V68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69" ht="15" customHeight="1">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>A 37054-2026</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D69" s="1" t="n">
-        <v>46273</v>
-      </c>
-      <c r="E69" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>KUNGSÖR</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I69" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="J69" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" t="n">
-        <v>0</v>
-      </c>
-      <c r="P69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
-      <c r="R69" t="n">
-        <v>0</v>
-      </c>
-      <c r="S69" t="n">
-        <v>0</v>
-      </c>
-      <c r="T69" t="n">
-        <v>0</v>
-      </c>
-      <c r="U69" t="n">
-        <v>0</v>
-      </c>
-      <c r="V69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>S 1310-2022</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Skogsgödsling</t>
-        </is>
-      </c>
-      <c r="D70" s="1" t="n">
-        <v>44628</v>
-      </c>
-      <c r="E70" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>KUNGSÖR</t>
-        </is>
-      </c>
-      <c r="I70" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
-      <c r="R70" t="n">
-        <v>0</v>
-      </c>
-      <c r="S70" t="n">
-        <v>0</v>
-      </c>
-      <c r="T70" t="n">
-        <v>0</v>
-      </c>
-      <c r="U70" t="n">
-        <v>0</v>
-      </c>
-      <c r="V70" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 53870-2022</t>
+          <t>A 25961-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44880</v>
+        <v>46181</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1430,13 +1430,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>2.3</v>
+        <v>7.3</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1448,7 +1443,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1460,10 +1455,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1472,46 +1467,50 @@
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 25961-2026</t>
+          <t>A 53870-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1525,10 +1524,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46181</v>
+        <v>44880</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1540,8 +1539,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>7.3</v>
+        <v>2.3</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1553,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1565,10 +1569,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1577,43 +1581,39 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
-        <v/>
-      </c>
-      <c r="Z10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44545</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44620</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 16735-2023</t>
+          <t>A 19082-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45030</v>
+        <v>45048</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2092,8 +2092,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>8.699999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2136,7 +2141,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 19082-2023</t>
+          <t>A 40607-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2150,10 +2155,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45048</v>
+        <v>45556</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2165,13 +2170,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>6.5</v>
+        <v>3.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2214,7 +2214,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 41446-2023</t>
+          <t>A 59805-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45175</v>
+        <v>45639</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2243,13 +2243,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>8.4</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2292,7 +2287,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 30621-2023</t>
+          <t>A 8193-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2306,10 +2301,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45112</v>
+        <v>44974</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2321,8 +2316,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>3.2</v>
+        <v>10.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2365,7 +2365,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 30623-2023</t>
+          <t>A 8228-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45112</v>
+        <v>44974</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.6</v>
+        <v>13.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2455,7 +2455,7 @@
         <v>45603</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 1040-2025</t>
+          <t>A 40815-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2525,10 +2525,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45666</v>
+        <v>44824</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>15.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2584,7 +2584,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 26029-2022</t>
+          <t>A 47123-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44734</v>
+        <v>45586</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2613,13 +2613,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>9.699999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2662,7 +2657,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 52802-2022</t>
+          <t>A 26274-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2676,10 +2671,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44875</v>
+        <v>46182</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2691,13 +2686,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>5.8</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2740,7 +2730,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 40607-2024</t>
+          <t>A 38308-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2754,10 +2744,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45556</v>
+        <v>45161</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2770,7 +2760,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2813,7 +2803,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 39269-2023</t>
+          <t>A 26257-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2827,10 +2817,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45166</v>
+        <v>46182</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2843,7 +2833,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2886,7 +2876,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 11771-2025</t>
+          <t>A 27399-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2896,14 +2886,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45727</v>
+        <v>46189</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2916,7 +2906,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2959,7 +2949,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 33022-2025</t>
+          <t>A 27400-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2969,14 +2959,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45840</v>
+        <v>46189</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2989,7 +2979,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3032,7 +3022,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 61260-2025</t>
+          <t>A 52795-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3046,10 +3036,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46000</v>
+        <v>45226</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3062,7 +3052,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3105,7 +3095,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 19266-2024</t>
+          <t>A 26029-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3119,10 +3109,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45428</v>
+        <v>44734</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3134,8 +3124,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>3.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3178,7 +3173,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 52809-2022</t>
+          <t>A 31883-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3192,10 +3187,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44875</v>
+        <v>44777</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3207,13 +3202,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3256,7 +3246,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 3683-2023</t>
+          <t>A 52789-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3270,10 +3260,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44950</v>
+        <v>45610</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3285,13 +3275,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>6.3</v>
+        <v>2.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3334,7 +3319,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 1906-2022</t>
+          <t>A 37865-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3348,10 +3333,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44575</v>
+        <v>46279</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3363,8 +3348,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>9.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3407,7 +3397,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 59853-2022</t>
+          <t>A 24023-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3421,10 +3411,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44908</v>
+        <v>45796</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3437,7 +3427,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3480,7 +3470,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 8193-2023</t>
+          <t>A 19420-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3494,10 +3484,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44974</v>
+        <v>45429</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3509,13 +3499,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>10.5</v>
+        <v>3.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3558,7 +3543,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 8228-2023</t>
+          <t>A 60754-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3572,10 +3557,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44974</v>
+        <v>45644</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3588,7 +3573,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>13.9</v>
+        <v>2.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3631,7 +3616,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 31883-2022</t>
+          <t>A 1040-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3645,10 +3630,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44777</v>
+        <v>45666</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3661,7 +3646,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3704,7 +3689,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 23574-2023</t>
+          <t>A 10298-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3718,10 +3703,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45077</v>
+        <v>46076</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3734,7 +3719,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3777,7 +3762,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 26382-2023</t>
+          <t>A 52802-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3791,10 +3776,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45092</v>
+        <v>44875</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3812,7 +3797,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>20.3</v>
+        <v>5.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3855,7 +3840,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 26274-2026</t>
+          <t>A 6734-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3869,10 +3854,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46182</v>
+        <v>44602</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3885,7 +3870,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.7</v>
+        <v>32.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3928,7 +3913,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 26257-2026</t>
+          <t>A 35521-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3942,10 +3927,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46182</v>
+        <v>46262</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3957,8 +3942,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>1.3</v>
+        <v>6.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4001,7 +3991,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 52789-2024</t>
+          <t>A 35459-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4015,10 +4005,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45610</v>
+        <v>46262</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4031,7 +4021,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4074,7 +4064,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 27399-2026</t>
+          <t>A 30621-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4084,14 +4074,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46189</v>
+        <v>45112</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4104,7 +4094,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4147,7 +4137,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 27400-2026</t>
+          <t>A 30623-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4157,14 +4147,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46189</v>
+        <v>45112</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4177,7 +4167,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4220,7 +4210,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 19420-2024</t>
+          <t>A 59853-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4234,10 +4224,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45429</v>
+        <v>44908</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4250,7 +4240,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4293,7 +4283,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 60754-2024</t>
+          <t>A 61260-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4307,10 +4297,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45644</v>
+        <v>46000</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4323,7 +4313,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4366,7 +4356,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 10298-2026</t>
+          <t>A 33022-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4380,10 +4370,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46076</v>
+        <v>45840</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4439,7 +4429,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 24023-2025</t>
+          <t>A 37045-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4453,10 +4443,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45796</v>
+        <v>46273</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4468,8 +4458,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>1.5</v>
+        <v>7.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4512,7 +4507,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 59805-2024</t>
+          <t>A 37054-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4526,10 +4521,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45639</v>
+        <v>46273</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4541,8 +4536,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>3</v>
+        <v>6.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4585,7 +4585,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 37045-2026</t>
+          <t>A 3683-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46273</v>
+        <v>44950</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>7.6</v>
+        <v>6.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4663,7 +4663,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 37054-2026</t>
+          <t>A 23574-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46273</v>
+        <v>45077</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4692,13 +4692,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>6.3</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4741,7 +4736,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 37865-2026</t>
+          <t>A 41446-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4755,10 +4750,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46279</v>
+        <v>45175</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4776,7 +4771,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>9.1</v>
+        <v>8.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4819,7 +4814,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 39717-2023</t>
+          <t>A 30634-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4833,10 +4828,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45167</v>
+        <v>45112</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4849,7 +4844,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.3</v>
+        <v>6.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4892,7 +4887,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 38308-2023</t>
+          <t>A 26382-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4906,10 +4901,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45161</v>
+        <v>45092</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4921,8 +4916,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>2.9</v>
+        <v>20.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4965,7 +4965,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 55003-2022</t>
+          <t>A 11771-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4979,10 +4979,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44886</v>
+        <v>45727</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>6.6</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 47123-2024</t>
+          <t>A 52809-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5052,10 +5052,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45586</v>
+        <v>44875</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5067,8 +5067,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>5.3</v>
+        <v>2.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5111,7 +5116,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 40815-2022</t>
+          <t>A 16735-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5125,10 +5130,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44824</v>
+        <v>45030</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5141,7 +5146,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>15.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5184,7 +5189,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 10516-2022</t>
+          <t>A 1906-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5198,10 +5203,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44623</v>
+        <v>44575</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5214,7 +5219,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5257,7 +5262,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 10517-2022</t>
+          <t>A 39269-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5271,10 +5276,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44623</v>
+        <v>45166</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5287,7 +5292,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5330,7 +5335,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 6734-2022</t>
+          <t>A 19266-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5344,10 +5349,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44602</v>
+        <v>45428</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5360,7 +5365,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>32.3</v>
+        <v>3.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5403,7 +5408,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 35521-2026</t>
+          <t>A 10516-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5417,10 +5422,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46262</v>
+        <v>44623</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5432,13 +5437,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>6.2</v>
+        <v>2.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 30634-2023</t>
+          <t>A 10517-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5495,10 +5495,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45112</v>
+        <v>44623</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>6.2</v>
+        <v>1.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5554,7 +5554,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 35459-2026</t>
+          <t>A 39717-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5568,10 +5568,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46262</v>
+        <v>45167</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5627,7 +5627,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 52795-2023</t>
+          <t>A 55003-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5641,10 +5641,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45226</v>
+        <v>44886</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.7</v>
+        <v>6.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5717,7 +5717,7 @@
         <v>44628</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>46181</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>44880</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44545</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44620</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>45048</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>45556</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>45639</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>44974</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>44974</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>45603</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>44824</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>45586</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>46182</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>45161</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>46182</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>46189</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>46189</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>45226</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>44734</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>44777</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>45610</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>46279</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>45796</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>45429</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>45644</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45666</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>46076</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>44875</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>44602</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>46262</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>46262</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>45112</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>45112</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>44908</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>46000</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>45840</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>46273</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>46273</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>44950</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>45077</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>45175</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>45112</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>45092</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>45727</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>44875</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>45030</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
         <v>44575</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>45166</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>45428</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>44623</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>44623</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>45167</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>44886</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>44628</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>46181</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>44880</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44545</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44620</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>45048</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>45556</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>45639</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>44974</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>44974</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>45603</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>44824</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>45586</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>46182</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>45161</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>46182</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>46189</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>46189</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>45226</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>44734</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>44777</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>45610</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>46279</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>45796</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>45429</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>45644</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45666</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>46076</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>44875</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>44602</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>46262</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>46262</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>45112</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>45112</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>44908</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>46000</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>45840</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>46273</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>46273</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>44950</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>45077</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>45175</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>45112</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>45092</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>45727</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>44875</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>45030</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
         <v>44575</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>45166</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>45428</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>44623</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>44623</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>45167</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>44886</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>44628</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25961-2026</t>
+          <t>A 53870-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46181</v>
+        <v>44880</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1430,8 +1430,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>7.3</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1443,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1455,10 +1460,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1467,50 +1472,46 @@
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
-        <v/>
-      </c>
-      <c r="Z9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 53870-2022</t>
+          <t>A 25961-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1524,10 +1525,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44880</v>
+        <v>46181</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1539,13 +1540,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>2.3</v>
+        <v>7.3</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1557,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1569,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1581,39 +1577,43 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 53870-2022 artfynd.xlsx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/artfynd/A 25961-2026 artfynd.xlsx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 53870-2022 karta.png", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor/A 25961-2026 karta.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 53870-2022 georefererad karta.tif", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/kartor_geotiff/A 25961-2026 georefererad karta.tif", "A 25961-2026")</f>
+        <v/>
+      </c>
+      <c r="Z10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/knärot/A 25961-2026 karta knärot.png", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 53870-2022 FSC-klagomål.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomål/A 25961-2026 FSC-klagomål.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 53870-2022 FSC-klagomål mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/klagomålsmail/A 25961-2026 FSC-klagomål mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 53870-2022 tillsynsbegäran.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsyn/A 25961-2026 tillsynsbegäran.docx", "A 25961-2026")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 53870-2022 tillsynsbegäran mail.docx", "A 53870-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1960/tillsynsmail/A 25961-2026 tillsynsbegäran mail.docx", "A 25961-2026")</f>
         <v/>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44545</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>44620</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 19082-2023</t>
+          <t>A 1906-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45048</v>
+        <v>44575</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2092,13 +2092,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>6.5</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2141,7 +2136,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 40607-2024</t>
+          <t>A 41446-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2155,10 +2150,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45556</v>
+        <v>45175</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2170,8 +2165,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>3.2</v>
+        <v>8.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2214,7 +2214,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 59805-2024</t>
+          <t>A 30621-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45639</v>
+        <v>45112</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2287,7 +2287,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 8193-2023</t>
+          <t>A 30623-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2301,10 +2301,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44974</v>
+        <v>45112</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2316,13 +2316,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>10.5</v>
+        <v>2.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2365,7 +2360,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 8228-2023</t>
+          <t>A 59853-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2379,10 +2374,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44974</v>
+        <v>44908</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2395,7 +2390,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>13.9</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2438,7 +2433,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 51096-2024</t>
+          <t>A 8193-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2452,10 +2447,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45603</v>
+        <v>44974</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2467,8 +2462,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>1.3</v>
+        <v>10.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2511,7 +2511,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 40815-2022</t>
+          <t>A 8228-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2525,10 +2525,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44824</v>
+        <v>44974</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>15.9</v>
+        <v>13.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2584,7 +2584,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 47123-2024</t>
+          <t>A 27399-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2594,14 +2594,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45586</v>
+        <v>46189</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5.3</v>
+        <v>1.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2657,7 +2657,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 26274-2026</t>
+          <t>A 51096-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46182</v>
+        <v>45603</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2730,7 +2730,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 38308-2023</t>
+          <t>A 31883-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45161</v>
+        <v>44777</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2803,7 +2803,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 26257-2026</t>
+          <t>A 27400-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2813,14 +2813,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46182</v>
+        <v>46189</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2876,7 +2876,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 27399-2026</t>
+          <t>A 40607-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2886,14 +2886,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46189</v>
+        <v>45556</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2949,7 +2949,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 27400-2026</t>
+          <t>A 23574-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2959,14 +2959,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46189</v>
+        <v>45077</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3022,7 +3022,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 52795-2023</t>
+          <t>A 11771-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3036,10 +3036,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45226</v>
+        <v>45727</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3095,7 +3095,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 26029-2022</t>
+          <t>A 26382-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3109,10 +3109,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44734</v>
+        <v>45092</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>9.699999999999999</v>
+        <v>20.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3173,7 +3173,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 31883-2022</t>
+          <t>A 52789-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44777</v>
+        <v>45610</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3246,7 +3246,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 52789-2024</t>
+          <t>A 19420-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3260,10 +3260,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45610</v>
+        <v>45429</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3319,7 +3319,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 37865-2026</t>
+          <t>A 60754-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3333,10 +3333,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46279</v>
+        <v>45644</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3348,13 +3348,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>9.1</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3414,7 +3409,7 @@
         <v>45796</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3470,7 +3465,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 19420-2024</t>
+          <t>A 59805-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3484,10 +3479,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45429</v>
+        <v>45639</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3500,7 +3495,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3543,7 +3538,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60754-2024</t>
+          <t>A 1040-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3557,10 +3552,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45644</v>
+        <v>45666</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3573,7 +3568,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3616,7 +3611,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 1040-2025</t>
+          <t>A 39717-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3630,10 +3625,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45666</v>
+        <v>45167</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3646,7 +3641,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3689,7 +3684,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 10298-2026</t>
+          <t>A 38308-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3703,10 +3698,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46076</v>
+        <v>45161</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3719,7 +3714,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3762,7 +3757,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 52802-2022</t>
+          <t>A 55003-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3776,10 +3771,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44875</v>
+        <v>44886</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3791,13 +3786,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3840,7 +3830,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 6734-2022</t>
+          <t>A 47123-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3854,10 +3844,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44602</v>
+        <v>45586</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3870,7 +3860,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>32.3</v>
+        <v>5.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3913,7 +3903,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 35521-2026</t>
+          <t>A 40815-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3927,10 +3917,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46262</v>
+        <v>44824</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3942,13 +3932,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>6.2</v>
+        <v>15.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3991,7 +3976,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 35459-2026</t>
+          <t>A 10516-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4005,10 +3990,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46262</v>
+        <v>44623</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4021,7 +4006,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4064,7 +4049,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 30621-2023</t>
+          <t>A 10517-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4078,10 +4063,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45112</v>
+        <v>44623</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4094,7 +4079,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4137,7 +4122,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 30623-2023</t>
+          <t>A 10298-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4151,10 +4136,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45112</v>
+        <v>46076</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4167,7 +4152,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4210,7 +4195,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 59853-2022</t>
+          <t>A 6734-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4224,10 +4209,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44908</v>
+        <v>44602</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4240,7 +4225,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>32.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4283,7 +4268,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 61260-2025</t>
+          <t>A 30634-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4297,10 +4282,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46000</v>
+        <v>45112</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4313,7 +4298,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4373,7 +4358,7 @@
         <v>45840</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4429,7 +4414,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 37045-2026</t>
+          <t>A 52795-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4443,10 +4428,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46273</v>
+        <v>45226</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4458,13 +4443,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>7.6</v>
+        <v>3.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4507,7 +4487,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 37054-2026</t>
+          <t>A 61260-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4521,10 +4501,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46273</v>
+        <v>46000</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4536,13 +4516,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>6.3</v>
+        <v>4.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4585,7 +4560,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 3683-2023</t>
+          <t>A 16735-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4599,10 +4574,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44950</v>
+        <v>45030</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4614,13 +4589,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>6.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4663,7 +4633,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 23574-2023</t>
+          <t>A 19082-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4677,10 +4647,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45077</v>
+        <v>45048</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4692,8 +4662,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4736,7 +4711,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 41446-2023</t>
+          <t>A 26029-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4750,10 +4725,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45175</v>
+        <v>44734</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4771,7 +4746,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>8.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4814,7 +4789,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 30634-2023</t>
+          <t>A 52802-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4828,10 +4803,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45112</v>
+        <v>44875</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4843,8 +4818,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4887,7 +4867,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 26382-2023</t>
+          <t>A 26274-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4901,10 +4881,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45092</v>
+        <v>46182</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4916,13 +4896,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>20.3</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4965,7 +4940,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 11771-2025</t>
+          <t>A 26257-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4979,10 +4954,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45727</v>
+        <v>46182</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4995,7 +4970,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5038,7 +5013,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 52809-2022</t>
+          <t>A 39269-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5052,10 +5027,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44875</v>
+        <v>45166</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5067,13 +5042,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5116,7 +5086,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 16735-2023</t>
+          <t>A 35521-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5130,10 +5100,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45030</v>
+        <v>46262</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5145,8 +5115,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>8.699999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5189,7 +5164,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 1906-2022</t>
+          <t>A 35459-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5203,10 +5178,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44575</v>
+        <v>46262</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5219,7 +5194,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5262,7 +5237,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 39269-2023</t>
+          <t>A 19266-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5276,10 +5251,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45166</v>
+        <v>45428</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5292,7 +5267,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5335,7 +5310,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 19266-2024</t>
+          <t>A 52809-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5349,10 +5324,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45428</v>
+        <v>44875</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5364,8 +5339,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5408,7 +5388,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 10516-2022</t>
+          <t>A 3683-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5422,10 +5402,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44623</v>
+        <v>44950</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5437,8 +5417,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>2.1</v>
+        <v>6.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5481,7 +5466,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 10517-2022</t>
+          <t>A 37045-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5495,10 +5480,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44623</v>
+        <v>46273</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5510,8 +5495,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>1.2</v>
+        <v>7.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5554,7 +5544,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 39717-2023</t>
+          <t>A 37054-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5568,10 +5558,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45167</v>
+        <v>46273</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5583,8 +5573,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>2.3</v>
+        <v>6.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5627,7 +5622,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 55003-2022</t>
+          <t>A 37865-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5641,10 +5636,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44886</v>
+        <v>46279</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5656,8 +5651,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>6.6</v>
+        <v>9.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5717,7 +5717,7 @@
         <v>44628</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44880</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>46181</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44545</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 9813-2022</t>
+          <t>A 23574-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44620</v>
+        <v>45077</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.3</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2063,7 +2063,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 1906-2022</t>
+          <t>A 41446-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44575</v>
+        <v>45175</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2092,8 +2092,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>8.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2136,7 +2141,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 41446-2023</t>
+          <t>A 9813-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2150,10 +2155,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45175</v>
+        <v>44620</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2165,13 +2170,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>8.4</v>
+        <v>4.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2214,7 +2214,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 30621-2023</t>
+          <t>A 19082-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45112</v>
+        <v>45048</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2243,8 +2243,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2287,7 +2292,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 30623-2023</t>
+          <t>A 31883-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2301,10 +2306,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45112</v>
+        <v>44777</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2317,7 +2322,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2360,7 +2365,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 59853-2022</t>
+          <t>A 30634-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2374,10 +2379,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44908</v>
+        <v>45112</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2390,7 +2395,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>6.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2433,7 +2438,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 8193-2023</t>
+          <t>A 26382-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2447,10 +2452,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44974</v>
+        <v>45092</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2468,7 +2473,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>10.5</v>
+        <v>20.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2511,7 +2516,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 8228-2023</t>
+          <t>A 40815-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2525,10 +2530,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44974</v>
+        <v>44824</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2541,7 +2546,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>13.9</v>
+        <v>15.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2584,7 +2589,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 27399-2026</t>
+          <t>A 52795-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2594,14 +2599,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46189</v>
+        <v>45226</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2614,7 +2619,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2657,7 +2662,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 51096-2024</t>
+          <t>A 52802-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2671,10 +2676,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45603</v>
+        <v>44875</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2686,8 +2691,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.3</v>
+        <v>5.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2730,7 +2740,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 31883-2022</t>
+          <t>A 6734-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2744,10 +2754,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44777</v>
+        <v>44602</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2760,7 +2770,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>32.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2803,7 +2813,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 27400-2026</t>
+          <t>A 11771-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2813,14 +2823,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46189</v>
+        <v>45727</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2833,7 +2843,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2876,7 +2886,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 40607-2024</t>
+          <t>A 30621-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2890,10 +2900,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45556</v>
+        <v>45112</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2949,7 +2959,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 23574-2023</t>
+          <t>A 30623-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2963,10 +2973,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45077</v>
+        <v>45112</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2979,7 +2989,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3022,7 +3032,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 11771-2025</t>
+          <t>A 52809-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3036,10 +3046,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45727</v>
+        <v>44875</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3051,8 +3061,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3095,7 +3110,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 26382-2023</t>
+          <t>A 59853-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3109,10 +3124,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45092</v>
+        <v>44908</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3124,13 +3139,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>20.3</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3173,7 +3183,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 52789-2024</t>
+          <t>A 16735-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3187,10 +3197,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45610</v>
+        <v>45030</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3203,7 +3213,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3246,7 +3256,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 19420-2024</t>
+          <t>A 1906-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3260,10 +3270,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45429</v>
+        <v>44575</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3276,7 +3286,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3319,7 +3329,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 60754-2024</t>
+          <t>A 3683-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3333,10 +3343,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45644</v>
+        <v>44950</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3348,8 +3358,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>6.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3392,7 +3407,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 24023-2025</t>
+          <t>A 52789-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3406,10 +3421,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45796</v>
+        <v>45610</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3422,7 +3437,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3465,7 +3480,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 59805-2024</t>
+          <t>A 39269-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3479,10 +3494,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45639</v>
+        <v>45166</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3495,7 +3510,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3538,7 +3553,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 1040-2025</t>
+          <t>A 19266-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3552,10 +3567,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45666</v>
+        <v>45428</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3568,7 +3583,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3611,7 +3626,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 39717-2023</t>
+          <t>A 24023-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3625,10 +3640,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45167</v>
+        <v>45796</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3641,7 +3656,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3684,7 +3699,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 38308-2023</t>
+          <t>A 10516-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3698,10 +3713,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45161</v>
+        <v>44623</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3714,7 +3729,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3757,7 +3772,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 55003-2022</t>
+          <t>A 10517-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3771,10 +3786,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44886</v>
+        <v>44623</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3787,7 +3802,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>6.6</v>
+        <v>1.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3830,7 +3845,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 47123-2024</t>
+          <t>A 19420-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3844,10 +3859,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45586</v>
+        <v>45429</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3860,7 +3875,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3903,7 +3918,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 40815-2022</t>
+          <t>A 60754-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3917,10 +3932,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44824</v>
+        <v>45644</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3933,7 +3948,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>15.9</v>
+        <v>2.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3976,7 +3991,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 10516-2022</t>
+          <t>A 39717-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3990,10 +4005,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44623</v>
+        <v>45167</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4006,7 +4021,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4049,7 +4064,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 10517-2022</t>
+          <t>A 10298-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4063,10 +4078,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44623</v>
+        <v>46076</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4079,7 +4094,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4122,7 +4137,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 10298-2026</t>
+          <t>A 55003-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4136,10 +4151,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46076</v>
+        <v>44886</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4152,7 +4167,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.5</v>
+        <v>6.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4195,7 +4210,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 6734-2022</t>
+          <t>A 61260-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4209,10 +4224,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44602</v>
+        <v>46000</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4225,7 +4240,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>32.3</v>
+        <v>4.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4268,7 +4283,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 30634-2023</t>
+          <t>A 35521-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4282,10 +4297,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45112</v>
+        <v>46262</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4295,6 +4310,11 @@
       <c r="G47" t="inlineStr">
         <is>
           <t>KUNGSÖR</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -4341,7 +4361,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 33022-2025</t>
+          <t>A 35459-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4355,10 +4375,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45840</v>
+        <v>46262</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4371,7 +4391,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4414,7 +4434,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 52795-2023</t>
+          <t>A 40607-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4428,10 +4448,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45226</v>
+        <v>45556</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4444,7 +4464,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4487,7 +4507,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 61260-2025</t>
+          <t>A 59805-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4501,10 +4521,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46000</v>
+        <v>45639</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4517,7 +4537,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4560,7 +4580,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 16735-2023</t>
+          <t>A 8193-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4574,10 +4594,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45030</v>
+        <v>44974</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4589,8 +4609,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>8.699999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4633,7 +4658,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 19082-2023</t>
+          <t>A 8228-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4647,10 +4672,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45048</v>
+        <v>44974</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4662,13 +4687,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>6.5</v>
+        <v>13.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4711,7 +4731,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 26029-2022</t>
+          <t>A 51096-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4725,10 +4745,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44734</v>
+        <v>45603</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4740,13 +4760,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>9.699999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4789,7 +4804,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 52802-2022</t>
+          <t>A 1040-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4803,10 +4818,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44875</v>
+        <v>45666</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4818,13 +4833,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>5.8</v>
+        <v>1.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4867,7 +4877,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 26274-2026</t>
+          <t>A 33022-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4881,10 +4891,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46182</v>
+        <v>45840</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4897,7 +4907,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4940,7 +4950,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 26257-2026</t>
+          <t>A 47123-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4954,10 +4964,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46182</v>
+        <v>45586</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4970,7 +4980,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.3</v>
+        <v>5.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5013,7 +5023,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 39269-2023</t>
+          <t>A 38308-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5027,10 +5037,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45166</v>
+        <v>45161</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5043,7 +5053,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5086,7 +5096,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 35521-2026</t>
+          <t>A 37045-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5100,10 +5110,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46262</v>
+        <v>46273</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5121,7 +5131,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5164,7 +5174,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 35459-2026</t>
+          <t>A 37054-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5178,10 +5188,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46262</v>
+        <v>46273</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5193,8 +5203,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>3.5</v>
+        <v>6.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5237,7 +5252,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 19266-2024</t>
+          <t>A 26029-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5251,10 +5266,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45428</v>
+        <v>44734</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5266,8 +5281,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>3.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5310,7 +5330,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 52809-2022</t>
+          <t>A 37865-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5324,10 +5344,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44875</v>
+        <v>46279</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5345,7 +5365,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.5</v>
+        <v>9.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5388,7 +5408,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 3683-2023</t>
+          <t>A 26274-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5402,10 +5422,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44950</v>
+        <v>46182</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5417,13 +5437,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>6.3</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5466,7 +5481,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 37045-2026</t>
+          <t>A 26257-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5480,10 +5495,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46273</v>
+        <v>46182</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5495,13 +5510,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>7.6</v>
+        <v>1.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5544,7 +5554,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 37054-2026</t>
+          <t>A 27399-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5554,14 +5564,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46273</v>
+        <v>46189</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5573,13 +5583,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>6.3</v>
+        <v>1.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5622,7 +5627,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 37865-2026</t>
+          <t>A 27400-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5632,14 +5637,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46279</v>
+        <v>46189</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5651,13 +5656,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>9.1</v>
+        <v>3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5717,7 +5717,7 @@
         <v>44628</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44880</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>46181</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44545</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 23574-2023</t>
+          <t>A 30634-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45077</v>
+        <v>45112</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>6.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2063,7 +2063,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 41446-2023</t>
+          <t>A 9813-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45175</v>
+        <v>44620</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2092,13 +2092,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>8.4</v>
+        <v>4.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2141,7 +2136,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 9813-2022</t>
+          <t>A 19420-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2155,10 +2150,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44620</v>
+        <v>45429</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2171,7 +2166,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2214,7 +2209,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 19082-2023</t>
+          <t>A 60754-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2228,10 +2223,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45048</v>
+        <v>45644</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2243,13 +2238,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>6.5</v>
+        <v>2.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2292,7 +2282,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 31883-2022</t>
+          <t>A 52795-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2306,10 +2296,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44777</v>
+        <v>45226</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2322,7 +2312,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2365,7 +2355,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 30634-2023</t>
+          <t>A 24023-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2379,10 +2369,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45112</v>
+        <v>45796</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2395,7 +2385,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>6.2</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2438,7 +2428,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 26382-2023</t>
+          <t>A 41446-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2452,10 +2442,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45092</v>
+        <v>45175</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2473,7 +2463,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>20.3</v>
+        <v>8.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2516,7 +2506,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 40815-2022</t>
+          <t>A 30621-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2530,10 +2520,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44824</v>
+        <v>45112</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2546,7 +2536,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>15.9</v>
+        <v>3.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2589,7 +2579,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 52795-2023</t>
+          <t>A 30623-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2603,10 +2593,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45226</v>
+        <v>45112</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2619,7 +2609,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2662,7 +2652,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 52802-2022</t>
+          <t>A 1040-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2676,10 +2666,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44875</v>
+        <v>45666</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2691,13 +2681,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>5.8</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2740,7 +2725,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 6734-2022</t>
+          <t>A 16735-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2754,10 +2739,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44602</v>
+        <v>45030</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2770,7 +2755,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>32.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2813,7 +2798,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 11771-2025</t>
+          <t>A 19082-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2827,10 +2812,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45727</v>
+        <v>45048</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2842,8 +2827,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>6.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2886,7 +2876,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 30621-2023</t>
+          <t>A 51096-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2900,10 +2890,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45112</v>
+        <v>45603</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2916,7 +2906,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2959,7 +2949,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 30623-2023</t>
+          <t>A 26029-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2973,10 +2963,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45112</v>
+        <v>44734</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2988,8 +2978,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>2.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3032,7 +3027,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 52809-2022</t>
+          <t>A 52802-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3049,7 +3044,7 @@
         <v>44875</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3067,7 +3062,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.5</v>
+        <v>5.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3110,7 +3105,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 59853-2022</t>
+          <t>A 39269-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3124,10 +3119,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44908</v>
+        <v>45166</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3140,7 +3135,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3183,7 +3178,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 16735-2023</t>
+          <t>A 40607-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3197,10 +3192,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45030</v>
+        <v>45556</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3213,7 +3208,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>8.699999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3256,7 +3251,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 1906-2022</t>
+          <t>A 11771-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3270,10 +3265,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44575</v>
+        <v>45727</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3286,7 +3281,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3329,7 +3324,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 3683-2023</t>
+          <t>A 19266-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3343,10 +3338,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44950</v>
+        <v>45428</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3358,13 +3353,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>6.3</v>
+        <v>3.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3407,7 +3397,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 52789-2024</t>
+          <t>A 52809-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3421,10 +3411,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45610</v>
+        <v>44875</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3436,8 +3426,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3480,7 +3475,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 39269-2023</t>
+          <t>A 3683-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3494,10 +3489,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45166</v>
+        <v>44950</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3509,8 +3504,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>3.3</v>
+        <v>6.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3553,7 +3553,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 19266-2024</t>
+          <t>A 26274-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3567,10 +3567,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45428</v>
+        <v>46182</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3626,7 +3626,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 24023-2025</t>
+          <t>A 26257-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45796</v>
+        <v>46182</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3699,7 +3699,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 10516-2022</t>
+          <t>A 1906-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3713,10 +3713,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44623</v>
+        <v>44575</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3772,7 +3772,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 10517-2022</t>
+          <t>A 27399-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3782,14 +3782,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44623</v>
+        <v>46189</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3845,7 +3845,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 19420-2024</t>
+          <t>A 27400-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3855,14 +3855,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45429</v>
+        <v>46189</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3918,7 +3918,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 60754-2024</t>
+          <t>A 59853-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45644</v>
+        <v>44908</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3991,7 +3991,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 39717-2023</t>
+          <t>A 8193-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45167</v>
+        <v>44974</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4020,8 +4020,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>2.3</v>
+        <v>10.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4064,7 +4069,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 10298-2026</t>
+          <t>A 8228-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4078,10 +4083,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46076</v>
+        <v>44974</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4094,7 +4099,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.5</v>
+        <v>13.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4137,7 +4142,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 55003-2022</t>
+          <t>A 31883-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4151,10 +4156,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44886</v>
+        <v>44777</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4167,7 +4172,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>6.6</v>
+        <v>1.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4210,7 +4215,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 61260-2025</t>
+          <t>A 10298-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4224,10 +4229,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46000</v>
+        <v>46076</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4240,7 +4245,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.4</v>
+        <v>1.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4283,7 +4288,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 35521-2026</t>
+          <t>A 23574-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4297,10 +4302,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46262</v>
+        <v>45077</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4312,13 +4317,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>6.2</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4361,7 +4361,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 35459-2026</t>
+          <t>A 26382-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4375,10 +4375,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46262</v>
+        <v>45092</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4390,8 +4390,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>3.5</v>
+        <v>20.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4434,7 +4439,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 40607-2024</t>
+          <t>A 52789-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4448,10 +4453,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45556</v>
+        <v>45610</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4464,7 +4469,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4507,7 +4512,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 59805-2024</t>
+          <t>A 33022-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4521,10 +4526,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45639</v>
+        <v>45840</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4537,7 +4542,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4580,7 +4585,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 8193-2023</t>
+          <t>A 61260-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4594,10 +4599,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44974</v>
+        <v>46000</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4609,13 +4614,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>10.5</v>
+        <v>4.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 8228-2023</t>
+          <t>A 59805-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4672,10 +4672,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44974</v>
+        <v>45639</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>13.9</v>
+        <v>3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4731,7 +4731,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 51096-2024</t>
+          <t>A 39717-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45603</v>
+        <v>45167</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4804,7 +4804,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 1040-2025</t>
+          <t>A 38308-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4818,10 +4818,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45666</v>
+        <v>45161</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4877,7 +4877,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 33022-2025</t>
+          <t>A 55003-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4891,10 +4891,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45840</v>
+        <v>44886</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.5</v>
+        <v>6.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4967,7 +4967,7 @@
         <v>45586</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 38308-2023</t>
+          <t>A 40815-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5037,10 +5037,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45161</v>
+        <v>44824</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.9</v>
+        <v>15.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 37045-2026</t>
+          <t>A 35521-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5110,10 +5110,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46273</v>
+        <v>46262</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5174,7 +5174,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 37054-2026</t>
+          <t>A 35459-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5188,10 +5188,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46273</v>
+        <v>46262</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5203,13 +5203,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>6.3</v>
+        <v>3.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5252,7 +5247,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 26029-2022</t>
+          <t>A 10516-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5266,10 +5261,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44734</v>
+        <v>44623</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5281,13 +5276,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>9.699999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5330,7 +5320,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 37865-2026</t>
+          <t>A 10517-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5344,10 +5334,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46279</v>
+        <v>44623</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5359,13 +5349,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>9.1</v>
+        <v>1.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5408,7 +5393,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 26274-2026</t>
+          <t>A 37045-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5422,10 +5407,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46182</v>
+        <v>46273</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5437,8 +5422,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>7.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5481,7 +5471,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 26257-2026</t>
+          <t>A 37054-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5495,10 +5485,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46182</v>
+        <v>46273</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5510,8 +5500,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>6.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5554,7 +5549,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 27399-2026</t>
+          <t>A 37865-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5564,14 +5559,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46189</v>
+        <v>46279</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5583,8 +5578,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>9.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5627,7 +5627,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 27400-2026</t>
+          <t>A 6734-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5637,14 +5637,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46189</v>
+        <v>44602</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3</v>
+        <v>32.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5717,7 +5717,7 @@
         <v>44628</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>

--- a/Översikt KUNGSÖR.xlsx
+++ b/Översikt KUNGSÖR.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE66"/>
+  <dimension ref="A1:AE68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45714</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>45709</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>44904</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45644</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45349</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46038</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44880</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>46181</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>44677</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44602</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>44803</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>44545</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>44600</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 30634-2023</t>
+          <t>A 9813-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45112</v>
+        <v>44620</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>6.2</v>
+        <v>4.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2063,7 +2063,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 9813-2022</t>
+          <t>A 41446-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44620</v>
+        <v>45175</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2092,8 +2092,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>4.3</v>
+        <v>8.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2136,7 +2141,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 19420-2024</t>
+          <t>A 30621-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2150,10 +2155,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45429</v>
+        <v>45112</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2166,7 +2171,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2209,7 +2214,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 60754-2024</t>
+          <t>A 30623-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2223,10 +2228,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45644</v>
+        <v>45112</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2239,7 +2244,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2282,7 +2287,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 52795-2023</t>
+          <t>A 51096-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2296,10 +2301,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45226</v>
+        <v>45603</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2312,7 +2317,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2355,7 +2360,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 24023-2025</t>
+          <t>A 40607-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2369,10 +2374,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45796</v>
+        <v>45556</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2385,7 +2390,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2428,7 +2433,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 41446-2023</t>
+          <t>A 11771-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2442,10 +2447,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45175</v>
+        <v>45727</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2457,13 +2462,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>8.4</v>
+        <v>0.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2506,7 +2506,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 30621-2023</t>
+          <t>A 1040-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2520,10 +2520,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45112</v>
+        <v>45666</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2579,7 +2579,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 30623-2023</t>
+          <t>A 59805-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45112</v>
+        <v>45639</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2652,7 +2652,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 1040-2025</t>
+          <t>A 39717-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45666</v>
+        <v>45167</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2725,7 +2725,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 16735-2023</t>
+          <t>A 38308-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45030</v>
+        <v>45161</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>8.699999999999999</v>
+        <v>2.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2798,7 +2798,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 19082-2023</t>
+          <t>A 55003-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2812,10 +2812,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45048</v>
+        <v>44886</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2827,13 +2827,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2876,7 +2871,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 51096-2024</t>
+          <t>A 47123-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2890,10 +2885,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45603</v>
+        <v>45586</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2906,7 +2901,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.3</v>
+        <v>5.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2949,7 +2944,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 26029-2022</t>
+          <t>A 40815-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2963,10 +2958,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44734</v>
+        <v>44824</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2978,13 +2973,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>9.699999999999999</v>
+        <v>15.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3027,7 +3017,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 52802-2022</t>
+          <t>A 10516-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3041,10 +3031,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44875</v>
+        <v>44623</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3056,13 +3046,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>5.8</v>
+        <v>2.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3105,7 +3090,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 39269-2023</t>
+          <t>A 10517-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3119,10 +3104,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45166</v>
+        <v>44623</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3135,7 +3120,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3178,7 +3163,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 40607-2024</t>
+          <t>A 10298-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3192,10 +3177,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45556</v>
+        <v>46076</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3208,7 +3193,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3251,7 +3236,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 11771-2025</t>
+          <t>A 6734-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3265,10 +3250,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45727</v>
+        <v>44602</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3281,7 +3266,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>32.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3324,7 +3309,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 19266-2024</t>
+          <t>A 30634-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3338,10 +3323,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45428</v>
+        <v>45112</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3354,7 +3339,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.8</v>
+        <v>6.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3397,7 +3382,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 52809-2022</t>
+          <t>A 52795-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3411,10 +3396,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44875</v>
+        <v>45226</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3426,13 +3411,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3475,7 +3455,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 3683-2023</t>
+          <t>A 33022-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3489,10 +3469,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44950</v>
+        <v>45840</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3504,13 +3484,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>6.3</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3553,7 +3528,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 26274-2026</t>
+          <t>A 61260-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3567,10 +3542,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46182</v>
+        <v>46000</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3583,7 +3558,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.7</v>
+        <v>4.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3626,7 +3601,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 26257-2026</t>
+          <t>A 16735-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3640,10 +3615,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46182</v>
+        <v>45030</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3656,7 +3631,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3699,7 +3674,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 1906-2022</t>
+          <t>A 19082-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3713,10 +3688,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44575</v>
+        <v>45048</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3728,8 +3703,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3772,7 +3752,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 27399-2026</t>
+          <t>A 26029-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3782,14 +3762,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46189</v>
+        <v>44734</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3801,8 +3781,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>1.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3845,7 +3830,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 27400-2026</t>
+          <t>A 52802-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3855,14 +3840,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46189</v>
+        <v>44875</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3874,8 +3859,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3918,7 +3908,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 59853-2022</t>
+          <t>A 39269-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3932,10 +3922,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44908</v>
+        <v>45166</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3948,7 +3938,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3991,7 +3981,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 8193-2023</t>
+          <t>A 26274-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4005,10 +3995,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44974</v>
+        <v>46182</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4020,13 +4010,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>10.5</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4069,7 +4054,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 8228-2023</t>
+          <t>A 26257-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4083,10 +4068,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44974</v>
+        <v>46182</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4099,7 +4084,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>13.9</v>
+        <v>1.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4142,7 +4127,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 31883-2022</t>
+          <t>A 27399-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4152,14 +4137,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44777</v>
+        <v>46189</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4172,7 +4157,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4215,7 +4200,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 10298-2026</t>
+          <t>A 27400-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4225,14 +4210,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46076</v>
+        <v>46189</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4245,7 +4230,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4288,7 +4273,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 23574-2023</t>
+          <t>A 19266-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4302,10 +4287,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45077</v>
+        <v>45428</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4318,7 +4303,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4361,7 +4346,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 26382-2023</t>
+          <t>A 52809-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4375,10 +4360,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45092</v>
+        <v>44875</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4396,7 +4381,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>20.3</v>
+        <v>2.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4439,7 +4424,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 52789-2024</t>
+          <t>A 3683-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4453,10 +4438,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45610</v>
+        <v>44950</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4468,8 +4453,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>2.4</v>
+        <v>6.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4512,7 +4502,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 33022-2025</t>
+          <t>A 1906-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4526,10 +4516,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45840</v>
+        <v>44575</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4542,7 +4532,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4585,7 +4575,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 61260-2025</t>
+          <t>A 59853-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4599,10 +4589,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46000</v>
+        <v>44908</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4615,7 +4605,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4658,7 +4648,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 59805-2024</t>
+          <t>A 8193-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4672,10 +4662,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45639</v>
+        <v>44974</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4687,8 +4677,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>3</v>
+        <v>10.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4731,7 +4726,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 39717-2023</t>
+          <t>A 8228-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4745,10 +4740,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45167</v>
+        <v>44974</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4761,7 +4756,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.3</v>
+        <v>13.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4804,7 +4799,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 38308-2023</t>
+          <t>A 31883-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4818,10 +4813,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45161</v>
+        <v>44777</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4834,7 +4829,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4877,7 +4872,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 55003-2022</t>
+          <t>A 23574-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4891,10 +4886,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44886</v>
+        <v>45077</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4907,7 +4902,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>6.6</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4950,7 +4945,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 47123-2024</t>
+          <t>A 26382-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4964,10 +4959,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45586</v>
+        <v>45092</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4979,8 +4974,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>5.3</v>
+        <v>20.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5023,7 +5023,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 40815-2022</t>
+          <t>A 52789-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5037,10 +5037,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44824</v>
+        <v>45610</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>15.9</v>
+        <v>2.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 35521-2026</t>
+          <t>A 19420-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5110,10 +5110,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46262</v>
+        <v>45429</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5125,13 +5125,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>6.2</v>
+        <v>3.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5174,7 +5169,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 35459-2026</t>
+          <t>A 60754-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5188,10 +5183,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46262</v>
+        <v>45644</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5204,7 +5199,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5247,7 +5242,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 10516-2022</t>
+          <t>A 24023-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5261,10 +5256,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44623</v>
+        <v>45796</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5277,7 +5272,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5320,7 +5315,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 10517-2022</t>
+          <t>A 35521-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5334,10 +5329,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44623</v>
+        <v>46262</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5349,8 +5344,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>6.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5393,7 +5393,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 37045-2026</t>
+          <t>A 35459-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5407,10 +5407,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46273</v>
+        <v>46262</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5422,13 +5422,8 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>7.6</v>
+        <v>3.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5471,7 +5466,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 37054-2026</t>
+          <t>A 37045-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5488,7 +5483,7 @@
         <v>46273</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5506,7 +5501,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>6.3</v>
+        <v>7.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5549,7 +5544,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 37865-2026</t>
+          <t>A 37054-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5563,10 +5558,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46279</v>
+        <v>46273</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5584,7 +5579,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>9.1</v>
+        <v>6.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5627,7 +5622,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 6734-2022</t>
+          <t>A 37865-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5641,10 +5636,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44602</v>
+        <v>46279</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5656,8 +5651,13 @@
           <t>KUNGSÖR</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>32.3</v>
+        <v>9.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5697,78 +5697,224 @@
       </c>
       <c r="V65" s="2" t="inlineStr"/>
     </row>
-    <row r="66">
+    <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
+          <t>A 45191-2026</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D66" s="1" t="n">
+        <v>46325</v>
+      </c>
+      <c r="E66" s="1" t="n">
+        <v>46326</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>KUNGSÖR</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>10</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67" ht="15" customHeight="1">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>A 45192-2026</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D67" s="1" t="n">
+        <v>46325</v>
+      </c>
+      <c r="E67" s="1" t="n">
+        <v>46326</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>KUNGSÖR</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>S 1310-2022</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>Skogsgödsling</t>
         </is>
       </c>
-      <c r="D66" s="1" t="n">
+      <c r="D68" s="1" t="n">
         <v>44628</v>
       </c>
-      <c r="E66" s="1" t="n">
-        <v>46324</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>KUNGSÖR</t>
-        </is>
-      </c>
-      <c r="I66" t="n">
+      <c r="E68" s="1" t="n">
+        <v>46326</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>KUNGSÖR</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
         <v>36.9</v>
       </c>
-      <c r="J66" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" t="n">
-        <v>0</v>
-      </c>
-      <c r="T66" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" t="n">
-        <v>0</v>
-      </c>
-      <c r="V66" s="2" t="inlineStr"/>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
